--- a/parcelamentos_local.xlsx
+++ b/parcelamentos_local.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.121.21.252\controladoria\Vitor\TRIBUTARIO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3F6A7E3-F71E-4C60-AB83-7CCCE56916EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71E595A2-57D5-4FA1-BA2F-B8E781543CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="804" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="804" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="PARCELAMENTOS" sheetId="1" r:id="rId1"/>
-    <sheet name="PARCELAMENTO 06062024" sheetId="4" r:id="rId2"/>
-    <sheet name="PARCELAMENTO 05122024" sheetId="2" r:id="rId3"/>
-    <sheet name="PARCELAMENTO 06062025" sheetId="10" r:id="rId4"/>
-    <sheet name="PARCELAMENTO 25112025 " sheetId="13" r:id="rId5"/>
-    <sheet name="PARCELAMENTO SC" sheetId="12" r:id="rId6"/>
-    <sheet name="IMPOSTOS NÃO PARCELADOS" sheetId="9" r:id="rId7"/>
-    <sheet name="ACOMPANHAMENTO MENSAL" sheetId="11" r:id="rId8"/>
+    <sheet name="SALDO CREDOR INSS" sheetId="14" r:id="rId1"/>
+    <sheet name="PARCELAMENTOS" sheetId="1" r:id="rId2"/>
+    <sheet name="PARCELAMENTO 06062024" sheetId="4" r:id="rId3"/>
+    <sheet name="PARCELAMENTO 05122024" sheetId="2" r:id="rId4"/>
+    <sheet name="PARCELAMENTO 06062025" sheetId="10" r:id="rId5"/>
+    <sheet name="PARCELAMENTO 25112025 " sheetId="13" r:id="rId6"/>
+    <sheet name="PARCELAMENTO SC" sheetId="12" r:id="rId7"/>
+    <sheet name="IMPOSTOS NÃO PARCELADOS" sheetId="9" r:id="rId8"/>
+    <sheet name="ACOMPANHAMENTO MENSAL" sheetId="11" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -104,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="111">
   <si>
     <t>TAURA AGRONEGOCIOS - IMPOSTOS EM ABERTO - NÃO PARCELADOS NA RECEITA FEDERAL</t>
   </si>
@@ -423,6 +424,21 @@
   <si>
     <t>Parcelamento 25/11/2025</t>
   </si>
+  <si>
+    <t>SALDO CREDOR INSS - JLE</t>
+  </si>
+  <si>
+    <t>COMPETÊNCIA</t>
+  </si>
+  <si>
+    <t>RETENÇÃO NF</t>
+  </si>
+  <si>
+    <t>UTILIZADO FOLHA</t>
+  </si>
+  <si>
+    <t>SALDO</t>
+  </si>
 </sst>
 </file>
 
@@ -433,7 +449,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;* #,##0.00_-;\-&quot;R$&quot;* #,##0.00_-;_-&quot;R$&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -562,6 +578,34 @@
       <b/>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -956,7 +1000,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1156,6 +1200,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="43" fontId="3" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1172,18 +1228,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1203,6 +1247,61 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="18" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="5" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="5" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="39" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="20" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="21" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="19" fillId="5" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="19" fillId="5" borderId="11" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="19" fillId="5" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="19" fillId="5" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="39" fontId="19" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="39" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="21" fillId="8" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -4802,6 +4901,538 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A737B4A5-C227-4B65-8FEE-4CA1A32A001E}">
+  <dimension ref="A1:G61"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5.33203125" style="114" customWidth="1"/>
+    <col min="2" max="2" width="11.77734375" style="114" customWidth="1"/>
+    <col min="3" max="3" width="18" style="114" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.77734375" style="114" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" style="114" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.6640625" style="114" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" style="114" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.88671875" style="114" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" style="114" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.88671875" style="114" customWidth="1"/>
+    <col min="11" max="11" width="2.5546875" style="114" customWidth="1"/>
+    <col min="12" max="13" width="15.44140625" style="114" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="13.88671875" style="114" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.88671875" style="114" customWidth="1"/>
+    <col min="17" max="17" width="15.44140625" style="114" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.6640625" style="114" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.88671875" style="114"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="18.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="113"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+    </row>
+    <row r="2" spans="1:7" s="115" customFormat="1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="116"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+    </row>
+    <row r="3" spans="1:7" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="117"/>
+      <c r="C3" s="117"/>
+      <c r="D3" s="117"/>
+      <c r="E3" s="117"/>
+      <c r="F3" s="117"/>
+      <c r="G3" s="117"/>
+    </row>
+    <row r="4" spans="1:7" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="117"/>
+      <c r="C4" s="117"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+    </row>
+    <row r="5" spans="1:7" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="117"/>
+      <c r="C5" s="117"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="117"/>
+      <c r="G5" s="117"/>
+    </row>
+    <row r="6" spans="1:7" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="118"/>
+      <c r="B6" s="119"/>
+      <c r="C6" s="119"/>
+      <c r="D6" s="119"/>
+      <c r="E6" s="119"/>
+      <c r="F6" s="119"/>
+      <c r="G6" s="119"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="113"/>
+      <c r="B8" s="130" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8" s="130"/>
+      <c r="D8" s="120"/>
+      <c r="E8" s="120"/>
+      <c r="F8" s="120"/>
+      <c r="G8" s="120"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="113"/>
+      <c r="B9" s="113"/>
+      <c r="C9" s="113"/>
+      <c r="D9" s="121"/>
+      <c r="E9" s="121"/>
+    </row>
+    <row r="10" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="122"/>
+      <c r="B10" s="131" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" s="131" t="s">
+        <v>108</v>
+      </c>
+      <c r="D10" s="131" t="s">
+        <v>109</v>
+      </c>
+      <c r="E10" s="131" t="s">
+        <v>110</v>
+      </c>
+      <c r="F10" s="123"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="124"/>
+      <c r="B11" s="132">
+        <v>46113</v>
+      </c>
+      <c r="C11" s="133">
+        <v>120627.34</v>
+      </c>
+      <c r="D11" s="134">
+        <v>102779.58</v>
+      </c>
+      <c r="E11" s="135">
+        <f>C11-D11</f>
+        <v>17847.759999999995</v>
+      </c>
+      <c r="F11" s="125"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="124"/>
+      <c r="B12" s="132">
+        <v>46143</v>
+      </c>
+      <c r="C12" s="133">
+        <v>126667.52</v>
+      </c>
+      <c r="D12" s="134">
+        <v>103847.05</v>
+      </c>
+      <c r="E12" s="135">
+        <f t="shared" ref="E12:E19" si="0">C12-D12</f>
+        <v>22820.47</v>
+      </c>
+      <c r="F12" s="126"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="124"/>
+      <c r="B13" s="132">
+        <v>46174</v>
+      </c>
+      <c r="C13" s="133">
+        <v>152096.76</v>
+      </c>
+      <c r="D13" s="134">
+        <v>95919.98</v>
+      </c>
+      <c r="E13" s="135">
+        <f t="shared" si="0"/>
+        <v>56176.780000000013</v>
+      </c>
+      <c r="F13" s="126"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="124"/>
+      <c r="B14" s="132">
+        <v>46204</v>
+      </c>
+      <c r="C14" s="133">
+        <v>135916.62</v>
+      </c>
+      <c r="D14" s="134">
+        <v>97086.87</v>
+      </c>
+      <c r="E14" s="135">
+        <f t="shared" si="0"/>
+        <v>38829.75</v>
+      </c>
+      <c r="F14" s="126"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="127"/>
+      <c r="B15" s="132">
+        <v>46235</v>
+      </c>
+      <c r="C15" s="136">
+        <v>124463.52</v>
+      </c>
+      <c r="D15" s="136">
+        <v>107769.34</v>
+      </c>
+      <c r="E15" s="135">
+        <f t="shared" si="0"/>
+        <v>16694.180000000008</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="127"/>
+      <c r="B16" s="132">
+        <v>46266</v>
+      </c>
+      <c r="C16" s="137"/>
+      <c r="D16" s="137"/>
+      <c r="E16" s="135">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="129"/>
+      <c r="B17" s="132">
+        <v>46296</v>
+      </c>
+      <c r="C17" s="137"/>
+      <c r="D17" s="137"/>
+      <c r="E17" s="135">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="127"/>
+      <c r="B18" s="132">
+        <v>46327</v>
+      </c>
+      <c r="C18" s="137"/>
+      <c r="D18" s="137"/>
+      <c r="E18" s="135">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="127"/>
+      <c r="B19" s="132">
+        <v>46357</v>
+      </c>
+      <c r="C19" s="137"/>
+      <c r="D19" s="137"/>
+      <c r="E19" s="135">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="127"/>
+      <c r="B20" s="138"/>
+      <c r="C20" s="138"/>
+      <c r="D20" s="138"/>
+      <c r="E20" s="139">
+        <f>SUM(E11:E19)</f>
+        <v>152368.94</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="127"/>
+      <c r="B21" s="128"/>
+      <c r="C21" s="128"/>
+      <c r="D21" s="128"/>
+      <c r="E21" s="128"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="127"/>
+      <c r="B22" s="128"/>
+      <c r="C22" s="128"/>
+      <c r="D22" s="128"/>
+      <c r="E22" s="128"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="127"/>
+      <c r="B23" s="128"/>
+      <c r="C23" s="128"/>
+      <c r="D23" s="128"/>
+      <c r="E23" s="128"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="127"/>
+      <c r="B24" s="128"/>
+      <c r="C24" s="128"/>
+      <c r="D24" s="128"/>
+      <c r="E24" s="128"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="127"/>
+      <c r="B25" s="128"/>
+      <c r="C25" s="128"/>
+      <c r="D25" s="128"/>
+      <c r="E25" s="128"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="127"/>
+      <c r="B26" s="128"/>
+      <c r="C26" s="128"/>
+      <c r="D26" s="128"/>
+      <c r="E26" s="128"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="127"/>
+      <c r="B27" s="128"/>
+      <c r="C27" s="128"/>
+      <c r="D27" s="128"/>
+      <c r="E27" s="128"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="127"/>
+      <c r="B28" s="128"/>
+      <c r="C28" s="128"/>
+      <c r="D28" s="128"/>
+      <c r="E28" s="128"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="127"/>
+      <c r="B29" s="128"/>
+      <c r="C29" s="128"/>
+      <c r="D29" s="128"/>
+      <c r="E29" s="128"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="127"/>
+      <c r="B30" s="128"/>
+      <c r="C30" s="128"/>
+      <c r="D30" s="128"/>
+      <c r="E30" s="128"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="127"/>
+      <c r="B31" s="128"/>
+      <c r="C31" s="128"/>
+      <c r="D31" s="128"/>
+      <c r="E31" s="128"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="127"/>
+      <c r="B32" s="128"/>
+      <c r="C32" s="128"/>
+      <c r="D32" s="128"/>
+      <c r="E32" s="128"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="127"/>
+      <c r="B33" s="128"/>
+      <c r="C33" s="128"/>
+      <c r="D33" s="128"/>
+      <c r="E33" s="128"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="127"/>
+      <c r="B34" s="128"/>
+      <c r="C34" s="128"/>
+      <c r="D34" s="128"/>
+      <c r="E34" s="128"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="127"/>
+      <c r="B35" s="128"/>
+      <c r="C35" s="128"/>
+      <c r="D35" s="128"/>
+      <c r="E35" s="128"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="127"/>
+      <c r="B36" s="128"/>
+      <c r="C36" s="128"/>
+      <c r="D36" s="128"/>
+      <c r="E36" s="128"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="127"/>
+      <c r="B37" s="128"/>
+      <c r="C37" s="128"/>
+      <c r="D37" s="128"/>
+      <c r="E37" s="128"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="127"/>
+      <c r="B38" s="128"/>
+      <c r="C38" s="128"/>
+      <c r="D38" s="128"/>
+      <c r="E38" s="128"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="127"/>
+      <c r="B39" s="128"/>
+      <c r="C39" s="128"/>
+      <c r="D39" s="128"/>
+      <c r="E39" s="128"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="127"/>
+      <c r="B40" s="128"/>
+      <c r="C40" s="128"/>
+      <c r="D40" s="128"/>
+      <c r="E40" s="128"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="127"/>
+      <c r="B41" s="128"/>
+      <c r="C41" s="128"/>
+      <c r="D41" s="128"/>
+      <c r="E41" s="128"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="127"/>
+      <c r="B42" s="128"/>
+      <c r="C42" s="128"/>
+      <c r="D42" s="128"/>
+      <c r="E42" s="128"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="127"/>
+      <c r="B43" s="128"/>
+      <c r="C43" s="128"/>
+      <c r="D43" s="128"/>
+      <c r="E43" s="128"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="127"/>
+      <c r="B44" s="128"/>
+      <c r="C44" s="128"/>
+      <c r="D44" s="128"/>
+      <c r="E44" s="128"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="127"/>
+      <c r="B45" s="128"/>
+      <c r="C45" s="128"/>
+      <c r="D45" s="128"/>
+      <c r="E45" s="128"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="127"/>
+      <c r="B46" s="128"/>
+      <c r="C46" s="128"/>
+      <c r="D46" s="128"/>
+      <c r="E46" s="128"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="127"/>
+      <c r="B47" s="128"/>
+      <c r="C47" s="128"/>
+      <c r="D47" s="128"/>
+      <c r="E47" s="128"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="127"/>
+      <c r="B48" s="128"/>
+      <c r="C48" s="128"/>
+      <c r="D48" s="128"/>
+      <c r="E48" s="128"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="127"/>
+      <c r="B49" s="128"/>
+      <c r="C49" s="128"/>
+      <c r="D49" s="128"/>
+      <c r="E49" s="128"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="127"/>
+      <c r="B50" s="128"/>
+      <c r="C50" s="128"/>
+      <c r="D50" s="128"/>
+      <c r="E50" s="128"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="127"/>
+      <c r="B51" s="128"/>
+      <c r="C51" s="128"/>
+      <c r="D51" s="128"/>
+      <c r="E51" s="128"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="127"/>
+      <c r="B52" s="128"/>
+      <c r="C52" s="128"/>
+      <c r="D52" s="128"/>
+      <c r="E52" s="128"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="127"/>
+      <c r="B53" s="128"/>
+      <c r="C53" s="128"/>
+      <c r="D53" s="128"/>
+      <c r="E53" s="128"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="127"/>
+      <c r="B54" s="128"/>
+      <c r="C54" s="128"/>
+      <c r="D54" s="128"/>
+      <c r="E54" s="128"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" s="127"/>
+      <c r="B55" s="128"/>
+      <c r="C55" s="128"/>
+      <c r="D55" s="128"/>
+      <c r="E55" s="128"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="127"/>
+      <c r="B56" s="128"/>
+      <c r="C56" s="128"/>
+      <c r="D56" s="128"/>
+      <c r="E56" s="128"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="127"/>
+      <c r="B57" s="128"/>
+      <c r="C57" s="128"/>
+      <c r="D57" s="128"/>
+      <c r="E57" s="128"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="127"/>
+      <c r="E58" s="128"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" s="127"/>
+      <c r="E59" s="128"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" s="127"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" s="127"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B8:C8"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G62"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4824,15 +5455,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="101" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="98"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="98"/>
-      <c r="E1" s="98"/>
-      <c r="F1" s="98"/>
-      <c r="G1" s="99"/>
+      <c r="B1" s="102"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="103"/>
     </row>
     <row r="2" spans="1:7" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -4933,22 +5564,22 @@
     </row>
     <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="100" t="s">
+      <c r="A8" s="104" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="101"/>
-      <c r="C8" s="102"/>
+      <c r="B8" s="105"/>
+      <c r="C8" s="106"/>
       <c r="D8" s="12"/>
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
       <c r="G8" s="12"/>
     </row>
     <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="100" t="s">
+      <c r="A9" s="104" t="s">
         <v>97</v>
       </c>
-      <c r="B9" s="101"/>
-      <c r="C9" s="102"/>
+      <c r="B9" s="105"/>
+      <c r="C9" s="106"/>
       <c r="D9" s="13"/>
       <c r="E9" s="13"/>
     </row>
@@ -5391,7 +6022,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:R85"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5602,10 +6233,10 @@
         <f>M5-I6</f>
         <v>511198.30999999994</v>
       </c>
-      <c r="O6" s="103" t="s">
+      <c r="O6" s="97" t="s">
         <v>89</v>
       </c>
-      <c r="P6" s="103"/>
+      <c r="P6" s="97"/>
       <c r="Q6" s="82">
         <f>(Q4/O4)-1</f>
         <v>-0.43333314486548447</v>
@@ -5736,11 +6367,11 @@
         <f>M8-I9</f>
         <v>484757.02999999991</v>
       </c>
-      <c r="O9" s="104" t="s">
+      <c r="O9" s="98" t="s">
         <v>87</v>
       </c>
-      <c r="P9" s="104"/>
-      <c r="Q9" s="104"/>
+      <c r="P9" s="98"/>
+      <c r="Q9" s="98"/>
     </row>
     <row r="10" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="81" t="s">
@@ -5782,11 +6413,11 @@
         <f t="shared" ref="M10:M63" si="2">M9-I10</f>
         <v>475943.2699999999</v>
       </c>
-      <c r="O10" s="105" t="s">
+      <c r="O10" s="99" t="s">
         <v>88</v>
       </c>
-      <c r="P10" s="105"/>
-      <c r="Q10" s="105"/>
+      <c r="P10" s="99"/>
+      <c r="Q10" s="99"/>
     </row>
     <row r="11" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="81" t="s">
@@ -5828,11 +6459,11 @@
         <f t="shared" si="2"/>
         <v>467129.50999999989</v>
       </c>
-      <c r="O11" s="106" t="s">
+      <c r="O11" s="100" t="s">
         <v>90</v>
       </c>
-      <c r="P11" s="106"/>
-      <c r="Q11" s="106"/>
+      <c r="P11" s="100"/>
+      <c r="Q11" s="100"/>
     </row>
     <row r="12" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="83" t="s">
@@ -7430,7 +8061,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:R125"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7638,10 +8269,10 @@
         <f>M5-I6</f>
         <v>1073254.2800000003</v>
       </c>
-      <c r="O6" s="103" t="s">
+      <c r="O6" s="97" t="s">
         <v>89</v>
       </c>
-      <c r="P6" s="103"/>
+      <c r="P6" s="97"/>
       <c r="Q6" s="82">
         <f>Q4/O4-1</f>
         <v>-0.3333332612783364</v>
@@ -7816,11 +8447,11 @@
         <f t="shared" si="2"/>
         <v>999236.76000000036</v>
       </c>
-      <c r="O10" s="104" t="s">
+      <c r="O10" s="98" t="s">
         <v>87</v>
       </c>
-      <c r="P10" s="104"/>
-      <c r="Q10" s="104"/>
+      <c r="P10" s="98"/>
+      <c r="Q10" s="98"/>
     </row>
     <row r="11" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="79" t="s">
@@ -7862,11 +8493,11 @@
         <f t="shared" si="2"/>
         <v>980732.38000000035</v>
       </c>
-      <c r="O11" s="105" t="s">
+      <c r="O11" s="99" t="s">
         <v>88</v>
       </c>
-      <c r="P11" s="105"/>
-      <c r="Q11" s="105"/>
+      <c r="P11" s="99"/>
+      <c r="Q11" s="99"/>
     </row>
     <row r="12" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="79" t="s">
@@ -10538,7 +11169,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{076A243B-6594-4F6F-90C2-83485C35A53B}">
   <dimension ref="B1:R85"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10748,10 +11379,10 @@
         <f>M5-I6</f>
         <v>1727211.77</v>
       </c>
-      <c r="O6" s="103" t="s">
+      <c r="O6" s="97" t="s">
         <v>89</v>
       </c>
-      <c r="P6" s="103"/>
+      <c r="P6" s="97"/>
       <c r="Q6" s="82">
         <f>(Q4/O4)-1</f>
         <v>-0.23333330852134659</v>
@@ -10882,11 +11513,11 @@
         <f t="shared" ref="M9:M63" si="2">M8-I9</f>
         <v>1637873.24</v>
       </c>
-      <c r="O9" s="104" t="s">
+      <c r="O9" s="98" t="s">
         <v>87</v>
       </c>
-      <c r="P9" s="104"/>
-      <c r="Q9" s="104"/>
+      <c r="P9" s="98"/>
+      <c r="Q9" s="98"/>
     </row>
     <row r="10" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="81" t="s">
@@ -10928,11 +11559,11 @@
         <f t="shared" si="2"/>
         <v>1608093.73</v>
       </c>
-      <c r="O10" s="105" t="s">
+      <c r="O10" s="99" t="s">
         <v>88</v>
       </c>
-      <c r="P10" s="105"/>
-      <c r="Q10" s="105"/>
+      <c r="P10" s="99"/>
+      <c r="Q10" s="99"/>
     </row>
     <row r="11" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="81" t="s">
@@ -10974,11 +11605,11 @@
         <f t="shared" si="2"/>
         <v>1578314.22</v>
       </c>
-      <c r="O11" s="106" t="s">
+      <c r="O11" s="100" t="s">
         <v>90</v>
       </c>
-      <c r="P11" s="106"/>
-      <c r="Q11" s="106"/>
+      <c r="P11" s="100"/>
+      <c r="Q11" s="100"/>
     </row>
     <row r="12" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="81" t="s">
@@ -12568,7 +13199,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08920BEF-61AE-469B-8613-B03EE9E56473}">
   <dimension ref="B1:R85"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -12750,10 +13381,10 @@
         <f>M5-I6</f>
         <v>88254.450000000012</v>
       </c>
-      <c r="O6" s="103" t="s">
+      <c r="O6" s="97" t="s">
         <v>89</v>
       </c>
-      <c r="P6" s="103"/>
+      <c r="P6" s="97"/>
       <c r="Q6" s="82">
         <f>(Q4/O4)-1</f>
         <v>-0.14999919494129588</v>
@@ -12839,11 +13470,11 @@
         <f t="shared" ref="M9:M63" si="2">M8-I9</f>
         <v>83689.590000000026</v>
       </c>
-      <c r="O9" s="104" t="s">
+      <c r="O9" s="98" t="s">
         <v>87</v>
       </c>
-      <c r="P9" s="104"/>
-      <c r="Q9" s="104"/>
+      <c r="P9" s="98"/>
+      <c r="Q9" s="98"/>
     </row>
     <row r="10" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="39"/>
@@ -12870,11 +13501,11 @@
         <f t="shared" si="2"/>
         <v>82167.97000000003</v>
       </c>
-      <c r="O10" s="105" t="s">
+      <c r="O10" s="99" t="s">
         <v>88</v>
       </c>
-      <c r="P10" s="105"/>
-      <c r="Q10" s="105"/>
+      <c r="P10" s="99"/>
+      <c r="Q10" s="99"/>
     </row>
     <row r="11" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="39"/>
@@ -12901,11 +13532,11 @@
         <f t="shared" si="2"/>
         <v>80646.350000000035</v>
       </c>
-      <c r="O11" s="106" t="s">
+      <c r="O11" s="100" t="s">
         <v>90</v>
       </c>
-      <c r="P11" s="106"/>
-      <c r="Q11" s="106"/>
+      <c r="P11" s="100"/>
+      <c r="Q11" s="100"/>
     </row>
     <row r="12" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="39"/>
@@ -14399,7 +15030,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00D981B1-E026-41C2-8293-91583FAD4939}">
   <dimension ref="B1:R58"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -14567,10 +15198,10 @@
         <f>M5-I6</f>
         <v>-501.4</v>
       </c>
-      <c r="O6" s="103" t="s">
+      <c r="O6" s="97" t="s">
         <v>89</v>
       </c>
-      <c r="P6" s="103"/>
+      <c r="P6" s="97"/>
       <c r="Q6" s="82">
         <f>(Q4/O4)-1</f>
         <v>-0.33618406919008692</v>
@@ -15581,7 +16212,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D05F36B-D5CF-4328-B814-E173D67EEF77}">
   <dimension ref="B1:Z28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -16525,7 +17156,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{420301BD-1EC9-404C-9D58-1869DDAA2327}">
   <dimension ref="B2:P9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/parcelamentos_local.xlsx
+++ b/parcelamentos_local.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.121.21.252\controladoria\Vitor\TRIBUTARIO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71E595A2-57D5-4FA1-BA2F-B8E781543CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B86B63A-7FD0-4B44-96DC-720567504730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="804" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="804" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SALDO CREDOR INSS" sheetId="14" r:id="rId1"/>
@@ -1000,7 +1000,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="140">
+  <cellXfs count="139">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1200,16 +1200,58 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="43" fontId="3" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="18" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="5" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="4" fillId="5" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="39" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="20" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="21" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="19" fillId="5" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="19" fillId="5" borderId="11" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="19" fillId="5" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="19" fillId="5" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="39" fontId="19" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="39" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="21" fillId="8" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1230,6 +1272,18 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1247,61 +1301,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="18" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="5" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="5" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="39" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="20" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="21" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="19" fillId="5" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="19" fillId="5" borderId="11" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="19" fillId="5" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="19" fillId="5" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="39" fontId="19" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="39" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="21" fillId="8" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2790,10 +2789,10 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>'ACOMPANHAMENTO MENSAL'!$C$2:$P$2</c:f>
+              <c:f>'ACOMPANHAMENTO MENSAL'!$C$2:$Q$2</c:f>
               <c:numCache>
                 <c:formatCode>mmm\-yy</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>45839</c:v>
                 </c:pt>
@@ -2835,16 +2834,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>46235</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46266</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ACOMPANHAMENTO MENSAL'!$C$3:$P$3</c:f>
+              <c:f>'ACOMPANHAMENTO MENSAL'!$C$3:$Q$3</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>4720740.33</c:v>
                 </c:pt>
@@ -2886,6 +2888,9 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>3196894.17</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3796974.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2922,10 +2927,10 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>'ACOMPANHAMENTO MENSAL'!$C$2:$P$2</c:f>
+              <c:f>'ACOMPANHAMENTO MENSAL'!$C$2:$Q$2</c:f>
               <c:numCache>
                 <c:formatCode>mmm\-yy</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>45839</c:v>
                 </c:pt>
@@ -2967,6 +2972,9 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>46235</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46266</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3054,10 +3062,10 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>'ACOMPANHAMENTO MENSAL'!$C$2:$P$2</c:f>
+              <c:f>'ACOMPANHAMENTO MENSAL'!$C$2:$Q$2</c:f>
               <c:numCache>
                 <c:formatCode>mmm\-yy</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>45839</c:v>
                 </c:pt>
@@ -3099,16 +3107,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>46235</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46266</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ACOMPANHAMENTO MENSAL'!$C$5:$P$5</c:f>
+              <c:f>'ACOMPANHAMENTO MENSAL'!$C$5:$Q$5</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>23389.74</c:v>
                 </c:pt>
@@ -3147,6 +3158,9 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>53315.91</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16179.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3183,10 +3197,10 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>'ACOMPANHAMENTO MENSAL'!$C$2:$P$2</c:f>
+              <c:f>'ACOMPANHAMENTO MENSAL'!$C$2:$Q$2</c:f>
               <c:numCache>
                 <c:formatCode>mmm\-yy</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>45839</c:v>
                 </c:pt>
@@ -3228,16 +3242,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>46235</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46266</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ACOMPANHAMENTO MENSAL'!$C$6:$P$6</c:f>
+              <c:f>'ACOMPANHAMENTO MENSAL'!$C$6:$Q$6</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>107597.6</c:v>
                 </c:pt>
@@ -3279,6 +3296,9 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>245472</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>74452.63</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3315,10 +3335,10 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>'ACOMPANHAMENTO MENSAL'!$C$2:$P$2</c:f>
+              <c:f>'ACOMPANHAMENTO MENSAL'!$C$2:$Q$2</c:f>
               <c:numCache>
                 <c:formatCode>mmm\-yy</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>45839</c:v>
                 </c:pt>
@@ -3360,6 +3380,9 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>46235</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46266</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3426,10 +3449,10 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>'ACOMPANHAMENTO MENSAL'!$C$2:$P$2</c:f>
+              <c:f>'ACOMPANHAMENTO MENSAL'!$C$2:$Q$2</c:f>
               <c:numCache>
                 <c:formatCode>mmm\-yy</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>45839</c:v>
                 </c:pt>
@@ -3471,6 +3494,9 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>46235</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46266</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4905,523 +4931,523 @@
   <dimension ref="A1:G61"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="114" customWidth="1"/>
-    <col min="2" max="2" width="11.77734375" style="114" customWidth="1"/>
-    <col min="3" max="3" width="18" style="114" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.77734375" style="114" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" style="114" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.6640625" style="114" customWidth="1"/>
-    <col min="7" max="7" width="15.88671875" style="114" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.88671875" style="114" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" style="114" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.88671875" style="114" customWidth="1"/>
-    <col min="11" max="11" width="2.5546875" style="114" customWidth="1"/>
-    <col min="12" max="13" width="15.44140625" style="114" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="13.88671875" style="114" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.88671875" style="114" customWidth="1"/>
-    <col min="17" max="17" width="15.44140625" style="114" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.6640625" style="114" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="8.88671875" style="114"/>
+    <col min="1" max="1" width="5.33203125" style="98" customWidth="1"/>
+    <col min="2" max="2" width="11.77734375" style="98" customWidth="1"/>
+    <col min="3" max="3" width="18" style="98" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.77734375" style="98" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" style="98" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.6640625" style="98" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" style="98" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.88671875" style="98" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" style="98" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.88671875" style="98" customWidth="1"/>
+    <col min="11" max="11" width="2.5546875" style="98" customWidth="1"/>
+    <col min="12" max="13" width="15.44140625" style="98" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="13.88671875" style="98" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.88671875" style="98" customWidth="1"/>
+    <col min="17" max="17" width="15.44140625" style="98" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.6640625" style="98" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.88671875" style="98"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="113"/>
-      <c r="B1" s="113"/>
-      <c r="C1" s="113"/>
-      <c r="D1" s="113"/>
-      <c r="E1" s="113"/>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-    </row>
-    <row r="2" spans="1:7" s="115" customFormat="1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="116"/>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
+      <c r="A1" s="97"/>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
+    </row>
+    <row r="2" spans="1:7" s="99" customFormat="1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="100"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
     </row>
     <row r="3" spans="1:7" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="117"/>
-      <c r="C3" s="117"/>
-      <c r="D3" s="117"/>
-      <c r="E3" s="117"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="117"/>
+      <c r="B3" s="101"/>
+      <c r="C3" s="101"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="101"/>
+      <c r="F3" s="101"/>
+      <c r="G3" s="101"/>
     </row>
     <row r="4" spans="1:7" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="117"/>
-      <c r="C4" s="117"/>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
+      <c r="B4" s="101"/>
+      <c r="C4" s="101"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="101"/>
     </row>
     <row r="5" spans="1:7" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="117"/>
-      <c r="C5" s="117"/>
-      <c r="D5" s="117"/>
-      <c r="E5" s="117"/>
-      <c r="F5" s="117"/>
-      <c r="G5" s="117"/>
+      <c r="B5" s="101"/>
+      <c r="C5" s="101"/>
+      <c r="D5" s="101"/>
+      <c r="E5" s="101"/>
+      <c r="F5" s="101"/>
+      <c r="G5" s="101"/>
     </row>
     <row r="6" spans="1:7" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="118"/>
-      <c r="B6" s="119"/>
-      <c r="C6" s="119"/>
-      <c r="D6" s="119"/>
-      <c r="E6" s="119"/>
-      <c r="F6" s="119"/>
-      <c r="G6" s="119"/>
+      <c r="A6" s="97"/>
+      <c r="B6" s="102"/>
+      <c r="C6" s="102"/>
+      <c r="D6" s="102"/>
+      <c r="E6" s="102"/>
+      <c r="F6" s="102"/>
+      <c r="G6" s="102"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="113"/>
-      <c r="B8" s="130" t="s">
+      <c r="A8" s="97"/>
+      <c r="B8" s="122" t="s">
         <v>106</v>
       </c>
-      <c r="C8" s="130"/>
-      <c r="D8" s="120"/>
-      <c r="E8" s="120"/>
-      <c r="F8" s="120"/>
-      <c r="G8" s="120"/>
+      <c r="C8" s="122"/>
+      <c r="D8" s="103"/>
+      <c r="E8" s="103"/>
+      <c r="F8" s="103"/>
+      <c r="G8" s="103"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="113"/>
-      <c r="B9" s="113"/>
-      <c r="C9" s="113"/>
-      <c r="D9" s="121"/>
-      <c r="E9" s="121"/>
+      <c r="A9" s="97"/>
+      <c r="B9" s="97"/>
+      <c r="C9" s="97"/>
+      <c r="D9" s="104"/>
+      <c r="E9" s="104"/>
     </row>
     <row r="10" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="122"/>
-      <c r="B10" s="131" t="s">
+      <c r="A10" s="105"/>
+      <c r="B10" s="113" t="s">
         <v>107</v>
       </c>
-      <c r="C10" s="131" t="s">
+      <c r="C10" s="113" t="s">
         <v>108</v>
       </c>
-      <c r="D10" s="131" t="s">
+      <c r="D10" s="113" t="s">
         <v>109</v>
       </c>
-      <c r="E10" s="131" t="s">
+      <c r="E10" s="113" t="s">
         <v>110</v>
       </c>
-      <c r="F10" s="123"/>
+      <c r="F10" s="106"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="124"/>
-      <c r="B11" s="132">
+      <c r="A11" s="107"/>
+      <c r="B11" s="114">
         <v>46113</v>
       </c>
-      <c r="C11" s="133">
+      <c r="C11" s="115">
         <v>120627.34</v>
       </c>
-      <c r="D11" s="134">
+      <c r="D11" s="116">
         <v>102779.58</v>
       </c>
-      <c r="E11" s="135">
+      <c r="E11" s="117">
         <f>C11-D11</f>
         <v>17847.759999999995</v>
       </c>
-      <c r="F11" s="125"/>
+      <c r="F11" s="108"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="124"/>
-      <c r="B12" s="132">
+      <c r="A12" s="107"/>
+      <c r="B12" s="114">
         <v>46143</v>
       </c>
-      <c r="C12" s="133">
+      <c r="C12" s="115">
         <v>126667.52</v>
       </c>
-      <c r="D12" s="134">
+      <c r="D12" s="116">
         <v>103847.05</v>
       </c>
-      <c r="E12" s="135">
+      <c r="E12" s="117">
         <f t="shared" ref="E12:E19" si="0">C12-D12</f>
         <v>22820.47</v>
       </c>
-      <c r="F12" s="126"/>
+      <c r="F12" s="109"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="124"/>
-      <c r="B13" s="132">
+      <c r="A13" s="107"/>
+      <c r="B13" s="114">
         <v>46174</v>
       </c>
-      <c r="C13" s="133">
+      <c r="C13" s="115">
         <v>152096.76</v>
       </c>
-      <c r="D13" s="134">
+      <c r="D13" s="116">
         <v>95919.98</v>
       </c>
-      <c r="E13" s="135">
+      <c r="E13" s="117">
         <f t="shared" si="0"/>
         <v>56176.780000000013</v>
       </c>
-      <c r="F13" s="126"/>
+      <c r="F13" s="109"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="124"/>
-      <c r="B14" s="132">
+      <c r="A14" s="107"/>
+      <c r="B14" s="114">
         <v>46204</v>
       </c>
-      <c r="C14" s="133">
+      <c r="C14" s="115">
         <v>135916.62</v>
       </c>
-      <c r="D14" s="134">
+      <c r="D14" s="116">
         <v>97086.87</v>
       </c>
-      <c r="E14" s="135">
+      <c r="E14" s="117">
         <f t="shared" si="0"/>
         <v>38829.75</v>
       </c>
-      <c r="F14" s="126"/>
+      <c r="F14" s="109"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="127"/>
-      <c r="B15" s="132">
+      <c r="A15" s="110"/>
+      <c r="B15" s="114">
         <v>46235</v>
       </c>
-      <c r="C15" s="136">
+      <c r="C15" s="118">
         <v>124463.52</v>
       </c>
-      <c r="D15" s="136">
+      <c r="D15" s="118">
         <v>107769.34</v>
       </c>
-      <c r="E15" s="135">
+      <c r="E15" s="117">
         <f t="shared" si="0"/>
         <v>16694.180000000008</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="127"/>
-      <c r="B16" s="132">
+      <c r="A16" s="110"/>
+      <c r="B16" s="114">
         <v>46266</v>
       </c>
-      <c r="C16" s="137"/>
-      <c r="D16" s="137"/>
-      <c r="E16" s="135">
+      <c r="C16" s="119"/>
+      <c r="D16" s="119"/>
+      <c r="E16" s="117">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="129"/>
-      <c r="B17" s="132">
+      <c r="A17" s="112"/>
+      <c r="B17" s="114">
         <v>46296</v>
       </c>
-      <c r="C17" s="137"/>
-      <c r="D17" s="137"/>
-      <c r="E17" s="135">
+      <c r="C17" s="119"/>
+      <c r="D17" s="119"/>
+      <c r="E17" s="117">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="127"/>
-      <c r="B18" s="132">
+      <c r="A18" s="110"/>
+      <c r="B18" s="114">
         <v>46327</v>
       </c>
-      <c r="C18" s="137"/>
-      <c r="D18" s="137"/>
-      <c r="E18" s="135">
+      <c r="C18" s="119"/>
+      <c r="D18" s="119"/>
+      <c r="E18" s="117">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="127"/>
-      <c r="B19" s="132">
+      <c r="A19" s="110"/>
+      <c r="B19" s="114">
         <v>46357</v>
       </c>
-      <c r="C19" s="137"/>
-      <c r="D19" s="137"/>
-      <c r="E19" s="135">
+      <c r="C19" s="119"/>
+      <c r="D19" s="119"/>
+      <c r="E19" s="117">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="127"/>
-      <c r="B20" s="138"/>
-      <c r="C20" s="138"/>
-      <c r="D20" s="138"/>
-      <c r="E20" s="139">
+      <c r="A20" s="110"/>
+      <c r="B20" s="120"/>
+      <c r="C20" s="120"/>
+      <c r="D20" s="120"/>
+      <c r="E20" s="121">
         <f>SUM(E11:E19)</f>
         <v>152368.94</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="127"/>
-      <c r="B21" s="128"/>
-      <c r="C21" s="128"/>
-      <c r="D21" s="128"/>
-      <c r="E21" s="128"/>
+      <c r="A21" s="110"/>
+      <c r="B21" s="111"/>
+      <c r="C21" s="111"/>
+      <c r="D21" s="111"/>
+      <c r="E21" s="111"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="127"/>
-      <c r="B22" s="128"/>
-      <c r="C22" s="128"/>
-      <c r="D22" s="128"/>
-      <c r="E22" s="128"/>
+      <c r="A22" s="110"/>
+      <c r="B22" s="111"/>
+      <c r="C22" s="111"/>
+      <c r="D22" s="111"/>
+      <c r="E22" s="111"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="127"/>
-      <c r="B23" s="128"/>
-      <c r="C23" s="128"/>
-      <c r="D23" s="128"/>
-      <c r="E23" s="128"/>
+      <c r="A23" s="110"/>
+      <c r="B23" s="111"/>
+      <c r="C23" s="111"/>
+      <c r="D23" s="111"/>
+      <c r="E23" s="111"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="127"/>
-      <c r="B24" s="128"/>
-      <c r="C24" s="128"/>
-      <c r="D24" s="128"/>
-      <c r="E24" s="128"/>
+      <c r="A24" s="110"/>
+      <c r="B24" s="111"/>
+      <c r="C24" s="111"/>
+      <c r="D24" s="111"/>
+      <c r="E24" s="111"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="127"/>
-      <c r="B25" s="128"/>
-      <c r="C25" s="128"/>
-      <c r="D25" s="128"/>
-      <c r="E25" s="128"/>
+      <c r="A25" s="110"/>
+      <c r="B25" s="111"/>
+      <c r="C25" s="111"/>
+      <c r="D25" s="111"/>
+      <c r="E25" s="111"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="127"/>
-      <c r="B26" s="128"/>
-      <c r="C26" s="128"/>
-      <c r="D26" s="128"/>
-      <c r="E26" s="128"/>
+      <c r="A26" s="110"/>
+      <c r="B26" s="111"/>
+      <c r="C26" s="111"/>
+      <c r="D26" s="111"/>
+      <c r="E26" s="111"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="127"/>
-      <c r="B27" s="128"/>
-      <c r="C27" s="128"/>
-      <c r="D27" s="128"/>
-      <c r="E27" s="128"/>
+      <c r="A27" s="110"/>
+      <c r="B27" s="111"/>
+      <c r="C27" s="111"/>
+      <c r="D27" s="111"/>
+      <c r="E27" s="111"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="127"/>
-      <c r="B28" s="128"/>
-      <c r="C28" s="128"/>
-      <c r="D28" s="128"/>
-      <c r="E28" s="128"/>
+      <c r="A28" s="110"/>
+      <c r="B28" s="111"/>
+      <c r="C28" s="111"/>
+      <c r="D28" s="111"/>
+      <c r="E28" s="111"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="127"/>
-      <c r="B29" s="128"/>
-      <c r="C29" s="128"/>
-      <c r="D29" s="128"/>
-      <c r="E29" s="128"/>
+      <c r="A29" s="110"/>
+      <c r="B29" s="111"/>
+      <c r="C29" s="111"/>
+      <c r="D29" s="111"/>
+      <c r="E29" s="111"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="127"/>
-      <c r="B30" s="128"/>
-      <c r="C30" s="128"/>
-      <c r="D30" s="128"/>
-      <c r="E30" s="128"/>
+      <c r="A30" s="110"/>
+      <c r="B30" s="111"/>
+      <c r="C30" s="111"/>
+      <c r="D30" s="111"/>
+      <c r="E30" s="111"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="127"/>
-      <c r="B31" s="128"/>
-      <c r="C31" s="128"/>
-      <c r="D31" s="128"/>
-      <c r="E31" s="128"/>
+      <c r="A31" s="110"/>
+      <c r="B31" s="111"/>
+      <c r="C31" s="111"/>
+      <c r="D31" s="111"/>
+      <c r="E31" s="111"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="127"/>
-      <c r="B32" s="128"/>
-      <c r="C32" s="128"/>
-      <c r="D32" s="128"/>
-      <c r="E32" s="128"/>
+      <c r="A32" s="110"/>
+      <c r="B32" s="111"/>
+      <c r="C32" s="111"/>
+      <c r="D32" s="111"/>
+      <c r="E32" s="111"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="127"/>
-      <c r="B33" s="128"/>
-      <c r="C33" s="128"/>
-      <c r="D33" s="128"/>
-      <c r="E33" s="128"/>
+      <c r="A33" s="110"/>
+      <c r="B33" s="111"/>
+      <c r="C33" s="111"/>
+      <c r="D33" s="111"/>
+      <c r="E33" s="111"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="127"/>
-      <c r="B34" s="128"/>
-      <c r="C34" s="128"/>
-      <c r="D34" s="128"/>
-      <c r="E34" s="128"/>
+      <c r="A34" s="110"/>
+      <c r="B34" s="111"/>
+      <c r="C34" s="111"/>
+      <c r="D34" s="111"/>
+      <c r="E34" s="111"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="127"/>
-      <c r="B35" s="128"/>
-      <c r="C35" s="128"/>
-      <c r="D35" s="128"/>
-      <c r="E35" s="128"/>
+      <c r="A35" s="110"/>
+      <c r="B35" s="111"/>
+      <c r="C35" s="111"/>
+      <c r="D35" s="111"/>
+      <c r="E35" s="111"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="127"/>
-      <c r="B36" s="128"/>
-      <c r="C36" s="128"/>
-      <c r="D36" s="128"/>
-      <c r="E36" s="128"/>
+      <c r="A36" s="110"/>
+      <c r="B36" s="111"/>
+      <c r="C36" s="111"/>
+      <c r="D36" s="111"/>
+      <c r="E36" s="111"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="127"/>
-      <c r="B37" s="128"/>
-      <c r="C37" s="128"/>
-      <c r="D37" s="128"/>
-      <c r="E37" s="128"/>
+      <c r="A37" s="110"/>
+      <c r="B37" s="111"/>
+      <c r="C37" s="111"/>
+      <c r="D37" s="111"/>
+      <c r="E37" s="111"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="127"/>
-      <c r="B38" s="128"/>
-      <c r="C38" s="128"/>
-      <c r="D38" s="128"/>
-      <c r="E38" s="128"/>
+      <c r="A38" s="110"/>
+      <c r="B38" s="111"/>
+      <c r="C38" s="111"/>
+      <c r="D38" s="111"/>
+      <c r="E38" s="111"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="127"/>
-      <c r="B39" s="128"/>
-      <c r="C39" s="128"/>
-      <c r="D39" s="128"/>
-      <c r="E39" s="128"/>
+      <c r="A39" s="110"/>
+      <c r="B39" s="111"/>
+      <c r="C39" s="111"/>
+      <c r="D39" s="111"/>
+      <c r="E39" s="111"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="127"/>
-      <c r="B40" s="128"/>
-      <c r="C40" s="128"/>
-      <c r="D40" s="128"/>
-      <c r="E40" s="128"/>
+      <c r="A40" s="110"/>
+      <c r="B40" s="111"/>
+      <c r="C40" s="111"/>
+      <c r="D40" s="111"/>
+      <c r="E40" s="111"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="127"/>
-      <c r="B41" s="128"/>
-      <c r="C41" s="128"/>
-      <c r="D41" s="128"/>
-      <c r="E41" s="128"/>
+      <c r="A41" s="110"/>
+      <c r="B41" s="111"/>
+      <c r="C41" s="111"/>
+      <c r="D41" s="111"/>
+      <c r="E41" s="111"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="127"/>
-      <c r="B42" s="128"/>
-      <c r="C42" s="128"/>
-      <c r="D42" s="128"/>
-      <c r="E42" s="128"/>
+      <c r="A42" s="110"/>
+      <c r="B42" s="111"/>
+      <c r="C42" s="111"/>
+      <c r="D42" s="111"/>
+      <c r="E42" s="111"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="127"/>
-      <c r="B43" s="128"/>
-      <c r="C43" s="128"/>
-      <c r="D43" s="128"/>
-      <c r="E43" s="128"/>
+      <c r="A43" s="110"/>
+      <c r="B43" s="111"/>
+      <c r="C43" s="111"/>
+      <c r="D43" s="111"/>
+      <c r="E43" s="111"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="127"/>
-      <c r="B44" s="128"/>
-      <c r="C44" s="128"/>
-      <c r="D44" s="128"/>
-      <c r="E44" s="128"/>
+      <c r="A44" s="110"/>
+      <c r="B44" s="111"/>
+      <c r="C44" s="111"/>
+      <c r="D44" s="111"/>
+      <c r="E44" s="111"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="127"/>
-      <c r="B45" s="128"/>
-      <c r="C45" s="128"/>
-      <c r="D45" s="128"/>
-      <c r="E45" s="128"/>
+      <c r="A45" s="110"/>
+      <c r="B45" s="111"/>
+      <c r="C45" s="111"/>
+      <c r="D45" s="111"/>
+      <c r="E45" s="111"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="127"/>
-      <c r="B46" s="128"/>
-      <c r="C46" s="128"/>
-      <c r="D46" s="128"/>
-      <c r="E46" s="128"/>
+      <c r="A46" s="110"/>
+      <c r="B46" s="111"/>
+      <c r="C46" s="111"/>
+      <c r="D46" s="111"/>
+      <c r="E46" s="111"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="127"/>
-      <c r="B47" s="128"/>
-      <c r="C47" s="128"/>
-      <c r="D47" s="128"/>
-      <c r="E47" s="128"/>
+      <c r="A47" s="110"/>
+      <c r="B47" s="111"/>
+      <c r="C47" s="111"/>
+      <c r="D47" s="111"/>
+      <c r="E47" s="111"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="127"/>
-      <c r="B48" s="128"/>
-      <c r="C48" s="128"/>
-      <c r="D48" s="128"/>
-      <c r="E48" s="128"/>
+      <c r="A48" s="110"/>
+      <c r="B48" s="111"/>
+      <c r="C48" s="111"/>
+      <c r="D48" s="111"/>
+      <c r="E48" s="111"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="127"/>
-      <c r="B49" s="128"/>
-      <c r="C49" s="128"/>
-      <c r="D49" s="128"/>
-      <c r="E49" s="128"/>
+      <c r="A49" s="110"/>
+      <c r="B49" s="111"/>
+      <c r="C49" s="111"/>
+      <c r="D49" s="111"/>
+      <c r="E49" s="111"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" s="127"/>
-      <c r="B50" s="128"/>
-      <c r="C50" s="128"/>
-      <c r="D50" s="128"/>
-      <c r="E50" s="128"/>
+      <c r="A50" s="110"/>
+      <c r="B50" s="111"/>
+      <c r="C50" s="111"/>
+      <c r="D50" s="111"/>
+      <c r="E50" s="111"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="127"/>
-      <c r="B51" s="128"/>
-      <c r="C51" s="128"/>
-      <c r="D51" s="128"/>
-      <c r="E51" s="128"/>
+      <c r="A51" s="110"/>
+      <c r="B51" s="111"/>
+      <c r="C51" s="111"/>
+      <c r="D51" s="111"/>
+      <c r="E51" s="111"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" s="127"/>
-      <c r="B52" s="128"/>
-      <c r="C52" s="128"/>
-      <c r="D52" s="128"/>
-      <c r="E52" s="128"/>
+      <c r="A52" s="110"/>
+      <c r="B52" s="111"/>
+      <c r="C52" s="111"/>
+      <c r="D52" s="111"/>
+      <c r="E52" s="111"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A53" s="127"/>
-      <c r="B53" s="128"/>
-      <c r="C53" s="128"/>
-      <c r="D53" s="128"/>
-      <c r="E53" s="128"/>
+      <c r="A53" s="110"/>
+      <c r="B53" s="111"/>
+      <c r="C53" s="111"/>
+      <c r="D53" s="111"/>
+      <c r="E53" s="111"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="127"/>
-      <c r="B54" s="128"/>
-      <c r="C54" s="128"/>
-      <c r="D54" s="128"/>
-      <c r="E54" s="128"/>
+      <c r="A54" s="110"/>
+      <c r="B54" s="111"/>
+      <c r="C54" s="111"/>
+      <c r="D54" s="111"/>
+      <c r="E54" s="111"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A55" s="127"/>
-      <c r="B55" s="128"/>
-      <c r="C55" s="128"/>
-      <c r="D55" s="128"/>
-      <c r="E55" s="128"/>
+      <c r="A55" s="110"/>
+      <c r="B55" s="111"/>
+      <c r="C55" s="111"/>
+      <c r="D55" s="111"/>
+      <c r="E55" s="111"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" s="127"/>
-      <c r="B56" s="128"/>
-      <c r="C56" s="128"/>
-      <c r="D56" s="128"/>
-      <c r="E56" s="128"/>
+      <c r="A56" s="110"/>
+      <c r="B56" s="111"/>
+      <c r="C56" s="111"/>
+      <c r="D56" s="111"/>
+      <c r="E56" s="111"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57" s="127"/>
-      <c r="B57" s="128"/>
-      <c r="C57" s="128"/>
-      <c r="D57" s="128"/>
-      <c r="E57" s="128"/>
+      <c r="A57" s="110"/>
+      <c r="B57" s="111"/>
+      <c r="C57" s="111"/>
+      <c r="D57" s="111"/>
+      <c r="E57" s="111"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58" s="127"/>
-      <c r="E58" s="128"/>
+      <c r="A58" s="110"/>
+      <c r="E58" s="111"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A59" s="127"/>
-      <c r="E59" s="128"/>
+      <c r="A59" s="110"/>
+      <c r="E59" s="111"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A60" s="127"/>
+      <c r="A60" s="110"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" s="127"/>
+      <c r="A61" s="110"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5455,15 +5481,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="123" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="103"/>
+      <c r="B1" s="124"/>
+      <c r="C1" s="124"/>
+      <c r="D1" s="124"/>
+      <c r="E1" s="124"/>
+      <c r="F1" s="124"/>
+      <c r="G1" s="125"/>
     </row>
     <row r="2" spans="1:7" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -5564,22 +5590,22 @@
     </row>
     <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="104" t="s">
+      <c r="A8" s="126" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="105"/>
-      <c r="C8" s="106"/>
+      <c r="B8" s="127"/>
+      <c r="C8" s="128"/>
       <c r="D8" s="12"/>
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
       <c r="G8" s="12"/>
     </row>
     <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="104" t="s">
+      <c r="A9" s="126" t="s">
         <v>97</v>
       </c>
-      <c r="B9" s="105"/>
-      <c r="C9" s="106"/>
+      <c r="B9" s="127"/>
+      <c r="C9" s="128"/>
       <c r="D9" s="13"/>
       <c r="E9" s="13"/>
     </row>
@@ -6233,10 +6259,10 @@
         <f>M5-I6</f>
         <v>511198.30999999994</v>
       </c>
-      <c r="O6" s="97" t="s">
+      <c r="O6" s="129" t="s">
         <v>89</v>
       </c>
-      <c r="P6" s="97"/>
+      <c r="P6" s="129"/>
       <c r="Q6" s="82">
         <f>(Q4/O4)-1</f>
         <v>-0.43333314486548447</v>
@@ -6367,11 +6393,11 @@
         <f>M8-I9</f>
         <v>484757.02999999991</v>
       </c>
-      <c r="O9" s="98" t="s">
+      <c r="O9" s="130" t="s">
         <v>87</v>
       </c>
-      <c r="P9" s="98"/>
-      <c r="Q9" s="98"/>
+      <c r="P9" s="130"/>
+      <c r="Q9" s="130"/>
     </row>
     <row r="10" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="81" t="s">
@@ -6413,11 +6439,11 @@
         <f t="shared" ref="M10:M63" si="2">M9-I10</f>
         <v>475943.2699999999</v>
       </c>
-      <c r="O10" s="99" t="s">
+      <c r="O10" s="131" t="s">
         <v>88</v>
       </c>
-      <c r="P10" s="99"/>
-      <c r="Q10" s="99"/>
+      <c r="P10" s="131"/>
+      <c r="Q10" s="131"/>
     </row>
     <row r="11" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="81" t="s">
@@ -6459,11 +6485,11 @@
         <f t="shared" si="2"/>
         <v>467129.50999999989</v>
       </c>
-      <c r="O11" s="100" t="s">
+      <c r="O11" s="132" t="s">
         <v>90</v>
       </c>
-      <c r="P11" s="100"/>
-      <c r="Q11" s="100"/>
+      <c r="P11" s="132"/>
+      <c r="Q11" s="132"/>
     </row>
     <row r="12" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="83" t="s">
@@ -8269,10 +8295,10 @@
         <f>M5-I6</f>
         <v>1073254.2800000003</v>
       </c>
-      <c r="O6" s="97" t="s">
+      <c r="O6" s="129" t="s">
         <v>89</v>
       </c>
-      <c r="P6" s="97"/>
+      <c r="P6" s="129"/>
       <c r="Q6" s="82">
         <f>Q4/O4-1</f>
         <v>-0.3333332612783364</v>
@@ -8401,11 +8427,11 @@
         <f t="shared" si="2"/>
         <v>1017741.1400000004</v>
       </c>
-      <c r="O9" s="107" t="s">
+      <c r="O9" s="133" t="s">
         <v>86</v>
       </c>
-      <c r="P9" s="107"/>
-      <c r="Q9" s="107"/>
+      <c r="P9" s="133"/>
+      <c r="Q9" s="133"/>
     </row>
     <row r="10" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="79" t="s">
@@ -8447,11 +8473,11 @@
         <f t="shared" si="2"/>
         <v>999236.76000000036</v>
       </c>
-      <c r="O10" s="98" t="s">
+      <c r="O10" s="130" t="s">
         <v>87</v>
       </c>
-      <c r="P10" s="98"/>
-      <c r="Q10" s="98"/>
+      <c r="P10" s="130"/>
+      <c r="Q10" s="130"/>
     </row>
     <row r="11" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="79" t="s">
@@ -8493,11 +8519,11 @@
         <f t="shared" si="2"/>
         <v>980732.38000000035</v>
       </c>
-      <c r="O11" s="99" t="s">
+      <c r="O11" s="131" t="s">
         <v>88</v>
       </c>
-      <c r="P11" s="99"/>
-      <c r="Q11" s="99"/>
+      <c r="P11" s="131"/>
+      <c r="Q11" s="131"/>
     </row>
     <row r="12" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="79" t="s">
@@ -11379,10 +11405,10 @@
         <f>M5-I6</f>
         <v>1727211.77</v>
       </c>
-      <c r="O6" s="97" t="s">
+      <c r="O6" s="129" t="s">
         <v>89</v>
       </c>
-      <c r="P6" s="97"/>
+      <c r="P6" s="129"/>
       <c r="Q6" s="82">
         <f>(Q4/O4)-1</f>
         <v>-0.23333330852134659</v>
@@ -11513,11 +11539,11 @@
         <f t="shared" ref="M9:M63" si="2">M8-I9</f>
         <v>1637873.24</v>
       </c>
-      <c r="O9" s="98" t="s">
+      <c r="O9" s="130" t="s">
         <v>87</v>
       </c>
-      <c r="P9" s="98"/>
-      <c r="Q9" s="98"/>
+      <c r="P9" s="130"/>
+      <c r="Q9" s="130"/>
     </row>
     <row r="10" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="81" t="s">
@@ -11559,11 +11585,11 @@
         <f t="shared" si="2"/>
         <v>1608093.73</v>
       </c>
-      <c r="O10" s="99" t="s">
+      <c r="O10" s="131" t="s">
         <v>88</v>
       </c>
-      <c r="P10" s="99"/>
-      <c r="Q10" s="99"/>
+      <c r="P10" s="131"/>
+      <c r="Q10" s="131"/>
     </row>
     <row r="11" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="81" t="s">
@@ -11605,11 +11631,11 @@
         <f t="shared" si="2"/>
         <v>1578314.22</v>
       </c>
-      <c r="O11" s="100" t="s">
+      <c r="O11" s="132" t="s">
         <v>90</v>
       </c>
-      <c r="P11" s="100"/>
-      <c r="Q11" s="100"/>
+      <c r="P11" s="132"/>
+      <c r="Q11" s="132"/>
     </row>
     <row r="12" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="81" t="s">
@@ -13381,10 +13407,10 @@
         <f>M5-I6</f>
         <v>88254.450000000012</v>
       </c>
-      <c r="O6" s="97" t="s">
+      <c r="O6" s="129" t="s">
         <v>89</v>
       </c>
-      <c r="P6" s="97"/>
+      <c r="P6" s="129"/>
       <c r="Q6" s="82">
         <f>(Q4/O4)-1</f>
         <v>-0.14999919494129588</v>
@@ -13470,11 +13496,11 @@
         <f t="shared" ref="M9:M63" si="2">M8-I9</f>
         <v>83689.590000000026</v>
       </c>
-      <c r="O9" s="98" t="s">
+      <c r="O9" s="130" t="s">
         <v>87</v>
       </c>
-      <c r="P9" s="98"/>
-      <c r="Q9" s="98"/>
+      <c r="P9" s="130"/>
+      <c r="Q9" s="130"/>
     </row>
     <row r="10" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="39"/>
@@ -13501,11 +13527,11 @@
         <f t="shared" si="2"/>
         <v>82167.97000000003</v>
       </c>
-      <c r="O10" s="99" t="s">
+      <c r="O10" s="131" t="s">
         <v>88</v>
       </c>
-      <c r="P10" s="99"/>
-      <c r="Q10" s="99"/>
+      <c r="P10" s="131"/>
+      <c r="Q10" s="131"/>
     </row>
     <row r="11" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="39"/>
@@ -13532,11 +13558,11 @@
         <f t="shared" si="2"/>
         <v>80646.350000000035</v>
       </c>
-      <c r="O11" s="100" t="s">
+      <c r="O11" s="132" t="s">
         <v>90</v>
       </c>
-      <c r="P11" s="100"/>
-      <c r="Q11" s="100"/>
+      <c r="P11" s="132"/>
+      <c r="Q11" s="132"/>
     </row>
     <row r="12" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="39"/>
@@ -15198,10 +15224,10 @@
         <f>M5-I6</f>
         <v>-501.4</v>
       </c>
-      <c r="O6" s="97" t="s">
+      <c r="O6" s="129" t="s">
         <v>89</v>
       </c>
-      <c r="P6" s="97"/>
+      <c r="P6" s="129"/>
       <c r="Q6" s="82">
         <f>(Q4/O4)-1</f>
         <v>-0.33618406919008692</v>
@@ -15284,9 +15310,9 @@
         <f t="shared" ref="M9:M36" si="1">M8-I9</f>
         <v>-1265.98</v>
       </c>
-      <c r="O9" s="108"/>
-      <c r="P9" s="108"/>
-      <c r="Q9" s="108"/>
+      <c r="O9" s="134"/>
+      <c r="P9" s="134"/>
+      <c r="Q9" s="134"/>
     </row>
     <row r="10" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="39"/>
@@ -15311,9 +15337,9 @@
         <f t="shared" si="1"/>
         <v>-1516.68</v>
       </c>
-      <c r="O10" s="108"/>
-      <c r="P10" s="108"/>
-      <c r="Q10" s="108"/>
+      <c r="O10" s="134"/>
+      <c r="P10" s="134"/>
+      <c r="Q10" s="134"/>
     </row>
     <row r="11" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="39"/>
@@ -15338,9 +15364,9 @@
         <f t="shared" si="1"/>
         <v>-1767.38</v>
       </c>
-      <c r="O11" s="108"/>
-      <c r="P11" s="108"/>
-      <c r="Q11" s="108"/>
+      <c r="O11" s="134"/>
+      <c r="P11" s="134"/>
+      <c r="Q11" s="134"/>
     </row>
     <row r="12" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="39"/>
@@ -16237,30 +16263,30 @@
   <sheetData>
     <row r="1" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:26" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="136" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="111"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="111"/>
-      <c r="F2" s="111"/>
-      <c r="G2" s="111"/>
-      <c r="H2" s="111"/>
-      <c r="I2" s="111"/>
-      <c r="J2" s="111"/>
-      <c r="K2" s="111"/>
-      <c r="L2" s="111"/>
-      <c r="M2" s="111"/>
-      <c r="N2" s="111"/>
-      <c r="O2" s="111"/>
-      <c r="P2" s="111"/>
-      <c r="Q2" s="111"/>
-      <c r="R2" s="111"/>
-      <c r="S2" s="111"/>
-      <c r="T2" s="111"/>
-      <c r="U2" s="111"/>
-      <c r="V2" s="111"/>
-      <c r="W2" s="112"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="137"/>
+      <c r="F2" s="137"/>
+      <c r="G2" s="137"/>
+      <c r="H2" s="137"/>
+      <c r="I2" s="137"/>
+      <c r="J2" s="137"/>
+      <c r="K2" s="137"/>
+      <c r="L2" s="137"/>
+      <c r="M2" s="137"/>
+      <c r="N2" s="137"/>
+      <c r="O2" s="137"/>
+      <c r="P2" s="137"/>
+      <c r="Q2" s="137"/>
+      <c r="R2" s="137"/>
+      <c r="S2" s="137"/>
+      <c r="T2" s="137"/>
+      <c r="U2" s="137"/>
+      <c r="V2" s="137"/>
+      <c r="W2" s="138"/>
     </row>
     <row r="3" spans="2:26" s="4" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="48" t="s">
@@ -17091,8 +17117,8 @@
       <c r="Z22" s="57"/>
     </row>
     <row r="24" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="P24" s="109"/>
-      <c r="Q24" s="109"/>
+      <c r="P24" s="135"/>
+      <c r="Q24" s="135"/>
       <c r="R24" s="73"/>
       <c r="S24" s="73"/>
       <c r="T24" s="73"/>
@@ -17101,8 +17127,8 @@
       <c r="W24" s="74"/>
     </row>
     <row r="25" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="P25" s="109"/>
-      <c r="Q25" s="109"/>
+      <c r="P25" s="135"/>
+      <c r="Q25" s="135"/>
       <c r="R25" s="73"/>
       <c r="S25" s="73"/>
       <c r="T25" s="73"/>
@@ -17111,8 +17137,8 @@
       <c r="W25" s="74"/>
     </row>
     <row r="26" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="P26" s="109"/>
-      <c r="Q26" s="109"/>
+      <c r="P26" s="135"/>
+      <c r="Q26" s="135"/>
       <c r="R26" s="73"/>
       <c r="S26" s="73"/>
       <c r="T26" s="73"/>
@@ -17121,8 +17147,8 @@
       <c r="W26" s="74"/>
     </row>
     <row r="27" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="P27" s="109"/>
-      <c r="Q27" s="109"/>
+      <c r="P27" s="135"/>
+      <c r="Q27" s="135"/>
       <c r="R27" s="73"/>
       <c r="S27" s="73"/>
       <c r="T27" s="73"/>
@@ -17131,8 +17157,8 @@
       <c r="W27" s="75"/>
     </row>
     <row r="28" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="P28" s="109"/>
-      <c r="Q28" s="109"/>
+      <c r="P28" s="135"/>
+      <c r="Q28" s="135"/>
       <c r="R28" s="73"/>
       <c r="S28" s="73"/>
       <c r="T28" s="73"/>
@@ -17158,14 +17184,14 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{420301BD-1EC9-404C-9D58-1869DDAA2327}">
-  <dimension ref="B2:P9"/>
+  <dimension ref="B2:Q9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="16" width="13.33203125" customWidth="1"/>
+    <col min="3" max="17" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:17" x14ac:dyDescent="0.3">
       <c r="C2" s="85">
         <v>45839</v>
       </c>
@@ -17208,8 +17234,11 @@
       <c r="P2" s="85">
         <v>46235</v>
       </c>
-    </row>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="Q2" s="85">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="3" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B3" s="84" t="s">
         <v>95</v>
       </c>
@@ -17259,8 +17288,11 @@
       <c r="P3" s="27">
         <v>3196894.17</v>
       </c>
-    </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="Q3" s="27">
+        <v>3796974.4</v>
+      </c>
+    </row>
+    <row r="4" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B4" s="84" t="s">
         <v>96</v>
       </c>
@@ -17306,8 +17338,11 @@
       <c r="P4" s="27">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="Q4" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B5" s="84" t="s">
         <v>76</v>
       </c>
@@ -17352,8 +17387,12 @@
       <c r="P5" s="27">
         <v>53315.91</v>
       </c>
-    </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="Q5" s="27">
+        <f>16179.2</f>
+        <v>16179.2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B6" s="84" t="s">
         <v>77</v>
       </c>
@@ -17400,8 +17439,12 @@
       <c r="P6" s="27">
         <v>245472</v>
       </c>
-    </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="Q6" s="27">
+        <f>74452.63</f>
+        <v>74452.63</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" s="84" t="s">
         <v>99</v>
       </c>
@@ -17435,8 +17478,9 @@
       <c r="N7" s="27"/>
       <c r="O7" s="27"/>
       <c r="P7" s="27"/>
-    </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="Q7" s="27"/>
+    </row>
+    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" s="84" t="s">
         <v>8</v>
       </c>
@@ -17469,8 +17513,9 @@
       <c r="N8" s="27"/>
       <c r="O8" s="27"/>
       <c r="P8" s="27"/>
-    </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="Q8" s="27"/>
+    </row>
+    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B9" s="84" t="s">
         <v>101</v>
       </c>
@@ -17527,8 +17572,12 @@
         <v>99156.49</v>
       </c>
       <c r="P9" s="96">
-        <f t="shared" ref="P9" si="2">SUM(P4:P8)</f>
+        <f t="shared" ref="P9:Q9" si="2">SUM(P4:P8)</f>
         <v>298787.91000000003</v>
+      </c>
+      <c r="Q9" s="96">
+        <f t="shared" si="2"/>
+        <v>90631.83</v>
       </c>
     </row>
   </sheetData>

--- a/parcelamentos_local.xlsx
+++ b/parcelamentos_local.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.121.21.252\controladoria\Vitor\TRIBUTARIO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B86B63A-7FD0-4B44-96DC-720567504730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FE07963-056A-44A7-9EF9-B187CA0DB9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="804" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="804" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SALDO CREDOR INSS" sheetId="14" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="PARCELAMENTO 06062025" sheetId="10" r:id="rId5"/>
     <sheet name="PARCELAMENTO 25112025 " sheetId="13" r:id="rId6"/>
     <sheet name="PARCELAMENTO SC" sheetId="12" r:id="rId7"/>
-    <sheet name="IMPOSTOS NÃO PARCELADOS" sheetId="9" r:id="rId8"/>
+    <sheet name="IMPOSTOS NÃO PARCELADOS" sheetId="9" state="hidden" r:id="rId8"/>
     <sheet name="ACOMPANHAMENTO MENSAL" sheetId="11" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -401,9 +401,6 @@
     <t>Saldo Devedor Impostos Parcelados - Atualizado em 06.06.2025</t>
   </si>
   <si>
-    <t>60/7</t>
-  </si>
-  <si>
     <t>IR</t>
   </si>
   <si>
@@ -411,15 +408,6 @@
   </si>
   <si>
     <t>TOTAL MÊS</t>
-  </si>
-  <si>
-    <t>60/25</t>
-  </si>
-  <si>
-    <t>60/20</t>
-  </si>
-  <si>
-    <t>60/9</t>
   </si>
   <si>
     <t>Parcelamento 25/11/2025</t>
@@ -438,6 +426,18 @@
   </si>
   <si>
     <t>SALDO</t>
+  </si>
+  <si>
+    <t>60/26</t>
+  </si>
+  <si>
+    <t>60/21</t>
+  </si>
+  <si>
+    <t>60/10</t>
+  </si>
+  <si>
+    <t>60/8</t>
   </si>
 </sst>
 </file>
@@ -3583,10 +3583,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'ACOMPANHAMENTO MENSAL'!$C$2:$P$2</c:f>
+              <c:f>'ACOMPANHAMENTO MENSAL'!$C$2:$Q$2</c:f>
               <c:numCache>
                 <c:formatCode>mmm\-yy</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>45839</c:v>
                 </c:pt>
@@ -3628,16 +3628,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>46235</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46266</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ACOMPANHAMENTO MENSAL'!$C$9:$P$9</c:f>
+              <c:f>'ACOMPANHAMENTO MENSAL'!$C$9:$Q$9</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>532107.21</c:v>
                 </c:pt>
@@ -3679,6 +3682,9 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>298787.91000000003</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>90631.83</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5003,7 +5009,7 @@
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="97"/>
       <c r="B8" s="122" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C8" s="122"/>
       <c r="D8" s="103"/>
@@ -5021,16 +5027,16 @@
     <row r="10" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A10" s="105"/>
       <c r="B10" s="113" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C10" s="113" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D10" s="113" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E10" s="113" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F10" s="106"/>
     </row>
@@ -5636,14 +5642,14 @@
       </c>
       <c r="C11" s="17">
         <f>'PARCELAMENTO 06062024'!Q4</f>
-        <v>299668.06999999989</v>
+        <v>282040.54999999987</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E11" s="19">
-        <f>60-25</f>
-        <v>35</v>
+        <f>60-26</f>
+        <v>34</v>
       </c>
       <c r="F11" s="26"/>
     </row>
@@ -5656,14 +5662,14 @@
       </c>
       <c r="C12" s="17">
         <f>'PARCELAMENTO 05122024'!Q4</f>
-        <v>740175.44</v>
+        <v>703166.67999999993</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E12" s="19">
-        <f>60-20</f>
-        <v>40</v>
+        <f>60-21</f>
+        <v>39</v>
       </c>
       <c r="F12" s="24"/>
     </row>
@@ -5676,20 +5682,20 @@
       </c>
       <c r="C13" s="17">
         <f>'PARCELAMENTO 06062025'!Q4</f>
-        <v>1369857.65</v>
+        <v>1310298.6299999999</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E13" s="19">
-        <f>60-9</f>
-        <v>51</v>
+        <f>60-10</f>
+        <v>50</v>
       </c>
       <c r="F13" s="24"/>
     </row>
     <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="15" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B14" s="16">
         <v>45986</v>
@@ -5698,11 +5704,11 @@
         <v>91297.69</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="E14" s="19">
-        <f>60-7</f>
-        <v>53</v>
+        <f>60-8</f>
+        <v>52</v>
       </c>
       <c r="F14" s="24"/>
     </row>
@@ -5711,7 +5717,7 @@
       <c r="B15" s="20"/>
       <c r="C15" s="89">
         <f>SUM(C11:C14)</f>
-        <v>2500998.8499999996</v>
+        <v>2386803.5499999993</v>
       </c>
       <c r="D15" s="20"/>
       <c r="E15" s="20"/>
@@ -6166,16 +6172,16 @@
         <v>528825.82999999996</v>
       </c>
       <c r="P4" s="33">
-        <f>I4+I5+I6+I7+I8+I9+I10+I11+I12+I13+I14+I15+I16+I17+I18+I19+I20+I21+I22+I23+I24+I25+I26+I27+I28+I29</f>
-        <v>229157.76000000007</v>
+        <f>I4+I5+I6+I7+I8+I9+I10+I11+I12+I13+I14+I15+I16+I17+I18+I19+I20+I21+I22+I23+I24+I25+I26+I27+I28+I29+I30+I31</f>
+        <v>246785.28000000009</v>
       </c>
       <c r="Q4" s="34">
         <f>O4-P4</f>
-        <v>299668.06999999989</v>
+        <v>282040.54999999987</v>
       </c>
       <c r="R4" s="34">
-        <f>J5+J6+J7+J8+J9+J10+J11+J12+J13+J14+J15+J16+J17+J18+J19+J20+J21+J22+J23+J24+J25+J26+J27+J28+J29</f>
-        <v>28929.75</v>
+        <f>J5+J6+J7+J8+J9+J10+J11+J12+J13+J14+J15+J16+J17+J18+J19+J20+J21+J22+J23+J24+J25+J26+J27+J28+J29+J30+J31</f>
+        <v>33892.76</v>
       </c>
     </row>
     <row r="5" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
@@ -6265,7 +6271,7 @@
       <c r="P6" s="129"/>
       <c r="Q6" s="82">
         <f>(Q4/O4)-1</f>
-        <v>-0.43333314486548447</v>
+        <v>-0.46666646370129106</v>
       </c>
     </row>
     <row r="7" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
@@ -6641,7 +6647,7 @@
         <v>8813.76</v>
       </c>
       <c r="J15" s="77">
-        <f t="shared" ref="J15:J29" si="3">K15-I15</f>
+        <f t="shared" ref="J15:J31" si="3">K15-I15</f>
         <v>906.93000000000029</v>
       </c>
       <c r="K15" s="28">
@@ -7018,10 +7024,12 @@
       <c r="I30" s="28">
         <v>8813.76</v>
       </c>
-      <c r="J30" s="77"/>
+      <c r="J30" s="77">
+        <f t="shared" si="3"/>
+        <v>2433.4699999999993</v>
+      </c>
       <c r="K30" s="28">
-        <f t="shared" si="1"/>
-        <v>8813.76</v>
+        <v>11247.23</v>
       </c>
       <c r="L30" s="29">
         <v>46265</v>
@@ -7041,10 +7049,12 @@
       <c r="I31" s="28">
         <v>8813.76</v>
       </c>
-      <c r="J31" s="77"/>
+      <c r="J31" s="77">
+        <f t="shared" si="3"/>
+        <v>2529.5399999999991</v>
+      </c>
       <c r="K31" s="28">
-        <f t="shared" si="1"/>
-        <v>8813.76</v>
+        <v>11343.3</v>
       </c>
       <c r="L31" s="29">
         <v>46295</v>
@@ -7803,11 +7813,11 @@
       </c>
       <c r="J64" s="87">
         <f>SUM(J4:J63)</f>
-        <v>28929.75</v>
+        <v>33892.76</v>
       </c>
       <c r="K64" s="87">
         <f>SUM(K4:K63)</f>
-        <v>557755.58000000019</v>
+        <v>562718.5900000002</v>
       </c>
       <c r="L64" s="43"/>
       <c r="M64" s="44"/>
@@ -8202,16 +8212,16 @@
         <v>1110263.04</v>
       </c>
       <c r="P4" s="33">
-        <f>I4+I5+I6+I7+I8+I9+I10+I11+I12+I13+I14+I15+I16+I17+I18+I19+I20+I21+I22+I23</f>
-        <v>370087.60000000003</v>
+        <f>I4+I5+I6+I7+I8+I9+I10+I11+I12+I13+I14+I15+I16+I17+I18+I19+I20+I21+I22+I23+I24+I25</f>
+        <v>407096.36000000004</v>
       </c>
       <c r="Q4" s="34">
         <f>O4-P4</f>
-        <v>740175.44</v>
+        <v>703166.67999999993</v>
       </c>
       <c r="R4" s="34">
-        <f>J5+J6+J7+J8+J9+J10+J11+J12+J13+J14+J15+J16+J17+J18+J19+J20+J21+J22+J23+J24+J25+J26+J27+J28+J29</f>
-        <v>38411.279999999984</v>
+        <f>J5+J6+J7+J8+J9+J10+J11+J12+J13+J14+J15+J16+J17+J18+J19+J20+J21+J22+J23+J24+J25</f>
+        <v>46880.719999999979</v>
       </c>
     </row>
     <row r="5" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
@@ -8301,7 +8311,7 @@
       <c r="P6" s="129"/>
       <c r="Q6" s="82">
         <f>Q4/O4-1</f>
-        <v>-0.3333332612783364</v>
+        <v>-0.36666658740617009</v>
       </c>
     </row>
     <row r="7" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
@@ -8414,7 +8424,7 @@
         <v>18504.38</v>
       </c>
       <c r="J9" s="28">
-        <f t="shared" ref="J9:J23" si="3">K9-I9</f>
+        <f t="shared" ref="J9:J25" si="3">K9-I9</f>
         <v>928.90999999999985</v>
       </c>
       <c r="K9" s="28">
@@ -9054,8 +9064,13 @@
       <c r="I24" s="28">
         <v>18504.38</v>
       </c>
-      <c r="J24" s="28"/>
-      <c r="K24" s="28"/>
+      <c r="J24" s="28">
+        <f t="shared" si="3"/>
+        <v>4133.869999999999</v>
+      </c>
+      <c r="K24" s="28">
+        <v>22638.25</v>
+      </c>
       <c r="L24" s="29">
         <v>46265</v>
       </c>
@@ -9091,8 +9106,13 @@
       <c r="I25" s="28">
         <v>18504.38</v>
       </c>
-      <c r="J25" s="28"/>
-      <c r="K25" s="28"/>
+      <c r="J25" s="28">
+        <f t="shared" si="3"/>
+        <v>4335.57</v>
+      </c>
+      <c r="K25" s="28">
+        <v>22839.95</v>
+      </c>
       <c r="L25" s="29">
         <v>46295</v>
       </c>
@@ -10388,11 +10408,11 @@
       </c>
       <c r="J64" s="78">
         <f>SUM(J4:J63)</f>
-        <v>38411.279999999984</v>
+        <v>46880.719999999979</v>
       </c>
       <c r="K64" s="78">
         <f>SUM(K4:K63)</f>
-        <v>389994.5</v>
+        <v>435472.7</v>
       </c>
       <c r="L64" s="43"/>
       <c r="M64" s="44"/>
@@ -11312,16 +11332,16 @@
         <v>1786770.79</v>
       </c>
       <c r="P4" s="33">
-        <f>I4+I5+I6+I7+I8+I9+I10+I11+I12+I13+I14+I15+I16+I17</f>
-        <v>416913.14000000007</v>
+        <f>I4+I5+I6+I7+I8+I9+I10+I11+I12+I13+I14+I15+I16+I17+I18+I19</f>
+        <v>476472.16000000009</v>
       </c>
       <c r="Q4" s="34">
         <f>O4-P4</f>
-        <v>1369857.65</v>
+        <v>1310298.6299999999</v>
       </c>
       <c r="R4" s="34">
-        <f>J5+J6+J7+J8+J9+J10+J11+J12+J13+J14+J15+J16+J17+J18+J19+J20+J21+J22+J23+J24+J25+J26+J27+J28+J29</f>
-        <v>31664.490000000016</v>
+        <f>J5+J6+J7+J8+J9+J10+J11+J12+J13+J14+J15+J16+J17+J18+J19</f>
+        <v>41566.170000000027</v>
       </c>
     </row>
     <row r="5" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
@@ -11351,7 +11371,7 @@
         <v>29779.51</v>
       </c>
       <c r="J5" s="77">
-        <f t="shared" ref="J5:J17" si="1">K5-I5</f>
+        <f t="shared" ref="J5:J19" si="1">K5-I5</f>
         <v>297.79000000000087</v>
       </c>
       <c r="K5" s="28">
@@ -11411,7 +11431,7 @@
       <c r="P6" s="129"/>
       <c r="Q6" s="82">
         <f>(Q4/O4)-1</f>
-        <v>-0.23333330852134659</v>
+        <v>-0.26666663831011039</v>
       </c>
     </row>
     <row r="7" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
@@ -11880,10 +11900,12 @@
       <c r="I18" s="28">
         <v>29779.51</v>
       </c>
-      <c r="J18" s="77"/>
+      <c r="J18" s="77">
+        <f t="shared" si="1"/>
+        <v>4788.5400000000045</v>
+      </c>
       <c r="K18" s="28">
-        <f t="shared" ref="K18:K63" si="3">I18+J18</f>
-        <v>29779.51</v>
+        <v>34568.050000000003</v>
       </c>
       <c r="L18" s="29">
         <v>45900</v>
@@ -11903,10 +11925,12 @@
       <c r="I19" s="28">
         <v>29779.51</v>
       </c>
-      <c r="J19" s="77"/>
+      <c r="J19" s="77">
+        <f t="shared" si="1"/>
+        <v>5113.1400000000031</v>
+      </c>
       <c r="K19" s="28">
-        <f t="shared" si="3"/>
-        <v>29779.51</v>
+        <v>34892.65</v>
       </c>
       <c r="L19" s="29">
         <v>45930</v>
@@ -11928,7 +11952,7 @@
       </c>
       <c r="J20" s="77"/>
       <c r="K20" s="28">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="K18:K63" si="3">I20+J20</f>
         <v>29779.51</v>
       </c>
       <c r="L20" s="29">
@@ -12941,11 +12965,11 @@
       </c>
       <c r="J64" s="78">
         <f>SUM(J4:J63)</f>
-        <v>31664.490000000016</v>
+        <v>41566.170000000027</v>
       </c>
       <c r="K64" s="78">
         <f>SUM(K4:K63)</f>
-        <v>1818435.2800000003</v>
+        <v>1828336.9600000002</v>
       </c>
       <c r="L64" s="43"/>
       <c r="M64" s="44"/>
@@ -13352,7 +13376,7 @@
       </c>
       <c r="R4" s="34">
         <f>J5+J6+J7+J8+J9+J10+J11+J12+J13+J14+J15+J16+J17+J18+J19+J20+J21+J22+J23+J24+J25+J26+J27+J28+J29</f>
-        <v>591.41000000000076</v>
+        <v>744.94000000000096</v>
       </c>
     </row>
     <row r="5" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
@@ -13394,7 +13418,7 @@
         <v>1521.62</v>
       </c>
       <c r="J6" s="77">
-        <f t="shared" ref="J6:J12" si="1">K6-I6</f>
+        <f t="shared" ref="J6:J13" si="1">K6-I6</f>
         <v>33.770000000000209</v>
       </c>
       <c r="K6" s="28">
@@ -13601,10 +13625,12 @@
       <c r="I13" s="27">
         <v>1521.62</v>
       </c>
-      <c r="J13" s="77"/>
+      <c r="J13" s="77">
+        <f t="shared" si="1"/>
+        <v>153.5300000000002</v>
+      </c>
       <c r="K13" s="28">
-        <f t="shared" si="0"/>
-        <v>1521.62</v>
+        <v>1675.15</v>
       </c>
       <c r="L13" s="29">
         <v>46262</v>
@@ -15136,7 +15162,7 @@
     </row>
     <row r="4" spans="2:18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="81" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C4" s="45"/>
       <c r="D4" s="46"/>
@@ -15145,32 +15171,34 @@
       <c r="G4" s="27"/>
       <c r="H4" s="93"/>
       <c r="I4" s="27">
-        <f>K4</f>
-        <v>250.7</v>
-      </c>
-      <c r="J4" s="77"/>
+        <v>210.53</v>
+      </c>
+      <c r="J4" s="77">
+        <v>12.67</v>
+      </c>
       <c r="K4" s="28">
-        <v>250.7</v>
+        <f>I4+J4</f>
+        <v>223.2</v>
       </c>
       <c r="L4" s="29">
-        <v>45991</v>
+        <v>45534</v>
       </c>
       <c r="M4" s="31"/>
       <c r="O4" s="32">
-        <f>I37</f>
-        <v>8285.5799999999963</v>
+        <f>I52</f>
+        <v>10105.300000000005</v>
       </c>
       <c r="P4" s="33">
-        <f>K5+K6+K7+K8+K9+K10+K11+K12+K13+K14+K15</f>
-        <v>2785.48</v>
+        <f>K5+K6+K7+K8+K9+K10+K11+K12+K13+K14+K15+K16+K17+K18+K19+K20+K21+K22+K23+K24+K25+K26+K27+K28+K29+K30+K31+K32</f>
+        <v>6249.5999999999967</v>
       </c>
       <c r="Q4" s="34">
         <f>O4-P4</f>
-        <v>5500.0999999999967</v>
+        <v>3855.700000000008</v>
       </c>
       <c r="R4" s="34">
-        <f>J5+J6+J7+J8+J9+J10+J11+J12+J13+J14+J15+J16+J17+J18+J19+J20+J21+J22+J23+J24+J25+J26+J27+J28+J29</f>
-        <v>15.30000000000004</v>
+        <f>J5+J6+J7+J8+J9+J10+J11+J12+J13+J14+J15+J16+J17+J18+J19+J20+J21+J22+J23+J24+J25+J26+J27+J28+J29+J30+J31+J32+J33+J34+J35+J36+J37+J38+J39+J40+J41+J42+J43+J44+J45+J46+J47+J48+J49+J50+J51-354.74</f>
+        <v>1312.349999999999</v>
       </c>
     </row>
     <row r="5" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
@@ -15182,21 +15210,21 @@
       <c r="G5" s="42"/>
       <c r="H5" s="42"/>
       <c r="I5" s="27">
-        <v>250.7</v>
+        <v>210.53</v>
       </c>
       <c r="J5" s="77">
-        <f>K5-I5</f>
-        <v>5.2600000000000193</v>
+        <v>12.67</v>
       </c>
       <c r="K5" s="28">
-        <v>255.96</v>
+        <f t="shared" ref="K5:K51" si="0">I5+J5</f>
+        <v>223.2</v>
       </c>
       <c r="L5" s="29">
-        <v>46022</v>
+        <v>45565</v>
       </c>
       <c r="M5" s="31">
         <f>H17-I4</f>
-        <v>-250.7</v>
+        <v>-210.53</v>
       </c>
     </row>
     <row r="6" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
@@ -15208,21 +15236,21 @@
       <c r="G6" s="42"/>
       <c r="H6" s="42"/>
       <c r="I6" s="27">
-        <v>250.7</v>
+        <v>210.53</v>
       </c>
       <c r="J6" s="77">
-        <f>K6-I6</f>
-        <v>10.04000000000002</v>
+        <v>12.67</v>
       </c>
       <c r="K6" s="28">
-        <v>260.74</v>
+        <f t="shared" si="0"/>
+        <v>223.2</v>
       </c>
       <c r="L6" s="29">
-        <v>46053</v>
+        <v>45595</v>
       </c>
       <c r="M6" s="31">
         <f>M5-I6</f>
-        <v>-501.4</v>
+        <v>-421.06</v>
       </c>
       <c r="O6" s="129" t="s">
         <v>89</v>
@@ -15230,7 +15258,7 @@
       <c r="P6" s="129"/>
       <c r="Q6" s="82">
         <f>(Q4/O4)-1</f>
-        <v>-0.33618406919008692</v>
+        <v>-0.61844774524259494</v>
       </c>
     </row>
     <row r="7" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
@@ -15242,22 +15270,21 @@
       <c r="G7" s="42"/>
       <c r="H7" s="42"/>
       <c r="I7" s="27">
-        <f t="shared" ref="I7:I36" si="0">K7</f>
-        <v>263.18</v>
+        <v>210.53</v>
       </c>
       <c r="J7" s="77">
-        <f>K7-I7</f>
-        <v>0</v>
+        <v>12.67</v>
       </c>
       <c r="K7" s="28">
-        <v>263.18</v>
+        <f t="shared" si="0"/>
+        <v>223.2</v>
       </c>
       <c r="L7" s="29">
-        <v>46081</v>
+        <v>45626</v>
       </c>
       <c r="M7" s="31">
         <f>M6-I7</f>
-        <v>-764.57999999999993</v>
+        <v>-631.59</v>
       </c>
       <c r="O7" s="39"/>
       <c r="P7" s="39"/>
@@ -15272,19 +15299,21 @@
       <c r="G8" s="42"/>
       <c r="H8" s="42"/>
       <c r="I8" s="27">
-        <f t="shared" si="0"/>
-        <v>250.7</v>
-      </c>
-      <c r="J8" s="77"/>
+        <v>210.53</v>
+      </c>
+      <c r="J8" s="77">
+        <v>12.67</v>
+      </c>
       <c r="K8" s="28">
-        <v>250.7</v>
+        <f t="shared" si="0"/>
+        <v>223.2</v>
       </c>
       <c r="L8" s="29">
-        <v>46112</v>
+        <v>45656</v>
       </c>
       <c r="M8" s="31">
         <f>M7-I8</f>
-        <v>-1015.28</v>
+        <v>-842.12</v>
       </c>
     </row>
     <row r="9" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
@@ -15296,19 +15325,21 @@
       <c r="G9" s="42"/>
       <c r="H9" s="42"/>
       <c r="I9" s="27">
-        <f t="shared" si="0"/>
-        <v>250.7</v>
-      </c>
-      <c r="J9" s="77"/>
+        <v>210.53</v>
+      </c>
+      <c r="J9" s="77">
+        <v>12.67</v>
+      </c>
       <c r="K9" s="28">
-        <v>250.7</v>
+        <f t="shared" si="0"/>
+        <v>223.2</v>
       </c>
       <c r="L9" s="29">
-        <v>46142</v>
+        <v>45687</v>
       </c>
       <c r="M9" s="31">
-        <f t="shared" ref="M9:M36" si="1">M8-I9</f>
-        <v>-1265.98</v>
+        <f t="shared" ref="M9:M51" si="1">M8-I9</f>
+        <v>-1052.6500000000001</v>
       </c>
       <c r="O9" s="134"/>
       <c r="P9" s="134"/>
@@ -15323,19 +15354,21 @@
       <c r="G10" s="42"/>
       <c r="H10" s="42"/>
       <c r="I10" s="27">
-        <f t="shared" si="0"/>
-        <v>250.7</v>
-      </c>
-      <c r="J10" s="77"/>
+        <v>210.53</v>
+      </c>
+      <c r="J10" s="77">
+        <v>12.67</v>
+      </c>
       <c r="K10" s="28">
-        <v>250.7</v>
+        <f t="shared" si="0"/>
+        <v>223.2</v>
       </c>
       <c r="L10" s="29">
-        <v>46173</v>
+        <v>45716</v>
       </c>
       <c r="M10" s="31">
         <f t="shared" si="1"/>
-        <v>-1516.68</v>
+        <v>-1263.18</v>
       </c>
       <c r="O10" s="134"/>
       <c r="P10" s="134"/>
@@ -15350,19 +15383,21 @@
       <c r="G11" s="42"/>
       <c r="H11" s="42"/>
       <c r="I11" s="27">
-        <f t="shared" si="0"/>
-        <v>250.7</v>
-      </c>
-      <c r="J11" s="77"/>
+        <v>210.53</v>
+      </c>
+      <c r="J11" s="77">
+        <v>12.67</v>
+      </c>
       <c r="K11" s="28">
-        <v>250.7</v>
+        <f t="shared" si="0"/>
+        <v>223.2</v>
       </c>
       <c r="L11" s="29">
-        <v>46203</v>
+        <v>45746</v>
       </c>
       <c r="M11" s="31">
         <f t="shared" si="1"/>
-        <v>-1767.38</v>
+        <v>-1473.71</v>
       </c>
       <c r="O11" s="134"/>
       <c r="P11" s="134"/>
@@ -15377,19 +15412,21 @@
       <c r="G12" s="42"/>
       <c r="H12" s="42"/>
       <c r="I12" s="27">
-        <f t="shared" si="0"/>
-        <v>250.7</v>
-      </c>
-      <c r="J12" s="77"/>
+        <v>210.53</v>
+      </c>
+      <c r="J12" s="77">
+        <v>12.67</v>
+      </c>
       <c r="K12" s="28">
-        <v>250.7</v>
+        <f t="shared" si="0"/>
+        <v>223.2</v>
       </c>
       <c r="L12" s="29">
-        <v>46234</v>
+        <v>45777</v>
       </c>
       <c r="M12" s="31">
         <f t="shared" si="1"/>
-        <v>-2018.0800000000002</v>
+        <v>-1684.24</v>
       </c>
     </row>
     <row r="13" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
@@ -15401,19 +15438,21 @@
       <c r="G13" s="42"/>
       <c r="H13" s="42"/>
       <c r="I13" s="27">
-        <f t="shared" si="0"/>
-        <v>250.7</v>
-      </c>
-      <c r="J13" s="77"/>
+        <v>210.53</v>
+      </c>
+      <c r="J13" s="77">
+        <v>12.67</v>
+      </c>
       <c r="K13" s="28">
-        <v>250.7</v>
+        <f t="shared" si="0"/>
+        <v>223.2</v>
       </c>
       <c r="L13" s="29">
-        <v>46265</v>
+        <v>45807</v>
       </c>
       <c r="M13" s="31">
         <f t="shared" si="1"/>
-        <v>-2268.7800000000002</v>
+        <v>-1894.77</v>
       </c>
     </row>
     <row r="14" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
@@ -15425,19 +15464,21 @@
       <c r="G14" s="42"/>
       <c r="H14" s="42"/>
       <c r="I14" s="27">
-        <f t="shared" si="0"/>
-        <v>250.7</v>
-      </c>
-      <c r="J14" s="77"/>
+        <v>210.53</v>
+      </c>
+      <c r="J14" s="77">
+        <v>12.67</v>
+      </c>
       <c r="K14" s="28">
-        <v>250.7</v>
+        <f t="shared" si="0"/>
+        <v>223.2</v>
       </c>
       <c r="L14" s="29">
-        <v>46295</v>
+        <v>45838</v>
       </c>
       <c r="M14" s="31">
         <f t="shared" si="1"/>
-        <v>-2519.48</v>
+        <v>-2105.3000000000002</v>
       </c>
     </row>
     <row r="15" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
@@ -15449,19 +15490,21 @@
       <c r="G15" s="42"/>
       <c r="H15" s="42"/>
       <c r="I15" s="27">
-        <f t="shared" si="0"/>
-        <v>250.7</v>
-      </c>
-      <c r="J15" s="77"/>
+        <v>210.53</v>
+      </c>
+      <c r="J15" s="77">
+        <v>12.67</v>
+      </c>
       <c r="K15" s="28">
-        <v>250.7</v>
+        <f t="shared" si="0"/>
+        <v>223.2</v>
       </c>
       <c r="L15" s="29">
-        <v>46326</v>
+        <v>45868</v>
       </c>
       <c r="M15" s="31">
         <f t="shared" si="1"/>
-        <v>-2770.18</v>
+        <v>-2315.8300000000004</v>
       </c>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.3">
@@ -15472,19 +15515,21 @@
       <c r="G16" s="42"/>
       <c r="H16" s="42"/>
       <c r="I16" s="27">
-        <f t="shared" si="0"/>
-        <v>250.7</v>
-      </c>
-      <c r="J16" s="77"/>
+        <v>210.53</v>
+      </c>
+      <c r="J16" s="77">
+        <v>12.67</v>
+      </c>
       <c r="K16" s="28">
-        <v>250.7</v>
+        <f t="shared" si="0"/>
+        <v>223.2</v>
       </c>
       <c r="L16" s="29">
-        <v>46356</v>
+        <v>45899</v>
       </c>
       <c r="M16" s="31">
         <f t="shared" si="1"/>
-        <v>-3020.8799999999997</v>
+        <v>-2526.3600000000006</v>
       </c>
     </row>
     <row r="17" spans="3:13" x14ac:dyDescent="0.3">
@@ -15495,19 +15540,21 @@
       <c r="G17" s="42"/>
       <c r="H17" s="92"/>
       <c r="I17" s="27">
-        <f t="shared" si="0"/>
-        <v>250.7</v>
-      </c>
-      <c r="J17" s="77"/>
+        <v>210.53</v>
+      </c>
+      <c r="J17" s="77">
+        <v>12.67</v>
+      </c>
       <c r="K17" s="28">
-        <v>250.7</v>
+        <f t="shared" si="0"/>
+        <v>223.2</v>
       </c>
       <c r="L17" s="29">
-        <v>46387</v>
+        <v>45930</v>
       </c>
       <c r="M17" s="31">
         <f t="shared" si="1"/>
-        <v>-3271.5799999999995</v>
+        <v>-2736.8900000000008</v>
       </c>
     </row>
     <row r="18" spans="3:13" x14ac:dyDescent="0.3">
@@ -15517,20 +15564,22 @@
       <c r="F18" s="42"/>
       <c r="G18" s="42"/>
       <c r="H18" s="42"/>
-      <c r="I18" s="28">
-        <f t="shared" si="0"/>
-        <v>250.7</v>
-      </c>
-      <c r="J18" s="77"/>
+      <c r="I18" s="27">
+        <v>210.53</v>
+      </c>
+      <c r="J18" s="77">
+        <v>12.67</v>
+      </c>
       <c r="K18" s="28">
-        <v>250.7</v>
+        <f t="shared" si="0"/>
+        <v>223.2</v>
       </c>
       <c r="L18" s="29">
-        <v>46418</v>
+        <v>45960</v>
       </c>
       <c r="M18" s="31">
         <f t="shared" si="1"/>
-        <v>-3522.2799999999993</v>
+        <v>-2947.420000000001</v>
       </c>
     </row>
     <row r="19" spans="3:13" x14ac:dyDescent="0.3">
@@ -15540,20 +15589,22 @@
       <c r="F19" s="42"/>
       <c r="G19" s="42"/>
       <c r="H19" s="42"/>
-      <c r="I19" s="28">
-        <f t="shared" si="0"/>
-        <v>250.7</v>
-      </c>
-      <c r="J19" s="77"/>
+      <c r="I19" s="27">
+        <v>210.53</v>
+      </c>
+      <c r="J19" s="77">
+        <v>12.67</v>
+      </c>
       <c r="K19" s="28">
-        <v>250.7</v>
+        <f t="shared" si="0"/>
+        <v>223.2</v>
       </c>
       <c r="L19" s="29">
-        <v>46446</v>
+        <v>45991</v>
       </c>
       <c r="M19" s="31">
         <f t="shared" si="1"/>
-        <v>-3772.9799999999991</v>
+        <v>-3157.9500000000012</v>
       </c>
     </row>
     <row r="20" spans="3:13" x14ac:dyDescent="0.3">
@@ -15563,20 +15614,22 @@
       <c r="F20" s="42"/>
       <c r="G20" s="42"/>
       <c r="H20" s="42"/>
-      <c r="I20" s="28">
-        <f t="shared" si="0"/>
-        <v>250.7</v>
-      </c>
-      <c r="J20" s="77"/>
+      <c r="I20" s="27">
+        <v>210.53</v>
+      </c>
+      <c r="J20" s="77">
+        <v>12.67</v>
+      </c>
       <c r="K20" s="28">
-        <v>250.7</v>
+        <f t="shared" si="0"/>
+        <v>223.2</v>
       </c>
       <c r="L20" s="29">
-        <v>46477</v>
+        <v>46021</v>
       </c>
       <c r="M20" s="31">
         <f t="shared" si="1"/>
-        <v>-4023.6799999999989</v>
+        <v>-3368.4800000000014</v>
       </c>
     </row>
     <row r="21" spans="3:13" x14ac:dyDescent="0.3">
@@ -15586,20 +15639,22 @@
       <c r="F21" s="42"/>
       <c r="G21" s="42"/>
       <c r="H21" s="42"/>
-      <c r="I21" s="28">
-        <f t="shared" si="0"/>
-        <v>250.7</v>
-      </c>
-      <c r="J21" s="77"/>
+      <c r="I21" s="27">
+        <v>210.53</v>
+      </c>
+      <c r="J21" s="77">
+        <v>12.67</v>
+      </c>
       <c r="K21" s="28">
-        <v>250.7</v>
+        <f t="shared" si="0"/>
+        <v>223.2</v>
       </c>
       <c r="L21" s="29">
-        <v>46507</v>
+        <v>46052</v>
       </c>
       <c r="M21" s="31">
         <f t="shared" si="1"/>
-        <v>-4274.3799999999992</v>
+        <v>-3579.0100000000016</v>
       </c>
     </row>
     <row r="22" spans="3:13" x14ac:dyDescent="0.3">
@@ -15609,20 +15664,22 @@
       <c r="F22" s="42"/>
       <c r="G22" s="42"/>
       <c r="H22" s="42"/>
-      <c r="I22" s="28">
-        <f t="shared" si="0"/>
-        <v>250.7</v>
-      </c>
-      <c r="J22" s="77"/>
+      <c r="I22" s="27">
+        <v>210.53</v>
+      </c>
+      <c r="J22" s="77">
+        <v>12.67</v>
+      </c>
       <c r="K22" s="28">
-        <v>250.7</v>
+        <f t="shared" si="0"/>
+        <v>223.2</v>
       </c>
       <c r="L22" s="29">
-        <v>46538</v>
+        <v>46081</v>
       </c>
       <c r="M22" s="31">
         <f t="shared" si="1"/>
-        <v>-4525.079999999999</v>
+        <v>-3789.5400000000018</v>
       </c>
     </row>
     <row r="23" spans="3:13" x14ac:dyDescent="0.3">
@@ -15632,20 +15689,22 @@
       <c r="F23" s="42"/>
       <c r="G23" s="42"/>
       <c r="H23" s="42"/>
-      <c r="I23" s="28">
-        <f t="shared" si="0"/>
-        <v>250.7</v>
-      </c>
-      <c r="J23" s="77"/>
+      <c r="I23" s="27">
+        <v>210.53</v>
+      </c>
+      <c r="J23" s="77">
+        <v>12.67</v>
+      </c>
       <c r="K23" s="28">
-        <v>250.7</v>
+        <f t="shared" si="0"/>
+        <v>223.2</v>
       </c>
       <c r="L23" s="29">
-        <v>46568</v>
+        <v>46111</v>
       </c>
       <c r="M23" s="31">
         <f t="shared" si="1"/>
-        <v>-4775.7799999999988</v>
+        <v>-4000.070000000002</v>
       </c>
     </row>
     <row r="24" spans="3:13" x14ac:dyDescent="0.3">
@@ -15655,20 +15714,22 @@
       <c r="F24" s="42"/>
       <c r="G24" s="42"/>
       <c r="H24" s="42"/>
-      <c r="I24" s="28">
-        <f t="shared" si="0"/>
-        <v>250.7</v>
-      </c>
-      <c r="J24" s="77"/>
+      <c r="I24" s="27">
+        <v>210.53</v>
+      </c>
+      <c r="J24" s="77">
+        <v>12.67</v>
+      </c>
       <c r="K24" s="28">
-        <v>250.7</v>
+        <f t="shared" si="0"/>
+        <v>223.2</v>
       </c>
       <c r="L24" s="29">
-        <v>46599</v>
+        <v>46142</v>
       </c>
       <c r="M24" s="31">
         <f t="shared" si="1"/>
-        <v>-5026.4799999999987</v>
+        <v>-4210.6000000000022</v>
       </c>
     </row>
     <row r="25" spans="3:13" x14ac:dyDescent="0.3">
@@ -15678,20 +15739,22 @@
       <c r="F25" s="42"/>
       <c r="G25" s="42"/>
       <c r="H25" s="42"/>
-      <c r="I25" s="28">
-        <f t="shared" si="0"/>
-        <v>250.7</v>
-      </c>
-      <c r="J25" s="77"/>
+      <c r="I25" s="27">
+        <v>210.53</v>
+      </c>
+      <c r="J25" s="77">
+        <v>12.67</v>
+      </c>
       <c r="K25" s="28">
-        <v>250.7</v>
+        <f t="shared" si="0"/>
+        <v>223.2</v>
       </c>
       <c r="L25" s="29">
-        <v>46630</v>
+        <v>46172</v>
       </c>
       <c r="M25" s="31">
         <f t="shared" si="1"/>
-        <v>-5277.1799999999985</v>
+        <v>-4421.1300000000019</v>
       </c>
     </row>
     <row r="26" spans="3:13" x14ac:dyDescent="0.3">
@@ -15701,20 +15764,22 @@
       <c r="F26" s="42"/>
       <c r="G26" s="42"/>
       <c r="H26" s="42"/>
-      <c r="I26" s="28">
-        <f t="shared" si="0"/>
-        <v>250.7</v>
-      </c>
-      <c r="J26" s="77"/>
+      <c r="I26" s="27">
+        <v>210.53</v>
+      </c>
+      <c r="J26" s="77">
+        <v>12.67</v>
+      </c>
       <c r="K26" s="28">
-        <v>250.7</v>
+        <f t="shared" si="0"/>
+        <v>223.2</v>
       </c>
       <c r="L26" s="29">
-        <v>46660</v>
+        <v>46203</v>
       </c>
       <c r="M26" s="31">
         <f t="shared" si="1"/>
-        <v>-5527.8799999999983</v>
+        <v>-4631.6600000000017</v>
       </c>
     </row>
     <row r="27" spans="3:13" x14ac:dyDescent="0.3">
@@ -15724,20 +15789,22 @@
       <c r="F27" s="42"/>
       <c r="G27" s="42"/>
       <c r="H27" s="42"/>
-      <c r="I27" s="28">
-        <f t="shared" si="0"/>
-        <v>250.7</v>
-      </c>
-      <c r="J27" s="77"/>
+      <c r="I27" s="27">
+        <v>210.53</v>
+      </c>
+      <c r="J27" s="77">
+        <v>12.67</v>
+      </c>
       <c r="K27" s="28">
-        <v>250.7</v>
+        <f t="shared" si="0"/>
+        <v>223.2</v>
       </c>
       <c r="L27" s="29">
-        <v>46691</v>
+        <v>46233</v>
       </c>
       <c r="M27" s="31">
         <f t="shared" si="1"/>
-        <v>-5778.5799999999981</v>
+        <v>-4842.1900000000014</v>
       </c>
     </row>
     <row r="28" spans="3:13" x14ac:dyDescent="0.3">
@@ -15747,20 +15814,22 @@
       <c r="F28" s="42"/>
       <c r="G28" s="42"/>
       <c r="H28" s="42"/>
-      <c r="I28" s="28">
-        <f t="shared" si="0"/>
-        <v>250.7</v>
-      </c>
-      <c r="J28" s="77"/>
+      <c r="I28" s="27">
+        <v>210.53</v>
+      </c>
+      <c r="J28" s="77">
+        <v>12.67</v>
+      </c>
       <c r="K28" s="28">
-        <v>250.7</v>
+        <f t="shared" si="0"/>
+        <v>223.2</v>
       </c>
       <c r="L28" s="29">
-        <v>46721</v>
+        <v>46264</v>
       </c>
       <c r="M28" s="31">
         <f t="shared" si="1"/>
-        <v>-6029.2799999999979</v>
+        <v>-5052.7200000000012</v>
       </c>
     </row>
     <row r="29" spans="3:13" x14ac:dyDescent="0.3">
@@ -15770,20 +15839,22 @@
       <c r="F29" s="42"/>
       <c r="G29" s="42"/>
       <c r="H29" s="42"/>
-      <c r="I29" s="28">
-        <f t="shared" si="0"/>
-        <v>250.7</v>
-      </c>
-      <c r="J29" s="77"/>
+      <c r="I29" s="27">
+        <v>210.53</v>
+      </c>
+      <c r="J29" s="77">
+        <v>12.67</v>
+      </c>
       <c r="K29" s="28">
-        <v>250.7</v>
+        <f t="shared" si="0"/>
+        <v>223.2</v>
       </c>
       <c r="L29" s="29">
-        <v>46752</v>
+        <v>46295</v>
       </c>
       <c r="M29" s="31">
         <f t="shared" si="1"/>
-        <v>-6279.9799999999977</v>
+        <v>-5263.2500000000009</v>
       </c>
     </row>
     <row r="30" spans="3:13" x14ac:dyDescent="0.3">
@@ -15793,20 +15864,22 @@
       <c r="F30" s="42"/>
       <c r="G30" s="42"/>
       <c r="H30" s="42"/>
-      <c r="I30" s="28">
-        <f t="shared" si="0"/>
-        <v>250.7</v>
-      </c>
-      <c r="J30" s="77"/>
+      <c r="I30" s="27">
+        <v>210.53</v>
+      </c>
+      <c r="J30" s="77">
+        <v>12.67</v>
+      </c>
       <c r="K30" s="28">
-        <v>250.7</v>
+        <f t="shared" si="0"/>
+        <v>223.2</v>
       </c>
       <c r="L30" s="29">
-        <v>46783</v>
+        <v>46325</v>
       </c>
       <c r="M30" s="31">
         <f t="shared" si="1"/>
-        <v>-6530.6799999999976</v>
+        <v>-5473.7800000000007</v>
       </c>
     </row>
     <row r="31" spans="3:13" x14ac:dyDescent="0.3">
@@ -15816,20 +15889,22 @@
       <c r="F31" s="42"/>
       <c r="G31" s="42"/>
       <c r="H31" s="42"/>
-      <c r="I31" s="28">
-        <f t="shared" si="0"/>
-        <v>250.7</v>
-      </c>
-      <c r="J31" s="77"/>
+      <c r="I31" s="27">
+        <v>210.53</v>
+      </c>
+      <c r="J31" s="77">
+        <v>12.67</v>
+      </c>
       <c r="K31" s="28">
-        <v>250.7</v>
+        <f t="shared" si="0"/>
+        <v>223.2</v>
       </c>
       <c r="L31" s="29">
-        <v>46812</v>
+        <v>46356</v>
       </c>
       <c r="M31" s="31">
         <f t="shared" si="1"/>
-        <v>-6781.3799999999974</v>
+        <v>-5684.31</v>
       </c>
     </row>
     <row r="32" spans="3:13" x14ac:dyDescent="0.3">
@@ -15839,20 +15914,22 @@
       <c r="F32" s="42"/>
       <c r="G32" s="42"/>
       <c r="H32" s="42"/>
-      <c r="I32" s="28">
-        <f t="shared" si="0"/>
-        <v>250.7</v>
-      </c>
-      <c r="J32" s="77"/>
+      <c r="I32" s="27">
+        <v>210.53</v>
+      </c>
+      <c r="J32" s="77">
+        <v>12.67</v>
+      </c>
       <c r="K32" s="28">
-        <v>250.7</v>
+        <f t="shared" si="0"/>
+        <v>223.2</v>
       </c>
       <c r="L32" s="29">
-        <v>46843</v>
+        <v>46386</v>
       </c>
       <c r="M32" s="31">
         <f t="shared" si="1"/>
-        <v>-7032.0799999999972</v>
+        <v>-5894.84</v>
       </c>
     </row>
     <row r="33" spans="3:13" x14ac:dyDescent="0.3">
@@ -15862,20 +15939,22 @@
       <c r="F33" s="42"/>
       <c r="G33" s="42"/>
       <c r="H33" s="42"/>
-      <c r="I33" s="28">
-        <f t="shared" si="0"/>
-        <v>250.7</v>
-      </c>
-      <c r="J33" s="77"/>
+      <c r="I33" s="27">
+        <v>210.53</v>
+      </c>
+      <c r="J33" s="77">
+        <v>69.069999999999993</v>
+      </c>
       <c r="K33" s="28">
-        <v>250.7</v>
+        <f t="shared" si="0"/>
+        <v>279.60000000000002</v>
       </c>
       <c r="L33" s="29">
-        <v>46873</v>
+        <v>46417</v>
       </c>
       <c r="M33" s="31">
         <f t="shared" si="1"/>
-        <v>-7282.779999999997</v>
+        <v>-6105.37</v>
       </c>
     </row>
     <row r="34" spans="3:13" x14ac:dyDescent="0.3">
@@ -15885,20 +15964,22 @@
       <c r="F34" s="42"/>
       <c r="G34" s="42"/>
       <c r="H34" s="42"/>
-      <c r="I34" s="28">
-        <f t="shared" si="0"/>
-        <v>250.7</v>
-      </c>
-      <c r="J34" s="77"/>
+      <c r="I34" s="27">
+        <v>210.53</v>
+      </c>
+      <c r="J34" s="77">
+        <v>69.069999999999993</v>
+      </c>
       <c r="K34" s="28">
-        <v>250.7</v>
+        <f t="shared" si="0"/>
+        <v>279.60000000000002</v>
       </c>
       <c r="L34" s="29">
-        <v>46904</v>
+        <v>46446</v>
       </c>
       <c r="M34" s="31">
         <f t="shared" si="1"/>
-        <v>-7533.4799999999968</v>
+        <v>-6315.9</v>
       </c>
     </row>
     <row r="35" spans="3:13" x14ac:dyDescent="0.3">
@@ -15908,20 +15989,22 @@
       <c r="F35" s="42"/>
       <c r="G35" s="42"/>
       <c r="H35" s="42"/>
-      <c r="I35" s="28">
-        <f t="shared" si="0"/>
-        <v>250.7</v>
-      </c>
-      <c r="J35" s="77"/>
+      <c r="I35" s="27">
+        <v>210.53</v>
+      </c>
+      <c r="J35" s="77">
+        <v>69.069999999999993</v>
+      </c>
       <c r="K35" s="28">
-        <v>250.7</v>
+        <f t="shared" si="0"/>
+        <v>279.60000000000002</v>
       </c>
       <c r="L35" s="29">
-        <v>46934</v>
+        <v>46476</v>
       </c>
       <c r="M35" s="31">
         <f t="shared" si="1"/>
-        <v>-7784.1799999999967</v>
+        <v>-6526.4299999999994</v>
       </c>
     </row>
     <row r="36" spans="3:13" x14ac:dyDescent="0.3">
@@ -15931,20 +16014,22 @@
       <c r="F36" s="42"/>
       <c r="G36" s="42"/>
       <c r="H36" s="42"/>
-      <c r="I36" s="28">
-        <f t="shared" si="0"/>
-        <v>250.7</v>
-      </c>
-      <c r="J36" s="77"/>
+      <c r="I36" s="27">
+        <v>210.53</v>
+      </c>
+      <c r="J36" s="77">
+        <v>69.069999999999993</v>
+      </c>
       <c r="K36" s="28">
-        <v>250.7</v>
+        <f t="shared" si="0"/>
+        <v>279.60000000000002</v>
       </c>
       <c r="L36" s="29">
-        <v>46965</v>
+        <v>46507</v>
       </c>
       <c r="M36" s="31">
         <f t="shared" si="1"/>
-        <v>-8034.8799999999965</v>
+        <v>-6736.9599999999991</v>
       </c>
     </row>
     <row r="37" spans="3:13" x14ac:dyDescent="0.3">
@@ -15954,14 +16039,23 @@
       <c r="F37" s="42"/>
       <c r="G37" s="42"/>
       <c r="H37" s="42"/>
-      <c r="I37" s="42">
-        <f>SUM(I4:I36)</f>
-        <v>8285.5799999999963</v>
-      </c>
-      <c r="J37" s="42"/>
-      <c r="K37" s="42"/>
-      <c r="L37" s="43"/>
-      <c r="M37" s="44"/>
+      <c r="I37" s="27">
+        <v>210.53</v>
+      </c>
+      <c r="J37" s="77">
+        <v>69.069999999999993</v>
+      </c>
+      <c r="K37" s="28">
+        <f t="shared" si="0"/>
+        <v>279.60000000000002</v>
+      </c>
+      <c r="L37" s="29">
+        <v>46537</v>
+      </c>
+      <c r="M37" s="31">
+        <f t="shared" si="1"/>
+        <v>-6947.4899999999989</v>
+      </c>
     </row>
     <row r="38" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C38" s="40"/>
@@ -15970,11 +16064,23 @@
       <c r="F38" s="42"/>
       <c r="G38" s="42"/>
       <c r="H38" s="42"/>
-      <c r="I38" s="42"/>
-      <c r="J38" s="42"/>
-      <c r="K38" s="42"/>
-      <c r="L38" s="43"/>
-      <c r="M38" s="44"/>
+      <c r="I38" s="27">
+        <v>210.53</v>
+      </c>
+      <c r="J38" s="77">
+        <v>69.069999999999993</v>
+      </c>
+      <c r="K38" s="28">
+        <f t="shared" si="0"/>
+        <v>279.60000000000002</v>
+      </c>
+      <c r="L38" s="29">
+        <v>46568</v>
+      </c>
+      <c r="M38" s="31">
+        <f t="shared" si="1"/>
+        <v>-7158.0199999999986</v>
+      </c>
     </row>
     <row r="39" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C39" s="40"/>
@@ -15983,11 +16089,23 @@
       <c r="F39" s="42"/>
       <c r="G39" s="42"/>
       <c r="H39" s="42"/>
-      <c r="I39" s="42"/>
-      <c r="J39" s="42"/>
-      <c r="K39" s="42"/>
-      <c r="L39" s="43"/>
-      <c r="M39" s="44"/>
+      <c r="I39" s="27">
+        <v>210.53</v>
+      </c>
+      <c r="J39" s="77">
+        <v>69.069999999999993</v>
+      </c>
+      <c r="K39" s="28">
+        <f t="shared" si="0"/>
+        <v>279.60000000000002</v>
+      </c>
+      <c r="L39" s="29">
+        <v>46598</v>
+      </c>
+      <c r="M39" s="31">
+        <f t="shared" si="1"/>
+        <v>-7368.5499999999984</v>
+      </c>
     </row>
     <row r="40" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C40" s="40"/>
@@ -15996,11 +16114,23 @@
       <c r="F40" s="42"/>
       <c r="G40" s="42"/>
       <c r="H40" s="42"/>
-      <c r="I40" s="42"/>
-      <c r="J40" s="42"/>
-      <c r="K40" s="42"/>
-      <c r="L40" s="43"/>
-      <c r="M40" s="44"/>
+      <c r="I40" s="27">
+        <v>210.53</v>
+      </c>
+      <c r="J40" s="77">
+        <v>69.069999999999993</v>
+      </c>
+      <c r="K40" s="28">
+        <f t="shared" si="0"/>
+        <v>279.60000000000002</v>
+      </c>
+      <c r="L40" s="29">
+        <v>46629</v>
+      </c>
+      <c r="M40" s="31">
+        <f t="shared" si="1"/>
+        <v>-7579.0799999999981</v>
+      </c>
     </row>
     <row r="41" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C41" s="40"/>
@@ -16009,11 +16139,23 @@
       <c r="F41" s="42"/>
       <c r="G41" s="42"/>
       <c r="H41" s="42"/>
-      <c r="I41" s="42"/>
-      <c r="J41" s="42"/>
-      <c r="K41" s="42"/>
-      <c r="L41" s="43"/>
-      <c r="M41" s="44"/>
+      <c r="I41" s="27">
+        <v>210.53</v>
+      </c>
+      <c r="J41" s="77">
+        <v>69.069999999999993</v>
+      </c>
+      <c r="K41" s="28">
+        <f t="shared" si="0"/>
+        <v>279.60000000000002</v>
+      </c>
+      <c r="L41" s="29">
+        <v>46660</v>
+      </c>
+      <c r="M41" s="31">
+        <f t="shared" si="1"/>
+        <v>-7789.6099999999979</v>
+      </c>
     </row>
     <row r="42" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C42" s="40"/>
@@ -16022,11 +16164,23 @@
       <c r="F42" s="42"/>
       <c r="G42" s="42"/>
       <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
-      <c r="L42" s="43"/>
-      <c r="M42" s="44"/>
+      <c r="I42" s="27">
+        <v>210.53</v>
+      </c>
+      <c r="J42" s="77">
+        <v>69.069999999999993</v>
+      </c>
+      <c r="K42" s="28">
+        <f t="shared" si="0"/>
+        <v>279.60000000000002</v>
+      </c>
+      <c r="L42" s="29">
+        <v>46690</v>
+      </c>
+      <c r="M42" s="31">
+        <f t="shared" si="1"/>
+        <v>-8000.1399999999976</v>
+      </c>
     </row>
     <row r="43" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C43" s="40"/>
@@ -16035,11 +16189,23 @@
       <c r="F43" s="42"/>
       <c r="G43" s="42"/>
       <c r="H43" s="42"/>
-      <c r="I43" s="42"/>
-      <c r="J43" s="42"/>
-      <c r="K43" s="42"/>
-      <c r="L43" s="43"/>
-      <c r="M43" s="44"/>
+      <c r="I43" s="27">
+        <v>210.53</v>
+      </c>
+      <c r="J43" s="77">
+        <v>69.069999999999993</v>
+      </c>
+      <c r="K43" s="28">
+        <f t="shared" si="0"/>
+        <v>279.60000000000002</v>
+      </c>
+      <c r="L43" s="29">
+        <v>46721</v>
+      </c>
+      <c r="M43" s="31">
+        <f t="shared" si="1"/>
+        <v>-8210.6699999999983</v>
+      </c>
     </row>
     <row r="44" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C44" s="40"/>
@@ -16048,11 +16214,23 @@
       <c r="F44" s="42"/>
       <c r="G44" s="42"/>
       <c r="H44" s="42"/>
-      <c r="I44" s="42"/>
-      <c r="J44" s="42"/>
-      <c r="K44" s="42"/>
-      <c r="L44" s="43"/>
-      <c r="M44" s="44"/>
+      <c r="I44" s="27">
+        <v>210.53</v>
+      </c>
+      <c r="J44" s="77">
+        <v>69.069999999999993</v>
+      </c>
+      <c r="K44" s="28">
+        <f t="shared" si="0"/>
+        <v>279.60000000000002</v>
+      </c>
+      <c r="L44" s="29">
+        <v>46751</v>
+      </c>
+      <c r="M44" s="31">
+        <f t="shared" si="1"/>
+        <v>-8421.1999999999989</v>
+      </c>
     </row>
     <row r="45" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C45" s="40"/>
@@ -16061,11 +16239,23 @@
       <c r="F45" s="42"/>
       <c r="G45" s="42"/>
       <c r="H45" s="42"/>
-      <c r="I45" s="42"/>
-      <c r="J45" s="42"/>
-      <c r="K45" s="42"/>
-      <c r="L45" s="43"/>
-      <c r="M45" s="44"/>
+      <c r="I45" s="27">
+        <v>210.53</v>
+      </c>
+      <c r="J45" s="77">
+        <v>69.069999999999993</v>
+      </c>
+      <c r="K45" s="28">
+        <f t="shared" si="0"/>
+        <v>279.60000000000002</v>
+      </c>
+      <c r="L45" s="29">
+        <v>46782</v>
+      </c>
+      <c r="M45" s="31">
+        <f t="shared" si="1"/>
+        <v>-8631.73</v>
+      </c>
     </row>
     <row r="46" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C46" s="40"/>
@@ -16074,11 +16264,23 @@
       <c r="F46" s="42"/>
       <c r="G46" s="42"/>
       <c r="H46" s="42"/>
-      <c r="I46" s="42"/>
-      <c r="J46" s="42"/>
-      <c r="K46" s="42"/>
-      <c r="L46" s="43"/>
-      <c r="M46" s="44"/>
+      <c r="I46" s="27">
+        <v>210.53</v>
+      </c>
+      <c r="J46" s="77">
+        <v>69.069999999999993</v>
+      </c>
+      <c r="K46" s="28">
+        <f t="shared" si="0"/>
+        <v>279.60000000000002</v>
+      </c>
+      <c r="L46" s="29">
+        <v>46812</v>
+      </c>
+      <c r="M46" s="31">
+        <f t="shared" si="1"/>
+        <v>-8842.26</v>
+      </c>
     </row>
     <row r="47" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C47" s="40"/>
@@ -16087,11 +16289,23 @@
       <c r="F47" s="42"/>
       <c r="G47" s="42"/>
       <c r="H47" s="42"/>
-      <c r="I47" s="42"/>
-      <c r="J47" s="42"/>
-      <c r="K47" s="42"/>
-      <c r="L47" s="43"/>
-      <c r="M47" s="44"/>
+      <c r="I47" s="27">
+        <v>210.53</v>
+      </c>
+      <c r="J47" s="77">
+        <v>69.069999999999993</v>
+      </c>
+      <c r="K47" s="28">
+        <f t="shared" si="0"/>
+        <v>279.60000000000002</v>
+      </c>
+      <c r="L47" s="29">
+        <v>46842</v>
+      </c>
+      <c r="M47" s="31">
+        <f t="shared" si="1"/>
+        <v>-9052.7900000000009</v>
+      </c>
     </row>
     <row r="48" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C48" s="40"/>
@@ -16100,11 +16314,23 @@
       <c r="F48" s="42"/>
       <c r="G48" s="42"/>
       <c r="H48" s="42"/>
-      <c r="I48" s="42"/>
-      <c r="J48" s="42"/>
-      <c r="K48" s="42"/>
-      <c r="L48" s="43"/>
-      <c r="M48" s="44"/>
+      <c r="I48" s="27">
+        <v>210.53</v>
+      </c>
+      <c r="J48" s="77">
+        <v>69.069999999999993</v>
+      </c>
+      <c r="K48" s="28">
+        <f t="shared" si="0"/>
+        <v>279.60000000000002</v>
+      </c>
+      <c r="L48" s="29">
+        <v>46873</v>
+      </c>
+      <c r="M48" s="31">
+        <f t="shared" si="1"/>
+        <v>-9263.3200000000015</v>
+      </c>
     </row>
     <row r="49" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C49" s="40"/>
@@ -16113,11 +16339,23 @@
       <c r="F49" s="42"/>
       <c r="G49" s="42"/>
       <c r="H49" s="42"/>
-      <c r="I49" s="42"/>
-      <c r="J49" s="42"/>
-      <c r="K49" s="42"/>
-      <c r="L49" s="43"/>
-      <c r="M49" s="44"/>
+      <c r="I49" s="27">
+        <v>210.53</v>
+      </c>
+      <c r="J49" s="77">
+        <v>69.069999999999993</v>
+      </c>
+      <c r="K49" s="28">
+        <f t="shared" si="0"/>
+        <v>279.60000000000002</v>
+      </c>
+      <c r="L49" s="29">
+        <v>46903</v>
+      </c>
+      <c r="M49" s="31">
+        <f t="shared" si="1"/>
+        <v>-9473.8500000000022</v>
+      </c>
     </row>
     <row r="50" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C50" s="40"/>
@@ -16126,11 +16364,23 @@
       <c r="F50" s="42"/>
       <c r="G50" s="42"/>
       <c r="H50" s="42"/>
-      <c r="I50" s="42"/>
-      <c r="J50" s="42"/>
-      <c r="K50" s="42"/>
-      <c r="L50" s="43"/>
-      <c r="M50" s="44"/>
+      <c r="I50" s="27">
+        <v>210.53</v>
+      </c>
+      <c r="J50" s="77">
+        <v>69.069999999999993</v>
+      </c>
+      <c r="K50" s="28">
+        <f t="shared" si="0"/>
+        <v>279.60000000000002</v>
+      </c>
+      <c r="L50" s="29">
+        <v>46934</v>
+      </c>
+      <c r="M50" s="31">
+        <f t="shared" si="1"/>
+        <v>-9684.3800000000028</v>
+      </c>
     </row>
     <row r="51" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C51" s="40"/>
@@ -16139,11 +16389,23 @@
       <c r="F51" s="42"/>
       <c r="G51" s="42"/>
       <c r="H51" s="42"/>
-      <c r="I51" s="42"/>
-      <c r="J51" s="42"/>
-      <c r="K51" s="42"/>
-      <c r="L51" s="43"/>
-      <c r="M51" s="44"/>
+      <c r="I51" s="27">
+        <v>210.53</v>
+      </c>
+      <c r="J51" s="77">
+        <v>69.069999999999993</v>
+      </c>
+      <c r="K51" s="28">
+        <f t="shared" si="0"/>
+        <v>279.60000000000002</v>
+      </c>
+      <c r="L51" s="29">
+        <v>46964</v>
+      </c>
+      <c r="M51" s="31">
+        <f t="shared" si="1"/>
+        <v>-9894.9100000000035</v>
+      </c>
     </row>
     <row r="52" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C52" s="40"/>
@@ -16152,7 +16414,10 @@
       <c r="F52" s="42"/>
       <c r="G52" s="42"/>
       <c r="H52" s="42"/>
-      <c r="I52" s="42"/>
+      <c r="I52" s="42">
+        <f>SUM(I4:I51)-0.14</f>
+        <v>10105.300000000005</v>
+      </c>
       <c r="J52" s="42"/>
       <c r="K52" s="42"/>
       <c r="L52" s="43"/>
@@ -17446,7 +17711,7 @@
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" s="84" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C7" s="27">
         <v>301206.3</v>
@@ -17517,7 +17782,7 @@
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B9" s="84" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C9" s="96">
         <f>SUM(C4:C8)</f>

--- a/parcelamentos_local.xlsx
+++ b/parcelamentos_local.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.121.21.252\controladoria\Vitor\TRIBUTARIO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FE07963-056A-44A7-9EF9-B187CA0DB9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D5196A9-8D69-4304-AEA4-21FBF8D93D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="804" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="804" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SALDO CREDOR INSS" sheetId="14" r:id="rId1"/>
@@ -105,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="115">
   <si>
     <t>TAURA AGRONEGOCIOS - IMPOSTOS EM ABERTO - NÃO PARCELADOS NA RECEITA FEDERAL</t>
   </si>
@@ -398,9 +398,6 @@
     <t>ISS</t>
   </si>
   <si>
-    <t>Saldo Devedor Impostos Parcelados - Atualizado em 06.06.2025</t>
-  </si>
-  <si>
     <t>IR</t>
   </si>
   <si>
@@ -438,6 +435,21 @@
   </si>
   <si>
     <t>60/8</t>
+  </si>
+  <si>
+    <t>Parcelamento SC 30/08/2025</t>
+  </si>
+  <si>
+    <t>48/29</t>
+  </si>
+  <si>
+    <t>Saldo Devedor Impostos Parcelados - Atualizado em 30.09.2026</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Pendente</t>
   </si>
 </sst>
 </file>
@@ -1000,7 +1012,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1251,9 +1263,6 @@
     <xf numFmtId="43" fontId="21" fillId="8" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1270,6 +1279,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1301,6 +1313,9 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -5008,10 +5023,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="97"/>
-      <c r="B8" s="122" t="s">
-        <v>102</v>
-      </c>
-      <c r="C8" s="122"/>
+      <c r="B8" s="128" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" s="128"/>
       <c r="D8" s="103"/>
       <c r="E8" s="103"/>
       <c r="F8" s="103"/>
@@ -5027,16 +5042,16 @@
     <row r="10" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A10" s="105"/>
       <c r="B10" s="113" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" s="113" t="s">
         <v>103</v>
       </c>
-      <c r="C10" s="113" t="s">
+      <c r="D10" s="113" t="s">
         <v>104</v>
       </c>
-      <c r="D10" s="113" t="s">
+      <c r="E10" s="113" t="s">
         <v>105</v>
-      </c>
-      <c r="E10" s="113" t="s">
-        <v>106</v>
       </c>
       <c r="F10" s="106"/>
     </row>
@@ -5487,15 +5502,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="123" t="s">
+      <c r="A1" s="122" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="124"/>
-      <c r="F1" s="124"/>
-      <c r="G1" s="125"/>
+      <c r="B1" s="123"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="123"/>
+      <c r="F1" s="123"/>
+      <c r="G1" s="124"/>
     </row>
     <row r="2" spans="1:7" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -5596,22 +5611,22 @@
     </row>
     <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="126" t="s">
+      <c r="A8" s="125" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="127"/>
-      <c r="C8" s="128"/>
+      <c r="B8" s="126"/>
+      <c r="C8" s="127"/>
       <c r="D8" s="12"/>
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
       <c r="G8" s="12"/>
     </row>
     <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="126" t="s">
-        <v>97</v>
-      </c>
-      <c r="B9" s="127"/>
-      <c r="C9" s="128"/>
+      <c r="A9" s="125" t="s">
+        <v>112</v>
+      </c>
+      <c r="B9" s="126"/>
+      <c r="C9" s="127"/>
       <c r="D9" s="13"/>
       <c r="E9" s="13"/>
     </row>
@@ -5645,7 +5660,7 @@
         <v>282040.54999999987</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E11" s="19">
         <f>60-26</f>
@@ -5665,7 +5680,7 @@
         <v>703166.67999999993</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E12" s="19">
         <f>60-21</f>
@@ -5685,7 +5700,7 @@
         <v>1310298.6299999999</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E13" s="19">
         <f>60-10</f>
@@ -5695,16 +5710,17 @@
     </row>
     <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B14" s="16">
         <v>45986</v>
       </c>
       <c r="C14" s="17">
+        <f>'PARCELAMENTO 25112025 '!O4</f>
         <v>91297.69</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E14" s="19">
         <f>60-8</f>
@@ -5713,19 +5729,32 @@
       <c r="F14" s="24"/>
     </row>
     <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="21"/>
-      <c r="B15" s="20"/>
-      <c r="C15" s="89">
-        <f>SUM(C11:C14)</f>
-        <v>2386803.5499999993</v>
-      </c>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="B15" s="16">
+        <v>45899</v>
+      </c>
+      <c r="C15" s="17">
+        <f>'PARCELAMENTO SC'!P4</f>
+        <v>10105.300000000005</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="E15" s="19">
+        <f>48-29</f>
+        <v>19</v>
+      </c>
+      <c r="F15" s="24"/>
+    </row>
+    <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="21"/>
       <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
+      <c r="C16" s="89">
+        <f>SUM(C11:C15)</f>
+        <v>2396908.8499999992</v>
+      </c>
       <c r="D16" s="20"/>
       <c r="E16" s="20"/>
     </row>
@@ -11952,7 +11981,7 @@
       </c>
       <c r="J20" s="77"/>
       <c r="K20" s="28">
-        <f t="shared" ref="K18:K63" si="3">I20+J20</f>
+        <f t="shared" ref="K20:K63" si="3">I20+J20</f>
         <v>29779.51</v>
       </c>
       <c r="L20" s="29">
@@ -15084,7 +15113,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00D981B1-E026-41C2-8293-91583FAD4939}">
-  <dimension ref="B1:R58"/>
+  <dimension ref="B1:S58"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.5546875" style="39" customWidth="1"/>
@@ -15100,17 +15129,22 @@
     <col min="11" max="11" width="13.33203125" style="39" customWidth="1"/>
     <col min="12" max="12" width="10.5546875" style="39" customWidth="1"/>
     <col min="13" max="13" width="12.88671875" style="39" customWidth="1"/>
-    <col min="14" max="14" width="4.33203125" style="39" customWidth="1"/>
-    <col min="15" max="15" width="13.109375" style="39" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.5546875" style="39" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.109375" style="39" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.6640625" style="39" customWidth="1"/>
-    <col min="19" max="16384" width="9.109375" style="39"/>
+    <col min="14" max="14" width="12.6640625" style="41" customWidth="1"/>
+    <col min="15" max="15" width="4.33203125" style="39" customWidth="1"/>
+    <col min="16" max="16" width="13.109375" style="39" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.5546875" style="39" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.109375" style="39" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.6640625" style="39" customWidth="1"/>
+    <col min="20" max="16384" width="9.109375" style="39"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="N1" s="4"/>
+    </row>
+    <row r="2" spans="2:19" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N2" s="4"/>
+    </row>
+    <row r="3" spans="2:19" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="37" t="s">
         <v>27</v>
       </c>
@@ -15147,22 +15181,25 @@
       <c r="M3" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="O3" s="36" t="s">
+      <c r="N3" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="P3" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="P3" s="36" t="s">
+      <c r="Q3" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="Q3" s="35" t="s">
+      <c r="R3" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="R3" s="35" t="s">
+      <c r="S3" s="35" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="2:18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:19" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="81" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C4" s="45"/>
       <c r="D4" s="46"/>
@@ -15184,24 +15221,27 @@
         <v>45534</v>
       </c>
       <c r="M4" s="31"/>
-      <c r="O4" s="32">
+      <c r="N4" s="84" t="s">
+        <v>25</v>
+      </c>
+      <c r="P4" s="32">
         <f>I52</f>
         <v>10105.300000000005</v>
       </c>
-      <c r="P4" s="33">
+      <c r="Q4" s="33">
         <f>K5+K6+K7+K8+K9+K10+K11+K12+K13+K14+K15+K16+K17+K18+K19+K20+K21+K22+K23+K24+K25+K26+K27+K28+K29+K30+K31+K32</f>
         <v>6249.5999999999967</v>
       </c>
-      <c r="Q4" s="34">
-        <f>O4-P4</f>
+      <c r="R4" s="34">
+        <f>P4-Q4</f>
         <v>3855.700000000008</v>
       </c>
-      <c r="R4" s="34">
+      <c r="S4" s="34">
         <f>J5+J6+J7+J8+J9+J10+J11+J12+J13+J14+J15+J16+J17+J18+J19+J20+J21+J22+J23+J24+J25+J26+J27+J28+J29+J30+J31+J32+J33+J34+J35+J36+J37+J38+J39+J40+J41+J42+J43+J44+J45+J46+J47+J48+J49+J50+J51-354.74</f>
         <v>1312.349999999999</v>
       </c>
     </row>
-    <row r="5" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="39"/>
       <c r="C5" s="90"/>
       <c r="D5" s="91"/>
@@ -15223,11 +15263,14 @@
         <v>45565</v>
       </c>
       <c r="M5" s="31">
-        <f>H17-I4</f>
-        <v>-210.53</v>
-      </c>
-    </row>
-    <row r="6" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
+        <f>$P$4-I4</f>
+        <v>9894.7700000000041</v>
+      </c>
+      <c r="N5" s="84" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="2:19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B6" s="39"/>
       <c r="C6" s="90"/>
       <c r="D6" s="91"/>
@@ -15250,18 +15293,21 @@
       </c>
       <c r="M6" s="31">
         <f>M5-I6</f>
-        <v>-421.06</v>
-      </c>
-      <c r="O6" s="129" t="s">
+        <v>9684.2400000000034</v>
+      </c>
+      <c r="N6" s="84" t="s">
+        <v>25</v>
+      </c>
+      <c r="P6" s="129" t="s">
         <v>89</v>
       </c>
-      <c r="P6" s="129"/>
-      <c r="Q6" s="82">
-        <f>(Q4/O4)-1</f>
+      <c r="Q6" s="129"/>
+      <c r="R6" s="82">
+        <f>(R4/P4)-1</f>
         <v>-0.61844774524259494</v>
       </c>
     </row>
-    <row r="7" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B7" s="39"/>
       <c r="C7" s="90"/>
       <c r="D7" s="91"/>
@@ -15283,14 +15329,17 @@
         <v>45626</v>
       </c>
       <c r="M7" s="31">
-        <f>M6-I7</f>
-        <v>-631.59</v>
-      </c>
-      <c r="O7" s="39"/>
+        <f t="shared" ref="M7:M51" si="1">M6-I7</f>
+        <v>9473.7100000000028</v>
+      </c>
+      <c r="N7" s="84" t="s">
+        <v>25</v>
+      </c>
       <c r="P7" s="39"/>
       <c r="Q7" s="39"/>
-    </row>
-    <row r="8" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R7" s="39"/>
+    </row>
+    <row r="8" spans="2:19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B8" s="39"/>
       <c r="C8" s="90"/>
       <c r="D8" s="91"/>
@@ -15312,11 +15361,14 @@
         <v>45656</v>
       </c>
       <c r="M8" s="31">
-        <f>M7-I8</f>
-        <v>-842.12</v>
-      </c>
-    </row>
-    <row r="9" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>9263.1800000000021</v>
+      </c>
+      <c r="N8" s="84" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="2:19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B9" s="39"/>
       <c r="C9" s="90"/>
       <c r="D9" s="91"/>
@@ -15338,14 +15390,17 @@
         <v>45687</v>
       </c>
       <c r="M9" s="31">
-        <f t="shared" ref="M9:M51" si="1">M8-I9</f>
-        <v>-1052.6500000000001</v>
-      </c>
-      <c r="O9" s="134"/>
+        <f t="shared" si="1"/>
+        <v>9052.6500000000015</v>
+      </c>
+      <c r="N9" s="84" t="s">
+        <v>25</v>
+      </c>
       <c r="P9" s="134"/>
       <c r="Q9" s="134"/>
-    </row>
-    <row r="10" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R9" s="134"/>
+    </row>
+    <row r="10" spans="2:19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="39"/>
       <c r="C10" s="90"/>
       <c r="D10" s="91"/>
@@ -15368,13 +15423,16 @@
       </c>
       <c r="M10" s="31">
         <f t="shared" si="1"/>
-        <v>-1263.18</v>
-      </c>
-      <c r="O10" s="134"/>
+        <v>8842.1200000000008</v>
+      </c>
+      <c r="N10" s="84" t="s">
+        <v>25</v>
+      </c>
       <c r="P10" s="134"/>
       <c r="Q10" s="134"/>
-    </row>
-    <row r="11" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R10" s="134"/>
+    </row>
+    <row r="11" spans="2:19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="39"/>
       <c r="C11" s="90"/>
       <c r="D11" s="91"/>
@@ -15397,13 +15455,16 @@
       </c>
       <c r="M11" s="31">
         <f t="shared" si="1"/>
-        <v>-1473.71</v>
-      </c>
-      <c r="O11" s="134"/>
+        <v>8631.59</v>
+      </c>
+      <c r="N11" s="84" t="s">
+        <v>25</v>
+      </c>
       <c r="P11" s="134"/>
       <c r="Q11" s="134"/>
-    </row>
-    <row r="12" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R11" s="134"/>
+    </row>
+    <row r="12" spans="2:19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="39"/>
       <c r="C12" s="90"/>
       <c r="D12" s="91"/>
@@ -15426,10 +15487,13 @@
       </c>
       <c r="M12" s="31">
         <f t="shared" si="1"/>
-        <v>-1684.24</v>
-      </c>
-    </row>
-    <row r="13" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
+        <v>8421.06</v>
+      </c>
+      <c r="N12" s="84" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B13" s="39"/>
       <c r="C13" s="90"/>
       <c r="D13" s="91"/>
@@ -15452,10 +15516,13 @@
       </c>
       <c r="M13" s="31">
         <f t="shared" si="1"/>
-        <v>-1894.77</v>
-      </c>
-    </row>
-    <row r="14" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
+        <v>8210.5299999999988</v>
+      </c>
+      <c r="N13" s="84" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="2:19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B14" s="39"/>
       <c r="C14" s="90"/>
       <c r="D14" s="91"/>
@@ -15478,10 +15545,13 @@
       </c>
       <c r="M14" s="31">
         <f t="shared" si="1"/>
-        <v>-2105.3000000000002</v>
-      </c>
-    </row>
-    <row r="15" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
+        <v>7999.9999999999991</v>
+      </c>
+      <c r="N14" s="84" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="2:19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B15" s="39"/>
       <c r="C15" s="90"/>
       <c r="D15" s="91"/>
@@ -15504,10 +15574,13 @@
       </c>
       <c r="M15" s="31">
         <f t="shared" si="1"/>
-        <v>-2315.8300000000004</v>
-      </c>
-    </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.3">
+        <v>7789.4699999999993</v>
+      </c>
+      <c r="N15" s="84" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="2:19" x14ac:dyDescent="0.3">
       <c r="C16" s="90"/>
       <c r="D16" s="91"/>
       <c r="E16" s="42"/>
@@ -15529,10 +15602,13 @@
       </c>
       <c r="M16" s="31">
         <f t="shared" si="1"/>
-        <v>-2526.3600000000006</v>
-      </c>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.3">
+        <v>7578.94</v>
+      </c>
+      <c r="N16" s="84" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C17" s="40"/>
       <c r="D17" s="41"/>
       <c r="E17" s="42"/>
@@ -15554,10 +15630,13 @@
       </c>
       <c r="M17" s="31">
         <f t="shared" si="1"/>
-        <v>-2736.8900000000008</v>
-      </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.3">
+        <v>7368.41</v>
+      </c>
+      <c r="N17" s="84" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C18" s="40"/>
       <c r="D18" s="41"/>
       <c r="E18" s="42"/>
@@ -15579,10 +15658,13 @@
       </c>
       <c r="M18" s="31">
         <f t="shared" si="1"/>
-        <v>-2947.420000000001</v>
-      </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.3">
+        <v>7157.88</v>
+      </c>
+      <c r="N18" s="84" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C19" s="40"/>
       <c r="D19" s="41"/>
       <c r="E19" s="42"/>
@@ -15604,10 +15686,13 @@
       </c>
       <c r="M19" s="31">
         <f t="shared" si="1"/>
-        <v>-3157.9500000000012</v>
-      </c>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.3">
+        <v>6947.35</v>
+      </c>
+      <c r="N19" s="84" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C20" s="40"/>
       <c r="D20" s="41"/>
       <c r="E20" s="42"/>
@@ -15629,10 +15714,13 @@
       </c>
       <c r="M20" s="31">
         <f t="shared" si="1"/>
-        <v>-3368.4800000000014</v>
-      </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.3">
+        <v>6736.8200000000006</v>
+      </c>
+      <c r="N20" s="84" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C21" s="40"/>
       <c r="D21" s="41"/>
       <c r="E21" s="42"/>
@@ -15654,10 +15742,13 @@
       </c>
       <c r="M21" s="31">
         <f t="shared" si="1"/>
-        <v>-3579.0100000000016</v>
-      </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.3">
+        <v>6526.2900000000009</v>
+      </c>
+      <c r="N21" s="84" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C22" s="40"/>
       <c r="D22" s="41"/>
       <c r="E22" s="42"/>
@@ -15679,10 +15770,13 @@
       </c>
       <c r="M22" s="31">
         <f t="shared" si="1"/>
-        <v>-3789.5400000000018</v>
-      </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.3">
+        <v>6315.7600000000011</v>
+      </c>
+      <c r="N22" s="84" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C23" s="40"/>
       <c r="D23" s="41"/>
       <c r="E23" s="42"/>
@@ -15704,10 +15798,13 @@
       </c>
       <c r="M23" s="31">
         <f t="shared" si="1"/>
-        <v>-4000.070000000002</v>
-      </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.3">
+        <v>6105.2300000000014</v>
+      </c>
+      <c r="N23" s="84" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C24" s="40"/>
       <c r="D24" s="41"/>
       <c r="E24" s="42"/>
@@ -15729,10 +15826,13 @@
       </c>
       <c r="M24" s="31">
         <f t="shared" si="1"/>
-        <v>-4210.6000000000022</v>
-      </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.3">
+        <v>5894.7000000000016</v>
+      </c>
+      <c r="N24" s="84" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C25" s="40"/>
       <c r="D25" s="41"/>
       <c r="E25" s="42"/>
@@ -15754,10 +15854,13 @@
       </c>
       <c r="M25" s="31">
         <f t="shared" si="1"/>
-        <v>-4421.1300000000019</v>
-      </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.3">
+        <v>5684.1700000000019</v>
+      </c>
+      <c r="N25" s="84" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C26" s="40"/>
       <c r="D26" s="41"/>
       <c r="E26" s="42"/>
@@ -15779,10 +15882,13 @@
       </c>
       <c r="M26" s="31">
         <f t="shared" si="1"/>
-        <v>-4631.6600000000017</v>
-      </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.3">
+        <v>5473.6400000000021</v>
+      </c>
+      <c r="N26" s="84" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C27" s="40"/>
       <c r="D27" s="41"/>
       <c r="E27" s="42"/>
@@ -15804,10 +15910,13 @@
       </c>
       <c r="M27" s="31">
         <f t="shared" si="1"/>
-        <v>-4842.1900000000014</v>
-      </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.3">
+        <v>5263.1100000000024</v>
+      </c>
+      <c r="N27" s="84" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C28" s="40"/>
       <c r="D28" s="41"/>
       <c r="E28" s="42"/>
@@ -15829,10 +15938,13 @@
       </c>
       <c r="M28" s="31">
         <f t="shared" si="1"/>
-        <v>-5052.7200000000012</v>
-      </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.3">
+        <v>5052.5800000000027</v>
+      </c>
+      <c r="N28" s="84" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C29" s="40"/>
       <c r="D29" s="41"/>
       <c r="E29" s="42"/>
@@ -15854,10 +15966,13 @@
       </c>
       <c r="M29" s="31">
         <f t="shared" si="1"/>
-        <v>-5263.2500000000009</v>
-      </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.3">
+        <v>4842.0500000000029</v>
+      </c>
+      <c r="N29" s="84" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C30" s="40"/>
       <c r="D30" s="41"/>
       <c r="E30" s="42"/>
@@ -15879,10 +15994,13 @@
       </c>
       <c r="M30" s="31">
         <f t="shared" si="1"/>
-        <v>-5473.7800000000007</v>
-      </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.3">
+        <v>4631.5200000000032</v>
+      </c>
+      <c r="N30" s="84" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C31" s="40"/>
       <c r="D31" s="41"/>
       <c r="E31" s="42"/>
@@ -15904,10 +16022,13 @@
       </c>
       <c r="M31" s="31">
         <f t="shared" si="1"/>
-        <v>-5684.31</v>
-      </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.3">
+        <v>4420.9900000000034</v>
+      </c>
+      <c r="N31" s="84" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C32" s="40"/>
       <c r="D32" s="41"/>
       <c r="E32" s="42"/>
@@ -15929,10 +16050,13 @@
       </c>
       <c r="M32" s="31">
         <f t="shared" si="1"/>
-        <v>-5894.84</v>
-      </c>
-    </row>
-    <row r="33" spans="3:13" x14ac:dyDescent="0.3">
+        <v>4210.4600000000037</v>
+      </c>
+      <c r="N32" s="84" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C33" s="40"/>
       <c r="D33" s="41"/>
       <c r="E33" s="42"/>
@@ -15954,10 +16078,13 @@
       </c>
       <c r="M33" s="31">
         <f t="shared" si="1"/>
-        <v>-6105.37</v>
-      </c>
-    </row>
-    <row r="34" spans="3:13" x14ac:dyDescent="0.3">
+        <v>3999.9300000000035</v>
+      </c>
+      <c r="N33" s="139" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="34" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C34" s="40"/>
       <c r="D34" s="41"/>
       <c r="E34" s="42"/>
@@ -15979,10 +16106,13 @@
       </c>
       <c r="M34" s="31">
         <f t="shared" si="1"/>
-        <v>-6315.9</v>
-      </c>
-    </row>
-    <row r="35" spans="3:13" x14ac:dyDescent="0.3">
+        <v>3789.4000000000033</v>
+      </c>
+      <c r="N34" s="139" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="35" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C35" s="40"/>
       <c r="D35" s="41"/>
       <c r="E35" s="42"/>
@@ -16004,10 +16134,13 @@
       </c>
       <c r="M35" s="31">
         <f t="shared" si="1"/>
-        <v>-6526.4299999999994</v>
-      </c>
-    </row>
-    <row r="36" spans="3:13" x14ac:dyDescent="0.3">
+        <v>3578.8700000000031</v>
+      </c>
+      <c r="N35" s="139" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="36" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C36" s="40"/>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
@@ -16029,10 +16162,13 @@
       </c>
       <c r="M36" s="31">
         <f t="shared" si="1"/>
-        <v>-6736.9599999999991</v>
-      </c>
-    </row>
-    <row r="37" spans="3:13" x14ac:dyDescent="0.3">
+        <v>3368.3400000000029</v>
+      </c>
+      <c r="N36" s="139" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="37" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C37" s="40"/>
       <c r="D37" s="41"/>
       <c r="E37" s="42"/>
@@ -16054,10 +16190,13 @@
       </c>
       <c r="M37" s="31">
         <f t="shared" si="1"/>
-        <v>-6947.4899999999989</v>
-      </c>
-    </row>
-    <row r="38" spans="3:13" x14ac:dyDescent="0.3">
+        <v>3157.8100000000027</v>
+      </c>
+      <c r="N37" s="139" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="38" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C38" s="40"/>
       <c r="D38" s="41"/>
       <c r="E38" s="42"/>
@@ -16079,10 +16218,13 @@
       </c>
       <c r="M38" s="31">
         <f t="shared" si="1"/>
-        <v>-7158.0199999999986</v>
-      </c>
-    </row>
-    <row r="39" spans="3:13" x14ac:dyDescent="0.3">
+        <v>2947.2800000000025</v>
+      </c>
+      <c r="N38" s="139" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="39" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C39" s="40"/>
       <c r="D39" s="41"/>
       <c r="E39" s="42"/>
@@ -16104,10 +16246,13 @@
       </c>
       <c r="M39" s="31">
         <f t="shared" si="1"/>
-        <v>-7368.5499999999984</v>
-      </c>
-    </row>
-    <row r="40" spans="3:13" x14ac:dyDescent="0.3">
+        <v>2736.7500000000023</v>
+      </c>
+      <c r="N39" s="139" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="40" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C40" s="40"/>
       <c r="D40" s="41"/>
       <c r="E40" s="42"/>
@@ -16129,10 +16274,13 @@
       </c>
       <c r="M40" s="31">
         <f t="shared" si="1"/>
-        <v>-7579.0799999999981</v>
-      </c>
-    </row>
-    <row r="41" spans="3:13" x14ac:dyDescent="0.3">
+        <v>2526.2200000000021</v>
+      </c>
+      <c r="N40" s="139" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="41" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C41" s="40"/>
       <c r="D41" s="41"/>
       <c r="E41" s="42"/>
@@ -16154,10 +16302,13 @@
       </c>
       <c r="M41" s="31">
         <f t="shared" si="1"/>
-        <v>-7789.6099999999979</v>
-      </c>
-    </row>
-    <row r="42" spans="3:13" x14ac:dyDescent="0.3">
+        <v>2315.6900000000019</v>
+      </c>
+      <c r="N41" s="139" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="42" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C42" s="40"/>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
@@ -16179,10 +16330,13 @@
       </c>
       <c r="M42" s="31">
         <f t="shared" si="1"/>
-        <v>-8000.1399999999976</v>
-      </c>
-    </row>
-    <row r="43" spans="3:13" x14ac:dyDescent="0.3">
+        <v>2105.1600000000017</v>
+      </c>
+      <c r="N42" s="139" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="43" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C43" s="40"/>
       <c r="D43" s="41"/>
       <c r="E43" s="42"/>
@@ -16204,10 +16358,13 @@
       </c>
       <c r="M43" s="31">
         <f t="shared" si="1"/>
-        <v>-8210.6699999999983</v>
-      </c>
-    </row>
-    <row r="44" spans="3:13" x14ac:dyDescent="0.3">
+        <v>1894.6300000000017</v>
+      </c>
+      <c r="N43" s="139" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="44" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C44" s="40"/>
       <c r="D44" s="41"/>
       <c r="E44" s="42"/>
@@ -16229,10 +16386,13 @@
       </c>
       <c r="M44" s="31">
         <f t="shared" si="1"/>
-        <v>-8421.1999999999989</v>
-      </c>
-    </row>
-    <row r="45" spans="3:13" x14ac:dyDescent="0.3">
+        <v>1684.1000000000017</v>
+      </c>
+      <c r="N44" s="139" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="45" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C45" s="40"/>
       <c r="D45" s="41"/>
       <c r="E45" s="42"/>
@@ -16254,10 +16414,13 @@
       </c>
       <c r="M45" s="31">
         <f t="shared" si="1"/>
-        <v>-8631.73</v>
-      </c>
-    </row>
-    <row r="46" spans="3:13" x14ac:dyDescent="0.3">
+        <v>1473.5700000000018</v>
+      </c>
+      <c r="N45" s="139" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="46" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C46" s="40"/>
       <c r="D46" s="41"/>
       <c r="E46" s="42"/>
@@ -16279,10 +16442,13 @@
       </c>
       <c r="M46" s="31">
         <f t="shared" si="1"/>
-        <v>-8842.26</v>
-      </c>
-    </row>
-    <row r="47" spans="3:13" x14ac:dyDescent="0.3">
+        <v>1263.0400000000018</v>
+      </c>
+      <c r="N46" s="139" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="47" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C47" s="40"/>
       <c r="D47" s="41"/>
       <c r="E47" s="42"/>
@@ -16304,10 +16470,13 @@
       </c>
       <c r="M47" s="31">
         <f t="shared" si="1"/>
-        <v>-9052.7900000000009</v>
-      </c>
-    </row>
-    <row r="48" spans="3:13" x14ac:dyDescent="0.3">
+        <v>1052.5100000000018</v>
+      </c>
+      <c r="N47" s="139" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="48" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C48" s="40"/>
       <c r="D48" s="41"/>
       <c r="E48" s="42"/>
@@ -16329,10 +16498,13 @@
       </c>
       <c r="M48" s="31">
         <f t="shared" si="1"/>
-        <v>-9263.3200000000015</v>
-      </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.3">
+        <v>841.98000000000184</v>
+      </c>
+      <c r="N48" s="139" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C49" s="40"/>
       <c r="D49" s="41"/>
       <c r="E49" s="42"/>
@@ -16354,10 +16526,13 @@
       </c>
       <c r="M49" s="31">
         <f t="shared" si="1"/>
-        <v>-9473.8500000000022</v>
-      </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.3">
+        <v>631.45000000000186</v>
+      </c>
+      <c r="N49" s="139" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C50" s="40"/>
       <c r="D50" s="41"/>
       <c r="E50" s="42"/>
@@ -16379,10 +16554,13 @@
       </c>
       <c r="M50" s="31">
         <f t="shared" si="1"/>
-        <v>-9684.3800000000028</v>
-      </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.3">
+        <v>420.92000000000189</v>
+      </c>
+      <c r="N50" s="139" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C51" s="40"/>
       <c r="D51" s="41"/>
       <c r="E51" s="42"/>
@@ -16404,10 +16582,13 @@
       </c>
       <c r="M51" s="31">
         <f t="shared" si="1"/>
-        <v>-9894.9100000000035</v>
-      </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.3">
+        <v>210.39000000000189</v>
+      </c>
+      <c r="N51" s="139" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C52" s="40"/>
       <c r="D52" s="41"/>
       <c r="E52" s="42"/>
@@ -16423,7 +16604,7 @@
       <c r="L52" s="43"/>
       <c r="M52" s="44"/>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C53" s="40"/>
       <c r="D53" s="41"/>
       <c r="E53" s="42"/>
@@ -16436,7 +16617,7 @@
       <c r="L53" s="43"/>
       <c r="M53" s="44"/>
     </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C54" s="40"/>
       <c r="D54" s="41"/>
       <c r="E54" s="42"/>
@@ -16449,7 +16630,7 @@
       <c r="L54" s="43"/>
       <c r="M54" s="44"/>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C55" s="40"/>
       <c r="D55" s="41"/>
       <c r="E55" s="42"/>
@@ -16462,7 +16643,7 @@
       <c r="L55" s="43"/>
       <c r="M55" s="44"/>
     </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C56" s="40"/>
       <c r="D56" s="41"/>
       <c r="E56" s="42"/>
@@ -16475,7 +16656,7 @@
       <c r="L56" s="43"/>
       <c r="M56" s="44"/>
     </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C57" s="40"/>
       <c r="D57" s="41"/>
       <c r="E57" s="42"/>
@@ -16488,16 +16669,16 @@
       <c r="L57" s="43"/>
       <c r="M57" s="44"/>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.3">
       <c r="H58" s="44"/>
       <c r="K58" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="O6:P6"/>
-    <mergeCell ref="O9:Q9"/>
-    <mergeCell ref="O10:Q10"/>
-    <mergeCell ref="O11:Q11"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="P9:R9"/>
+    <mergeCell ref="P10:R10"/>
+    <mergeCell ref="P11:R11"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -17711,7 +17892,7 @@
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" s="84" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C7" s="27">
         <v>301206.3</v>
@@ -17782,7 +17963,7 @@
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B9" s="84" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C9" s="96">
         <f>SUM(C4:C8)</f>

--- a/parcelamentos_local.xlsx
+++ b/parcelamentos_local.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.121.21.252\controladoria\Vitor\TRIBUTARIO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D5196A9-8D69-4304-AEA4-21FBF8D93D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{469E9222-E42F-478F-B55E-489D032C95AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="804" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="804" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SALDO CREDOR INSS" sheetId="14" r:id="rId1"/>
@@ -1263,6 +1263,9 @@
     <xf numFmtId="43" fontId="21" fillId="8" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1313,9 +1316,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -5023,10 +5023,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="97"/>
-      <c r="B8" s="128" t="s">
+      <c r="B8" s="129" t="s">
         <v>101</v>
       </c>
-      <c r="C8" s="128"/>
+      <c r="C8" s="129"/>
       <c r="D8" s="103"/>
       <c r="E8" s="103"/>
       <c r="F8" s="103"/>
@@ -5144,11 +5144,17 @@
       <c r="B16" s="114">
         <v>46266</v>
       </c>
-      <c r="C16" s="119"/>
-      <c r="D16" s="119"/>
+      <c r="C16" s="119">
+        <f>130875.23</f>
+        <v>130875.23</v>
+      </c>
+      <c r="D16" s="119">
+        <f>101785.2</f>
+        <v>101785.2</v>
+      </c>
       <c r="E16" s="117">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>29090.03</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -5194,7 +5200,7 @@
       <c r="D20" s="120"/>
       <c r="E20" s="121">
         <f>SUM(E11:E19)</f>
-        <v>152368.94</v>
+        <v>181458.97</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -5502,15 +5508,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="123" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="123"/>
-      <c r="C1" s="123"/>
-      <c r="D1" s="123"/>
-      <c r="E1" s="123"/>
-      <c r="F1" s="123"/>
-      <c r="G1" s="124"/>
+      <c r="B1" s="124"/>
+      <c r="C1" s="124"/>
+      <c r="D1" s="124"/>
+      <c r="E1" s="124"/>
+      <c r="F1" s="124"/>
+      <c r="G1" s="125"/>
     </row>
     <row r="2" spans="1:7" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -5611,22 +5617,22 @@
     </row>
     <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="125" t="s">
+      <c r="A8" s="126" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="126"/>
-      <c r="C8" s="127"/>
+      <c r="B8" s="127"/>
+      <c r="C8" s="128"/>
       <c r="D8" s="12"/>
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
       <c r="G8" s="12"/>
     </row>
     <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="125" t="s">
+      <c r="A9" s="126" t="s">
         <v>112</v>
       </c>
-      <c r="B9" s="126"/>
-      <c r="C9" s="127"/>
+      <c r="B9" s="127"/>
+      <c r="C9" s="128"/>
       <c r="D9" s="13"/>
       <c r="E9" s="13"/>
     </row>
@@ -5716,8 +5722,8 @@
         <v>45986</v>
       </c>
       <c r="C14" s="17">
-        <f>'PARCELAMENTO 25112025 '!O4</f>
-        <v>91297.69</v>
+        <f>'PARCELAMENTO 25112025 '!Q4</f>
+        <v>77603.11</v>
       </c>
       <c r="D14" s="18" t="s">
         <v>109</v>
@@ -5736,8 +5742,8 @@
         <v>45899</v>
       </c>
       <c r="C15" s="17">
-        <f>'PARCELAMENTO SC'!P4</f>
-        <v>10105.300000000005</v>
+        <f>'PARCELAMENTO SC'!R4</f>
+        <v>3855.700000000008</v>
       </c>
       <c r="D15" s="18" t="s">
         <v>111</v>
@@ -5753,7 +5759,7 @@
       <c r="B16" s="20"/>
       <c r="C16" s="89">
         <f>SUM(C11:C15)</f>
-        <v>2396908.8499999992</v>
+        <v>2376964.6699999995</v>
       </c>
       <c r="D16" s="20"/>
       <c r="E16" s="20"/>
@@ -6294,10 +6300,10 @@
         <f>M5-I6</f>
         <v>511198.30999999994</v>
       </c>
-      <c r="O6" s="129" t="s">
+      <c r="O6" s="130" t="s">
         <v>89</v>
       </c>
-      <c r="P6" s="129"/>
+      <c r="P6" s="130"/>
       <c r="Q6" s="82">
         <f>(Q4/O4)-1</f>
         <v>-0.46666646370129106</v>
@@ -6428,11 +6434,11 @@
         <f>M8-I9</f>
         <v>484757.02999999991</v>
       </c>
-      <c r="O9" s="130" t="s">
+      <c r="O9" s="131" t="s">
         <v>87</v>
       </c>
-      <c r="P9" s="130"/>
-      <c r="Q9" s="130"/>
+      <c r="P9" s="131"/>
+      <c r="Q9" s="131"/>
     </row>
     <row r="10" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="81" t="s">
@@ -6474,11 +6480,11 @@
         <f t="shared" ref="M10:M63" si="2">M9-I10</f>
         <v>475943.2699999999</v>
       </c>
-      <c r="O10" s="131" t="s">
+      <c r="O10" s="132" t="s">
         <v>88</v>
       </c>
-      <c r="P10" s="131"/>
-      <c r="Q10" s="131"/>
+      <c r="P10" s="132"/>
+      <c r="Q10" s="132"/>
     </row>
     <row r="11" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="81" t="s">
@@ -6520,11 +6526,11 @@
         <f t="shared" si="2"/>
         <v>467129.50999999989</v>
       </c>
-      <c r="O11" s="132" t="s">
+      <c r="O11" s="133" t="s">
         <v>90</v>
       </c>
-      <c r="P11" s="132"/>
-      <c r="Q11" s="132"/>
+      <c r="P11" s="133"/>
+      <c r="Q11" s="133"/>
     </row>
     <row r="12" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="83" t="s">
@@ -8334,10 +8340,10 @@
         <f>M5-I6</f>
         <v>1073254.2800000003</v>
       </c>
-      <c r="O6" s="129" t="s">
+      <c r="O6" s="130" t="s">
         <v>89</v>
       </c>
-      <c r="P6" s="129"/>
+      <c r="P6" s="130"/>
       <c r="Q6" s="82">
         <f>Q4/O4-1</f>
         <v>-0.36666658740617009</v>
@@ -8466,11 +8472,11 @@
         <f t="shared" si="2"/>
         <v>1017741.1400000004</v>
       </c>
-      <c r="O9" s="133" t="s">
+      <c r="O9" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="P9" s="133"/>
-      <c r="Q9" s="133"/>
+      <c r="P9" s="134"/>
+      <c r="Q9" s="134"/>
     </row>
     <row r="10" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="79" t="s">
@@ -8512,11 +8518,11 @@
         <f t="shared" si="2"/>
         <v>999236.76000000036</v>
       </c>
-      <c r="O10" s="130" t="s">
+      <c r="O10" s="131" t="s">
         <v>87</v>
       </c>
-      <c r="P10" s="130"/>
-      <c r="Q10" s="130"/>
+      <c r="P10" s="131"/>
+      <c r="Q10" s="131"/>
     </row>
     <row r="11" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="79" t="s">
@@ -8558,11 +8564,11 @@
         <f t="shared" si="2"/>
         <v>980732.38000000035</v>
       </c>
-      <c r="O11" s="131" t="s">
+      <c r="O11" s="132" t="s">
         <v>88</v>
       </c>
-      <c r="P11" s="131"/>
-      <c r="Q11" s="131"/>
+      <c r="P11" s="132"/>
+      <c r="Q11" s="132"/>
     </row>
     <row r="12" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="79" t="s">
@@ -11454,10 +11460,10 @@
         <f>M5-I6</f>
         <v>1727211.77</v>
       </c>
-      <c r="O6" s="129" t="s">
+      <c r="O6" s="130" t="s">
         <v>89</v>
       </c>
-      <c r="P6" s="129"/>
+      <c r="P6" s="130"/>
       <c r="Q6" s="82">
         <f>(Q4/O4)-1</f>
         <v>-0.26666663831011039</v>
@@ -11588,11 +11594,11 @@
         <f t="shared" ref="M9:M63" si="2">M8-I9</f>
         <v>1637873.24</v>
       </c>
-      <c r="O9" s="130" t="s">
+      <c r="O9" s="131" t="s">
         <v>87</v>
       </c>
-      <c r="P9" s="130"/>
-      <c r="Q9" s="130"/>
+      <c r="P9" s="131"/>
+      <c r="Q9" s="131"/>
     </row>
     <row r="10" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="81" t="s">
@@ -11634,11 +11640,11 @@
         <f t="shared" si="2"/>
         <v>1608093.73</v>
       </c>
-      <c r="O10" s="131" t="s">
+      <c r="O10" s="132" t="s">
         <v>88</v>
       </c>
-      <c r="P10" s="131"/>
-      <c r="Q10" s="131"/>
+      <c r="P10" s="132"/>
+      <c r="Q10" s="132"/>
     </row>
     <row r="11" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="81" t="s">
@@ -11680,11 +11686,11 @@
         <f t="shared" si="2"/>
         <v>1578314.22</v>
       </c>
-      <c r="O11" s="132" t="s">
+      <c r="O11" s="133" t="s">
         <v>90</v>
       </c>
-      <c r="P11" s="132"/>
-      <c r="Q11" s="132"/>
+      <c r="P11" s="133"/>
+      <c r="Q11" s="133"/>
     </row>
     <row r="12" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="81" t="s">
@@ -13460,10 +13466,10 @@
         <f>M5-I6</f>
         <v>88254.450000000012</v>
       </c>
-      <c r="O6" s="129" t="s">
+      <c r="O6" s="130" t="s">
         <v>89</v>
       </c>
-      <c r="P6" s="129"/>
+      <c r="P6" s="130"/>
       <c r="Q6" s="82">
         <f>(Q4/O4)-1</f>
         <v>-0.14999919494129588</v>
@@ -13549,11 +13555,11 @@
         <f t="shared" ref="M9:M63" si="2">M8-I9</f>
         <v>83689.590000000026</v>
       </c>
-      <c r="O9" s="130" t="s">
+      <c r="O9" s="131" t="s">
         <v>87</v>
       </c>
-      <c r="P9" s="130"/>
-      <c r="Q9" s="130"/>
+      <c r="P9" s="131"/>
+      <c r="Q9" s="131"/>
     </row>
     <row r="10" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="39"/>
@@ -13580,11 +13586,11 @@
         <f t="shared" si="2"/>
         <v>82167.97000000003</v>
       </c>
-      <c r="O10" s="131" t="s">
+      <c r="O10" s="132" t="s">
         <v>88</v>
       </c>
-      <c r="P10" s="131"/>
-      <c r="Q10" s="131"/>
+      <c r="P10" s="132"/>
+      <c r="Q10" s="132"/>
     </row>
     <row r="11" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="39"/>
@@ -13611,11 +13617,11 @@
         <f t="shared" si="2"/>
         <v>80646.350000000035</v>
       </c>
-      <c r="O11" s="132" t="s">
+      <c r="O11" s="133" t="s">
         <v>90</v>
       </c>
-      <c r="P11" s="132"/>
-      <c r="Q11" s="132"/>
+      <c r="P11" s="133"/>
+      <c r="Q11" s="133"/>
     </row>
     <row r="12" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="39"/>
@@ -15298,10 +15304,10 @@
       <c r="N6" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="P6" s="129" t="s">
+      <c r="P6" s="130" t="s">
         <v>89</v>
       </c>
-      <c r="Q6" s="129"/>
+      <c r="Q6" s="130"/>
       <c r="R6" s="82">
         <f>(R4/P4)-1</f>
         <v>-0.61844774524259494</v>
@@ -15396,9 +15402,9 @@
       <c r="N9" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="P9" s="134"/>
-      <c r="Q9" s="134"/>
-      <c r="R9" s="134"/>
+      <c r="P9" s="135"/>
+      <c r="Q9" s="135"/>
+      <c r="R9" s="135"/>
     </row>
     <row r="10" spans="2:19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="39"/>
@@ -15428,9 +15434,9 @@
       <c r="N10" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="P10" s="134"/>
-      <c r="Q10" s="134"/>
-      <c r="R10" s="134"/>
+      <c r="P10" s="135"/>
+      <c r="Q10" s="135"/>
+      <c r="R10" s="135"/>
     </row>
     <row r="11" spans="2:19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="39"/>
@@ -15460,9 +15466,9 @@
       <c r="N11" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="P11" s="134"/>
-      <c r="Q11" s="134"/>
-      <c r="R11" s="134"/>
+      <c r="P11" s="135"/>
+      <c r="Q11" s="135"/>
+      <c r="R11" s="135"/>
     </row>
     <row r="12" spans="2:19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="39"/>
@@ -16080,7 +16086,7 @@
         <f t="shared" si="1"/>
         <v>3999.9300000000035</v>
       </c>
-      <c r="N33" s="139" t="s">
+      <c r="N33" s="122" t="s">
         <v>114</v>
       </c>
     </row>
@@ -16108,7 +16114,7 @@
         <f t="shared" si="1"/>
         <v>3789.4000000000033</v>
       </c>
-      <c r="N34" s="139" t="s">
+      <c r="N34" s="122" t="s">
         <v>114</v>
       </c>
     </row>
@@ -16136,7 +16142,7 @@
         <f t="shared" si="1"/>
         <v>3578.8700000000031</v>
       </c>
-      <c r="N35" s="139" t="s">
+      <c r="N35" s="122" t="s">
         <v>114</v>
       </c>
     </row>
@@ -16164,7 +16170,7 @@
         <f t="shared" si="1"/>
         <v>3368.3400000000029</v>
       </c>
-      <c r="N36" s="139" t="s">
+      <c r="N36" s="122" t="s">
         <v>114</v>
       </c>
     </row>
@@ -16192,7 +16198,7 @@
         <f t="shared" si="1"/>
         <v>3157.8100000000027</v>
       </c>
-      <c r="N37" s="139" t="s">
+      <c r="N37" s="122" t="s">
         <v>114</v>
       </c>
     </row>
@@ -16220,7 +16226,7 @@
         <f t="shared" si="1"/>
         <v>2947.2800000000025</v>
       </c>
-      <c r="N38" s="139" t="s">
+      <c r="N38" s="122" t="s">
         <v>114</v>
       </c>
     </row>
@@ -16248,7 +16254,7 @@
         <f t="shared" si="1"/>
         <v>2736.7500000000023</v>
       </c>
-      <c r="N39" s="139" t="s">
+      <c r="N39" s="122" t="s">
         <v>114</v>
       </c>
     </row>
@@ -16276,7 +16282,7 @@
         <f t="shared" si="1"/>
         <v>2526.2200000000021</v>
       </c>
-      <c r="N40" s="139" t="s">
+      <c r="N40" s="122" t="s">
         <v>114</v>
       </c>
     </row>
@@ -16304,7 +16310,7 @@
         <f t="shared" si="1"/>
         <v>2315.6900000000019</v>
       </c>
-      <c r="N41" s="139" t="s">
+      <c r="N41" s="122" t="s">
         <v>114</v>
       </c>
     </row>
@@ -16332,7 +16338,7 @@
         <f t="shared" si="1"/>
         <v>2105.1600000000017</v>
       </c>
-      <c r="N42" s="139" t="s">
+      <c r="N42" s="122" t="s">
         <v>114</v>
       </c>
     </row>
@@ -16360,7 +16366,7 @@
         <f t="shared" si="1"/>
         <v>1894.6300000000017</v>
       </c>
-      <c r="N43" s="139" t="s">
+      <c r="N43" s="122" t="s">
         <v>114</v>
       </c>
     </row>
@@ -16388,7 +16394,7 @@
         <f t="shared" si="1"/>
         <v>1684.1000000000017</v>
       </c>
-      <c r="N44" s="139" t="s">
+      <c r="N44" s="122" t="s">
         <v>114</v>
       </c>
     </row>
@@ -16416,7 +16422,7 @@
         <f t="shared" si="1"/>
         <v>1473.5700000000018</v>
       </c>
-      <c r="N45" s="139" t="s">
+      <c r="N45" s="122" t="s">
         <v>114</v>
       </c>
     </row>
@@ -16444,7 +16450,7 @@
         <f t="shared" si="1"/>
         <v>1263.0400000000018</v>
       </c>
-      <c r="N46" s="139" t="s">
+      <c r="N46" s="122" t="s">
         <v>114</v>
       </c>
     </row>
@@ -16472,7 +16478,7 @@
         <f t="shared" si="1"/>
         <v>1052.5100000000018</v>
       </c>
-      <c r="N47" s="139" t="s">
+      <c r="N47" s="122" t="s">
         <v>114</v>
       </c>
     </row>
@@ -16500,7 +16506,7 @@
         <f t="shared" si="1"/>
         <v>841.98000000000184</v>
       </c>
-      <c r="N48" s="139" t="s">
+      <c r="N48" s="122" t="s">
         <v>114</v>
       </c>
     </row>
@@ -16528,7 +16534,7 @@
         <f t="shared" si="1"/>
         <v>631.45000000000186</v>
       </c>
-      <c r="N49" s="139" t="s">
+      <c r="N49" s="122" t="s">
         <v>114</v>
       </c>
     </row>
@@ -16556,7 +16562,7 @@
         <f t="shared" si="1"/>
         <v>420.92000000000189</v>
       </c>
-      <c r="N50" s="139" t="s">
+      <c r="N50" s="122" t="s">
         <v>114</v>
       </c>
     </row>
@@ -16584,7 +16590,7 @@
         <f t="shared" si="1"/>
         <v>210.39000000000189</v>
       </c>
-      <c r="N51" s="139" t="s">
+      <c r="N51" s="122" t="s">
         <v>114</v>
       </c>
     </row>
@@ -16709,30 +16715,30 @@
   <sheetData>
     <row r="1" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:26" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="136" t="s">
+      <c r="B2" s="137" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="137"/>
-      <c r="F2" s="137"/>
-      <c r="G2" s="137"/>
-      <c r="H2" s="137"/>
-      <c r="I2" s="137"/>
-      <c r="J2" s="137"/>
-      <c r="K2" s="137"/>
-      <c r="L2" s="137"/>
-      <c r="M2" s="137"/>
-      <c r="N2" s="137"/>
-      <c r="O2" s="137"/>
-      <c r="P2" s="137"/>
-      <c r="Q2" s="137"/>
-      <c r="R2" s="137"/>
-      <c r="S2" s="137"/>
-      <c r="T2" s="137"/>
-      <c r="U2" s="137"/>
-      <c r="V2" s="137"/>
-      <c r="W2" s="138"/>
+      <c r="C2" s="138"/>
+      <c r="D2" s="138"/>
+      <c r="E2" s="138"/>
+      <c r="F2" s="138"/>
+      <c r="G2" s="138"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
+      <c r="K2" s="138"/>
+      <c r="L2" s="138"/>
+      <c r="M2" s="138"/>
+      <c r="N2" s="138"/>
+      <c r="O2" s="138"/>
+      <c r="P2" s="138"/>
+      <c r="Q2" s="138"/>
+      <c r="R2" s="138"/>
+      <c r="S2" s="138"/>
+      <c r="T2" s="138"/>
+      <c r="U2" s="138"/>
+      <c r="V2" s="138"/>
+      <c r="W2" s="139"/>
     </row>
     <row r="3" spans="2:26" s="4" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="48" t="s">
@@ -17563,8 +17569,8 @@
       <c r="Z22" s="57"/>
     </row>
     <row r="24" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="P24" s="135"/>
-      <c r="Q24" s="135"/>
+      <c r="P24" s="136"/>
+      <c r="Q24" s="136"/>
       <c r="R24" s="73"/>
       <c r="S24" s="73"/>
       <c r="T24" s="73"/>
@@ -17573,8 +17579,8 @@
       <c r="W24" s="74"/>
     </row>
     <row r="25" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="P25" s="135"/>
-      <c r="Q25" s="135"/>
+      <c r="P25" s="136"/>
+      <c r="Q25" s="136"/>
       <c r="R25" s="73"/>
       <c r="S25" s="73"/>
       <c r="T25" s="73"/>
@@ -17583,8 +17589,8 @@
       <c r="W25" s="74"/>
     </row>
     <row r="26" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="P26" s="135"/>
-      <c r="Q26" s="135"/>
+      <c r="P26" s="136"/>
+      <c r="Q26" s="136"/>
       <c r="R26" s="73"/>
       <c r="S26" s="73"/>
       <c r="T26" s="73"/>
@@ -17593,8 +17599,8 @@
       <c r="W26" s="74"/>
     </row>
     <row r="27" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="P27" s="135"/>
-      <c r="Q27" s="135"/>
+      <c r="P27" s="136"/>
+      <c r="Q27" s="136"/>
       <c r="R27" s="73"/>
       <c r="S27" s="73"/>
       <c r="T27" s="73"/>
@@ -17603,8 +17609,8 @@
       <c r="W27" s="75"/>
     </row>
     <row r="28" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="P28" s="135"/>
-      <c r="Q28" s="135"/>
+      <c r="P28" s="136"/>
+      <c r="Q28" s="136"/>
       <c r="R28" s="73"/>
       <c r="S28" s="73"/>
       <c r="T28" s="73"/>

--- a/parcelamentos_local.xlsx
+++ b/parcelamentos_local.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.121.21.252\controladoria\Vitor\TRIBUTARIO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{469E9222-E42F-478F-B55E-489D032C95AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3F9CF56-881C-45B9-A69C-14C3D94E8347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="804" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="804" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SALDO CREDOR INSS" sheetId="14" r:id="rId1"/>
@@ -105,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="114">
   <si>
     <t>TAURA AGRONEGOCIOS - IMPOSTOS EM ABERTO - NÃO PARCELADOS NA RECEITA FEDERAL</t>
   </si>
@@ -447,9 +447,6 @@
   </si>
   <si>
     <t>Status</t>
-  </si>
-  <si>
-    <t>Pendente</t>
   </si>
 </sst>
 </file>
@@ -1012,7 +1009,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="140">
+  <cellXfs count="139">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1263,7 +1260,7 @@
     <xf numFmtId="43" fontId="21" fillId="8" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1282,9 +1279,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5023,10 +5017,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="97"/>
-      <c r="B8" s="129" t="s">
+      <c r="B8" s="122" t="s">
         <v>101</v>
       </c>
-      <c r="C8" s="129"/>
+      <c r="C8" s="122"/>
       <c r="D8" s="103"/>
       <c r="E8" s="103"/>
       <c r="F8" s="103"/>
@@ -5743,7 +5737,7 @@
       </c>
       <c r="C15" s="17">
         <f>'PARCELAMENTO SC'!R4</f>
-        <v>3855.700000000008</v>
+        <v>0</v>
       </c>
       <c r="D15" s="18" t="s">
         <v>111</v>
@@ -5759,7 +5753,7 @@
       <c r="B16" s="20"/>
       <c r="C16" s="89">
         <f>SUM(C11:C15)</f>
-        <v>2376964.6699999995</v>
+        <v>2373108.9699999993</v>
       </c>
       <c r="D16" s="20"/>
       <c r="E16" s="20"/>
@@ -6300,10 +6294,10 @@
         <f>M5-I6</f>
         <v>511198.30999999994</v>
       </c>
-      <c r="O6" s="130" t="s">
+      <c r="O6" s="129" t="s">
         <v>89</v>
       </c>
-      <c r="P6" s="130"/>
+      <c r="P6" s="129"/>
       <c r="Q6" s="82">
         <f>(Q4/O4)-1</f>
         <v>-0.46666646370129106</v>
@@ -6434,11 +6428,11 @@
         <f>M8-I9</f>
         <v>484757.02999999991</v>
       </c>
-      <c r="O9" s="131" t="s">
+      <c r="O9" s="130" t="s">
         <v>87</v>
       </c>
-      <c r="P9" s="131"/>
-      <c r="Q9" s="131"/>
+      <c r="P9" s="130"/>
+      <c r="Q9" s="130"/>
     </row>
     <row r="10" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="81" t="s">
@@ -6480,11 +6474,11 @@
         <f t="shared" ref="M10:M63" si="2">M9-I10</f>
         <v>475943.2699999999</v>
       </c>
-      <c r="O10" s="132" t="s">
+      <c r="O10" s="131" t="s">
         <v>88</v>
       </c>
-      <c r="P10" s="132"/>
-      <c r="Q10" s="132"/>
+      <c r="P10" s="131"/>
+      <c r="Q10" s="131"/>
     </row>
     <row r="11" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="81" t="s">
@@ -6526,11 +6520,11 @@
         <f t="shared" si="2"/>
         <v>467129.50999999989</v>
       </c>
-      <c r="O11" s="133" t="s">
+      <c r="O11" s="132" t="s">
         <v>90</v>
       </c>
-      <c r="P11" s="133"/>
-      <c r="Q11" s="133"/>
+      <c r="P11" s="132"/>
+      <c r="Q11" s="132"/>
     </row>
     <row r="12" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="83" t="s">
@@ -8340,10 +8334,10 @@
         <f>M5-I6</f>
         <v>1073254.2800000003</v>
       </c>
-      <c r="O6" s="130" t="s">
+      <c r="O6" s="129" t="s">
         <v>89</v>
       </c>
-      <c r="P6" s="130"/>
+      <c r="P6" s="129"/>
       <c r="Q6" s="82">
         <f>Q4/O4-1</f>
         <v>-0.36666658740617009</v>
@@ -8472,11 +8466,11 @@
         <f t="shared" si="2"/>
         <v>1017741.1400000004</v>
       </c>
-      <c r="O9" s="134" t="s">
+      <c r="O9" s="133" t="s">
         <v>86</v>
       </c>
-      <c r="P9" s="134"/>
-      <c r="Q9" s="134"/>
+      <c r="P9" s="133"/>
+      <c r="Q9" s="133"/>
     </row>
     <row r="10" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="79" t="s">
@@ -8518,11 +8512,11 @@
         <f t="shared" si="2"/>
         <v>999236.76000000036</v>
       </c>
-      <c r="O10" s="131" t="s">
+      <c r="O10" s="130" t="s">
         <v>87</v>
       </c>
-      <c r="P10" s="131"/>
-      <c r="Q10" s="131"/>
+      <c r="P10" s="130"/>
+      <c r="Q10" s="130"/>
     </row>
     <row r="11" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="79" t="s">
@@ -8564,11 +8558,11 @@
         <f t="shared" si="2"/>
         <v>980732.38000000035</v>
       </c>
-      <c r="O11" s="132" t="s">
+      <c r="O11" s="131" t="s">
         <v>88</v>
       </c>
-      <c r="P11" s="132"/>
-      <c r="Q11" s="132"/>
+      <c r="P11" s="131"/>
+      <c r="Q11" s="131"/>
     </row>
     <row r="12" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="79" t="s">
@@ -11460,10 +11454,10 @@
         <f>M5-I6</f>
         <v>1727211.77</v>
       </c>
-      <c r="O6" s="130" t="s">
+      <c r="O6" s="129" t="s">
         <v>89</v>
       </c>
-      <c r="P6" s="130"/>
+      <c r="P6" s="129"/>
       <c r="Q6" s="82">
         <f>(Q4/O4)-1</f>
         <v>-0.26666663831011039</v>
@@ -11594,11 +11588,11 @@
         <f t="shared" ref="M9:M63" si="2">M8-I9</f>
         <v>1637873.24</v>
       </c>
-      <c r="O9" s="131" t="s">
+      <c r="O9" s="130" t="s">
         <v>87</v>
       </c>
-      <c r="P9" s="131"/>
-      <c r="Q9" s="131"/>
+      <c r="P9" s="130"/>
+      <c r="Q9" s="130"/>
     </row>
     <row r="10" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="81" t="s">
@@ -11640,11 +11634,11 @@
         <f t="shared" si="2"/>
         <v>1608093.73</v>
       </c>
-      <c r="O10" s="132" t="s">
+      <c r="O10" s="131" t="s">
         <v>88</v>
       </c>
-      <c r="P10" s="132"/>
-      <c r="Q10" s="132"/>
+      <c r="P10" s="131"/>
+      <c r="Q10" s="131"/>
     </row>
     <row r="11" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="81" t="s">
@@ -11686,11 +11680,11 @@
         <f t="shared" si="2"/>
         <v>1578314.22</v>
       </c>
-      <c r="O11" s="133" t="s">
+      <c r="O11" s="132" t="s">
         <v>90</v>
       </c>
-      <c r="P11" s="133"/>
-      <c r="Q11" s="133"/>
+      <c r="P11" s="132"/>
+      <c r="Q11" s="132"/>
     </row>
     <row r="12" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="81" t="s">
@@ -13466,10 +13460,10 @@
         <f>M5-I6</f>
         <v>88254.450000000012</v>
       </c>
-      <c r="O6" s="130" t="s">
+      <c r="O6" s="129" t="s">
         <v>89</v>
       </c>
-      <c r="P6" s="130"/>
+      <c r="P6" s="129"/>
       <c r="Q6" s="82">
         <f>(Q4/O4)-1</f>
         <v>-0.14999919494129588</v>
@@ -13555,11 +13549,11 @@
         <f t="shared" ref="M9:M63" si="2">M8-I9</f>
         <v>83689.590000000026</v>
       </c>
-      <c r="O9" s="131" t="s">
+      <c r="O9" s="130" t="s">
         <v>87</v>
       </c>
-      <c r="P9" s="131"/>
-      <c r="Q9" s="131"/>
+      <c r="P9" s="130"/>
+      <c r="Q9" s="130"/>
     </row>
     <row r="10" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="39"/>
@@ -13586,11 +13580,11 @@
         <f t="shared" si="2"/>
         <v>82167.97000000003</v>
       </c>
-      <c r="O10" s="132" t="s">
+      <c r="O10" s="131" t="s">
         <v>88</v>
       </c>
-      <c r="P10" s="132"/>
-      <c r="Q10" s="132"/>
+      <c r="P10" s="131"/>
+      <c r="Q10" s="131"/>
     </row>
     <row r="11" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="39"/>
@@ -13617,11 +13611,11 @@
         <f t="shared" si="2"/>
         <v>80646.350000000035</v>
       </c>
-      <c r="O11" s="133" t="s">
+      <c r="O11" s="132" t="s">
         <v>90</v>
       </c>
-      <c r="P11" s="133"/>
-      <c r="Q11" s="133"/>
+      <c r="P11" s="132"/>
+      <c r="Q11" s="132"/>
     </row>
     <row r="12" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="39"/>
@@ -15232,15 +15226,15 @@
       </c>
       <c r="P4" s="32">
         <f>I52</f>
-        <v>10105.300000000005</v>
+        <v>11562</v>
       </c>
       <c r="Q4" s="33">
-        <f>K5+K6+K7+K8+K9+K10+K11+K12+K13+K14+K15+K16+K17+K18+K19+K20+K21+K22+K23+K24+K25+K26+K27+K28+K29+K30+K31+K32</f>
-        <v>6249.5999999999967</v>
+        <f>K5+K6+K7+K8+K9+K10+K11+K12+K13+K14+K15+K16+K17+K18+K19+K20+K21+K22+K23+K24+K25+K26+K27+K28+K29+K30+K31+K32+K33+K34+K35+K36+K37+K38+K39+K40+K41+K42+K43+K44+K45+K46+K47+K48+K49+K50+K51</f>
+        <v>11562.000000000004</v>
       </c>
       <c r="R4" s="34">
         <f>P4-Q4</f>
-        <v>3855.700000000008</v>
+        <v>0</v>
       </c>
       <c r="S4" s="34">
         <f>J5+J6+J7+J8+J9+J10+J11+J12+J13+J14+J15+J16+J17+J18+J19+J20+J21+J22+J23+J24+J25+J26+J27+J28+J29+J30+J31+J32+J33+J34+J35+J36+J37+J38+J39+J40+J41+J42+J43+J44+J45+J46+J47+J48+J49+J50+J51-354.74</f>
@@ -15270,7 +15264,7 @@
       </c>
       <c r="M5" s="31">
         <f>$P$4-I4</f>
-        <v>9894.7700000000041</v>
+        <v>11351.47</v>
       </c>
       <c r="N5" s="84" t="s">
         <v>25</v>
@@ -15299,18 +15293,18 @@
       </c>
       <c r="M6" s="31">
         <f>M5-I6</f>
-        <v>9684.2400000000034</v>
+        <v>11140.939999999999</v>
       </c>
       <c r="N6" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="P6" s="130" t="s">
+      <c r="P6" s="129" t="s">
         <v>89</v>
       </c>
-      <c r="Q6" s="130"/>
+      <c r="Q6" s="129"/>
       <c r="R6" s="82">
         <f>(R4/P4)-1</f>
-        <v>-0.61844774524259494</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7" spans="2:19" customFormat="1" x14ac:dyDescent="0.3">
@@ -15336,7 +15330,7 @@
       </c>
       <c r="M7" s="31">
         <f t="shared" ref="M7:M51" si="1">M6-I7</f>
-        <v>9473.7100000000028</v>
+        <v>10930.409999999998</v>
       </c>
       <c r="N7" s="84" t="s">
         <v>25</v>
@@ -15368,10 +15362,14 @@
       </c>
       <c r="M8" s="31">
         <f t="shared" si="1"/>
-        <v>9263.1800000000021</v>
+        <v>10719.879999999997</v>
       </c>
       <c r="N8" s="84" t="s">
         <v>25</v>
+      </c>
+      <c r="R8" s="88">
+        <f>Q4-P4</f>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:19" customFormat="1" x14ac:dyDescent="0.3">
@@ -15397,14 +15395,14 @@
       </c>
       <c r="M9" s="31">
         <f t="shared" si="1"/>
-        <v>9052.6500000000015</v>
+        <v>10509.349999999997</v>
       </c>
       <c r="N9" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="P9" s="135"/>
-      <c r="Q9" s="135"/>
-      <c r="R9" s="135"/>
+      <c r="P9" s="134"/>
+      <c r="Q9" s="134"/>
+      <c r="R9" s="134"/>
     </row>
     <row r="10" spans="2:19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="39"/>
@@ -15429,14 +15427,14 @@
       </c>
       <c r="M10" s="31">
         <f t="shared" si="1"/>
-        <v>8842.1200000000008</v>
+        <v>10298.819999999996</v>
       </c>
       <c r="N10" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="P10" s="135"/>
-      <c r="Q10" s="135"/>
-      <c r="R10" s="135"/>
+      <c r="P10" s="134"/>
+      <c r="Q10" s="134"/>
+      <c r="R10" s="134"/>
     </row>
     <row r="11" spans="2:19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="39"/>
@@ -15461,14 +15459,14 @@
       </c>
       <c r="M11" s="31">
         <f t="shared" si="1"/>
-        <v>8631.59</v>
+        <v>10088.289999999995</v>
       </c>
       <c r="N11" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="P11" s="135"/>
-      <c r="Q11" s="135"/>
-      <c r="R11" s="135"/>
+      <c r="P11" s="134"/>
+      <c r="Q11" s="134"/>
+      <c r="R11" s="134"/>
     </row>
     <row r="12" spans="2:19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="39"/>
@@ -15493,7 +15491,7 @@
       </c>
       <c r="M12" s="31">
         <f t="shared" si="1"/>
-        <v>8421.06</v>
+        <v>9877.7599999999948</v>
       </c>
       <c r="N12" s="84" t="s">
         <v>25</v>
@@ -15522,7 +15520,7 @@
       </c>
       <c r="M13" s="31">
         <f t="shared" si="1"/>
-        <v>8210.5299999999988</v>
+        <v>9667.2299999999941</v>
       </c>
       <c r="N13" s="84" t="s">
         <v>25</v>
@@ -15551,7 +15549,7 @@
       </c>
       <c r="M14" s="31">
         <f t="shared" si="1"/>
-        <v>7999.9999999999991</v>
+        <v>9456.6999999999935</v>
       </c>
       <c r="N14" s="84" t="s">
         <v>25</v>
@@ -15580,7 +15578,7 @@
       </c>
       <c r="M15" s="31">
         <f t="shared" si="1"/>
-        <v>7789.4699999999993</v>
+        <v>9246.1699999999928</v>
       </c>
       <c r="N15" s="84" t="s">
         <v>25</v>
@@ -15608,7 +15606,7 @@
       </c>
       <c r="M16" s="31">
         <f t="shared" si="1"/>
-        <v>7578.94</v>
+        <v>9035.6399999999921</v>
       </c>
       <c r="N16" s="84" t="s">
         <v>25</v>
@@ -15636,7 +15634,7 @@
       </c>
       <c r="M17" s="31">
         <f t="shared" si="1"/>
-        <v>7368.41</v>
+        <v>8825.1099999999915</v>
       </c>
       <c r="N17" s="84" t="s">
         <v>25</v>
@@ -15664,7 +15662,7 @@
       </c>
       <c r="M18" s="31">
         <f t="shared" si="1"/>
-        <v>7157.88</v>
+        <v>8614.5799999999908</v>
       </c>
       <c r="N18" s="84" t="s">
         <v>25</v>
@@ -15692,7 +15690,7 @@
       </c>
       <c r="M19" s="31">
         <f t="shared" si="1"/>
-        <v>6947.35</v>
+        <v>8404.0499999999902</v>
       </c>
       <c r="N19" s="84" t="s">
         <v>25</v>
@@ -15720,7 +15718,7 @@
       </c>
       <c r="M20" s="31">
         <f t="shared" si="1"/>
-        <v>6736.8200000000006</v>
+        <v>8193.5199999999895</v>
       </c>
       <c r="N20" s="84" t="s">
         <v>25</v>
@@ -15748,7 +15746,7 @@
       </c>
       <c r="M21" s="31">
         <f t="shared" si="1"/>
-        <v>6526.2900000000009</v>
+        <v>7982.9899999999898</v>
       </c>
       <c r="N21" s="84" t="s">
         <v>25</v>
@@ -15776,7 +15774,7 @@
       </c>
       <c r="M22" s="31">
         <f t="shared" si="1"/>
-        <v>6315.7600000000011</v>
+        <v>7772.45999999999</v>
       </c>
       <c r="N22" s="84" t="s">
         <v>25</v>
@@ -15804,7 +15802,7 @@
       </c>
       <c r="M23" s="31">
         <f t="shared" si="1"/>
-        <v>6105.2300000000014</v>
+        <v>7561.9299999999903</v>
       </c>
       <c r="N23" s="84" t="s">
         <v>25</v>
@@ -15832,7 +15830,7 @@
       </c>
       <c r="M24" s="31">
         <f t="shared" si="1"/>
-        <v>5894.7000000000016</v>
+        <v>7351.3999999999905</v>
       </c>
       <c r="N24" s="84" t="s">
         <v>25</v>
@@ -15860,7 +15858,7 @@
       </c>
       <c r="M25" s="31">
         <f t="shared" si="1"/>
-        <v>5684.1700000000019</v>
+        <v>7140.8699999999908</v>
       </c>
       <c r="N25" s="84" t="s">
         <v>25</v>
@@ -15888,7 +15886,7 @@
       </c>
       <c r="M26" s="31">
         <f t="shared" si="1"/>
-        <v>5473.6400000000021</v>
+        <v>6930.3399999999911</v>
       </c>
       <c r="N26" s="84" t="s">
         <v>25</v>
@@ -15916,7 +15914,7 @@
       </c>
       <c r="M27" s="31">
         <f t="shared" si="1"/>
-        <v>5263.1100000000024</v>
+        <v>6719.8099999999913</v>
       </c>
       <c r="N27" s="84" t="s">
         <v>25</v>
@@ -15944,7 +15942,7 @@
       </c>
       <c r="M28" s="31">
         <f t="shared" si="1"/>
-        <v>5052.5800000000027</v>
+        <v>6509.2799999999916</v>
       </c>
       <c r="N28" s="84" t="s">
         <v>25</v>
@@ -15972,7 +15970,7 @@
       </c>
       <c r="M29" s="31">
         <f t="shared" si="1"/>
-        <v>4842.0500000000029</v>
+        <v>6298.7499999999918</v>
       </c>
       <c r="N29" s="84" t="s">
         <v>25</v>
@@ -16000,7 +15998,7 @@
       </c>
       <c r="M30" s="31">
         <f t="shared" si="1"/>
-        <v>4631.5200000000032</v>
+        <v>6088.2199999999921</v>
       </c>
       <c r="N30" s="84" t="s">
         <v>25</v>
@@ -16028,7 +16026,7 @@
       </c>
       <c r="M31" s="31">
         <f t="shared" si="1"/>
-        <v>4420.9900000000034</v>
+        <v>5877.6899999999923</v>
       </c>
       <c r="N31" s="84" t="s">
         <v>25</v>
@@ -16056,7 +16054,7 @@
       </c>
       <c r="M32" s="31">
         <f t="shared" si="1"/>
-        <v>4210.4600000000037</v>
+        <v>5667.1599999999926</v>
       </c>
       <c r="N32" s="84" t="s">
         <v>25</v>
@@ -16084,10 +16082,10 @@
       </c>
       <c r="M33" s="31">
         <f t="shared" si="1"/>
-        <v>3999.9300000000035</v>
-      </c>
-      <c r="N33" s="122" t="s">
-        <v>114</v>
+        <v>5456.6299999999928</v>
+      </c>
+      <c r="N33" s="84" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="34" spans="3:14" x14ac:dyDescent="0.3">
@@ -16112,10 +16110,10 @@
       </c>
       <c r="M34" s="31">
         <f t="shared" si="1"/>
-        <v>3789.4000000000033</v>
-      </c>
-      <c r="N34" s="122" t="s">
-        <v>114</v>
+        <v>5246.0999999999931</v>
+      </c>
+      <c r="N34" s="84" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="35" spans="3:14" x14ac:dyDescent="0.3">
@@ -16140,10 +16138,10 @@
       </c>
       <c r="M35" s="31">
         <f t="shared" si="1"/>
-        <v>3578.8700000000031</v>
-      </c>
-      <c r="N35" s="122" t="s">
-        <v>114</v>
+        <v>5035.5699999999933</v>
+      </c>
+      <c r="N35" s="84" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="3:14" x14ac:dyDescent="0.3">
@@ -16168,10 +16166,10 @@
       </c>
       <c r="M36" s="31">
         <f t="shared" si="1"/>
-        <v>3368.3400000000029</v>
-      </c>
-      <c r="N36" s="122" t="s">
-        <v>114</v>
+        <v>4825.0399999999936</v>
+      </c>
+      <c r="N36" s="84" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="3:14" x14ac:dyDescent="0.3">
@@ -16196,10 +16194,10 @@
       </c>
       <c r="M37" s="31">
         <f t="shared" si="1"/>
-        <v>3157.8100000000027</v>
-      </c>
-      <c r="N37" s="122" t="s">
-        <v>114</v>
+        <v>4614.5099999999939</v>
+      </c>
+      <c r="N37" s="84" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="3:14" x14ac:dyDescent="0.3">
@@ -16224,10 +16222,10 @@
       </c>
       <c r="M38" s="31">
         <f t="shared" si="1"/>
-        <v>2947.2800000000025</v>
-      </c>
-      <c r="N38" s="122" t="s">
-        <v>114</v>
+        <v>4403.9799999999941</v>
+      </c>
+      <c r="N38" s="84" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="39" spans="3:14" x14ac:dyDescent="0.3">
@@ -16252,10 +16250,10 @@
       </c>
       <c r="M39" s="31">
         <f t="shared" si="1"/>
-        <v>2736.7500000000023</v>
-      </c>
-      <c r="N39" s="122" t="s">
-        <v>114</v>
+        <v>4193.4499999999944</v>
+      </c>
+      <c r="N39" s="84" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="40" spans="3:14" x14ac:dyDescent="0.3">
@@ -16280,10 +16278,10 @@
       </c>
       <c r="M40" s="31">
         <f t="shared" si="1"/>
-        <v>2526.2200000000021</v>
-      </c>
-      <c r="N40" s="122" t="s">
-        <v>114</v>
+        <v>3982.9199999999942</v>
+      </c>
+      <c r="N40" s="84" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="41" spans="3:14" x14ac:dyDescent="0.3">
@@ -16308,10 +16306,10 @@
       </c>
       <c r="M41" s="31">
         <f t="shared" si="1"/>
-        <v>2315.6900000000019</v>
-      </c>
-      <c r="N41" s="122" t="s">
-        <v>114</v>
+        <v>3772.389999999994</v>
+      </c>
+      <c r="N41" s="84" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="42" spans="3:14" x14ac:dyDescent="0.3">
@@ -16336,10 +16334,10 @@
       </c>
       <c r="M42" s="31">
         <f t="shared" si="1"/>
-        <v>2105.1600000000017</v>
-      </c>
-      <c r="N42" s="122" t="s">
-        <v>114</v>
+        <v>3561.8599999999938</v>
+      </c>
+      <c r="N42" s="84" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="43" spans="3:14" x14ac:dyDescent="0.3">
@@ -16364,10 +16362,10 @@
       </c>
       <c r="M43" s="31">
         <f t="shared" si="1"/>
-        <v>1894.6300000000017</v>
-      </c>
-      <c r="N43" s="122" t="s">
-        <v>114</v>
+        <v>3351.3299999999936</v>
+      </c>
+      <c r="N43" s="84" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="44" spans="3:14" x14ac:dyDescent="0.3">
@@ -16392,10 +16390,10 @@
       </c>
       <c r="M44" s="31">
         <f t="shared" si="1"/>
-        <v>1684.1000000000017</v>
-      </c>
-      <c r="N44" s="122" t="s">
-        <v>114</v>
+        <v>3140.7999999999934</v>
+      </c>
+      <c r="N44" s="84" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="45" spans="3:14" x14ac:dyDescent="0.3">
@@ -16420,10 +16418,10 @@
       </c>
       <c r="M45" s="31">
         <f t="shared" si="1"/>
-        <v>1473.5700000000018</v>
-      </c>
-      <c r="N45" s="122" t="s">
-        <v>114</v>
+        <v>2930.2699999999932</v>
+      </c>
+      <c r="N45" s="84" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="46" spans="3:14" x14ac:dyDescent="0.3">
@@ -16448,10 +16446,10 @@
       </c>
       <c r="M46" s="31">
         <f t="shared" si="1"/>
-        <v>1263.0400000000018</v>
-      </c>
-      <c r="N46" s="122" t="s">
-        <v>114</v>
+        <v>2719.739999999993</v>
+      </c>
+      <c r="N46" s="84" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="47" spans="3:14" x14ac:dyDescent="0.3">
@@ -16476,10 +16474,10 @@
       </c>
       <c r="M47" s="31">
         <f t="shared" si="1"/>
-        <v>1052.5100000000018</v>
-      </c>
-      <c r="N47" s="122" t="s">
-        <v>114</v>
+        <v>2509.2099999999928</v>
+      </c>
+      <c r="N47" s="84" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="48" spans="3:14" x14ac:dyDescent="0.3">
@@ -16504,10 +16502,10 @@
       </c>
       <c r="M48" s="31">
         <f t="shared" si="1"/>
-        <v>841.98000000000184</v>
-      </c>
-      <c r="N48" s="122" t="s">
-        <v>114</v>
+        <v>2298.6799999999926</v>
+      </c>
+      <c r="N48" s="84" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="49" spans="3:14" x14ac:dyDescent="0.3">
@@ -16532,10 +16530,10 @@
       </c>
       <c r="M49" s="31">
         <f t="shared" si="1"/>
-        <v>631.45000000000186</v>
-      </c>
-      <c r="N49" s="122" t="s">
-        <v>114</v>
+        <v>2088.1499999999924</v>
+      </c>
+      <c r="N49" s="84" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="50" spans="3:14" x14ac:dyDescent="0.3">
@@ -16560,10 +16558,10 @@
       </c>
       <c r="M50" s="31">
         <f t="shared" si="1"/>
-        <v>420.92000000000189</v>
-      </c>
-      <c r="N50" s="122" t="s">
-        <v>114</v>
+        <v>1877.6199999999924</v>
+      </c>
+      <c r="N50" s="84" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="51" spans="3:14" x14ac:dyDescent="0.3">
@@ -16588,10 +16586,10 @@
       </c>
       <c r="M51" s="31">
         <f t="shared" si="1"/>
-        <v>210.39000000000189</v>
-      </c>
-      <c r="N51" s="122" t="s">
-        <v>114</v>
+        <v>1667.0899999999924</v>
+      </c>
+      <c r="N51" s="84" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="52" spans="3:14" x14ac:dyDescent="0.3">
@@ -16602,8 +16600,8 @@
       <c r="G52" s="42"/>
       <c r="H52" s="42"/>
       <c r="I52" s="42">
-        <f>SUM(I4:I51)-0.14</f>
-        <v>10105.300000000005</v>
+        <f>SUM(I4:I51)-0.14+J33+J34+J35+J36+J37+J38+J39+J40+J41+J42+J43+J44+J45+J46+J47+J48+J49+J50+J51+144.37</f>
+        <v>11562</v>
       </c>
       <c r="J52" s="42"/>
       <c r="K52" s="42"/>
@@ -16715,30 +16713,30 @@
   <sheetData>
     <row r="1" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:26" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="137" t="s">
+      <c r="B2" s="136" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="138"/>
-      <c r="D2" s="138"/>
-      <c r="E2" s="138"/>
-      <c r="F2" s="138"/>
-      <c r="G2" s="138"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="138"/>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="138"/>
-      <c r="M2" s="138"/>
-      <c r="N2" s="138"/>
-      <c r="O2" s="138"/>
-      <c r="P2" s="138"/>
-      <c r="Q2" s="138"/>
-      <c r="R2" s="138"/>
-      <c r="S2" s="138"/>
-      <c r="T2" s="138"/>
-      <c r="U2" s="138"/>
-      <c r="V2" s="138"/>
-      <c r="W2" s="139"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="137"/>
+      <c r="F2" s="137"/>
+      <c r="G2" s="137"/>
+      <c r="H2" s="137"/>
+      <c r="I2" s="137"/>
+      <c r="J2" s="137"/>
+      <c r="K2" s="137"/>
+      <c r="L2" s="137"/>
+      <c r="M2" s="137"/>
+      <c r="N2" s="137"/>
+      <c r="O2" s="137"/>
+      <c r="P2" s="137"/>
+      <c r="Q2" s="137"/>
+      <c r="R2" s="137"/>
+      <c r="S2" s="137"/>
+      <c r="T2" s="137"/>
+      <c r="U2" s="137"/>
+      <c r="V2" s="137"/>
+      <c r="W2" s="138"/>
     </row>
     <row r="3" spans="2:26" s="4" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="48" t="s">
@@ -17569,8 +17567,8 @@
       <c r="Z22" s="57"/>
     </row>
     <row r="24" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="P24" s="136"/>
-      <c r="Q24" s="136"/>
+      <c r="P24" s="135"/>
+      <c r="Q24" s="135"/>
       <c r="R24" s="73"/>
       <c r="S24" s="73"/>
       <c r="T24" s="73"/>
@@ -17579,8 +17577,8 @@
       <c r="W24" s="74"/>
     </row>
     <row r="25" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="P25" s="136"/>
-      <c r="Q25" s="136"/>
+      <c r="P25" s="135"/>
+      <c r="Q25" s="135"/>
       <c r="R25" s="73"/>
       <c r="S25" s="73"/>
       <c r="T25" s="73"/>
@@ -17589,8 +17587,8 @@
       <c r="W25" s="74"/>
     </row>
     <row r="26" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="P26" s="136"/>
-      <c r="Q26" s="136"/>
+      <c r="P26" s="135"/>
+      <c r="Q26" s="135"/>
       <c r="R26" s="73"/>
       <c r="S26" s="73"/>
       <c r="T26" s="73"/>
@@ -17599,8 +17597,8 @@
       <c r="W26" s="74"/>
     </row>
     <row r="27" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="P27" s="136"/>
-      <c r="Q27" s="136"/>
+      <c r="P27" s="135"/>
+      <c r="Q27" s="135"/>
       <c r="R27" s="73"/>
       <c r="S27" s="73"/>
       <c r="T27" s="73"/>
@@ -17609,8 +17607,8 @@
       <c r="W27" s="75"/>
     </row>
     <row r="28" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="P28" s="136"/>
-      <c r="Q28" s="136"/>
+      <c r="P28" s="135"/>
+      <c r="Q28" s="135"/>
       <c r="R28" s="73"/>
       <c r="S28" s="73"/>
       <c r="T28" s="73"/>

--- a/parcelamentos_local.xlsx
+++ b/parcelamentos_local.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.121.21.252\controladoria\Vitor\TRIBUTARIO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3F9CF56-881C-45B9-A69C-14C3D94E8347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A96A1E39-68A3-4984-8191-C9CAFE0E0404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="804" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="804" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SALDO CREDOR INSS" sheetId="14" r:id="rId1"/>
@@ -1260,6 +1260,12 @@
     <xf numFmtId="43" fontId="21" fillId="8" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1281,9 +1287,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1294,9 +1297,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2798,10 +2798,10 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>'ACOMPANHAMENTO MENSAL'!$C$2:$Q$2</c:f>
+              <c:f>'ACOMPANHAMENTO MENSAL'!$C$2:$R$2</c:f>
               <c:numCache>
                 <c:formatCode>mmm\-yy</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>45839</c:v>
                 </c:pt>
@@ -2846,16 +2846,19 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>46266</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46296</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ACOMPANHAMENTO MENSAL'!$C$3:$Q$3</c:f>
+              <c:f>'ACOMPANHAMENTO MENSAL'!$C$3:$R$3</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>4720740.33</c:v>
                 </c:pt>
@@ -2900,6 +2903,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>3796974.4</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3713217.08</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2936,10 +2942,10 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>'ACOMPANHAMENTO MENSAL'!$C$2:$Q$2</c:f>
+              <c:f>'ACOMPANHAMENTO MENSAL'!$C$2:$R$2</c:f>
               <c:numCache>
                 <c:formatCode>mmm\-yy</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>45839</c:v>
                 </c:pt>
@@ -2984,6 +2990,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>46266</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46296</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3071,10 +3080,10 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>'ACOMPANHAMENTO MENSAL'!$C$2:$Q$2</c:f>
+              <c:f>'ACOMPANHAMENTO MENSAL'!$C$2:$R$2</c:f>
               <c:numCache>
                 <c:formatCode>mmm\-yy</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>45839</c:v>
                 </c:pt>
@@ -3119,6 +3128,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>46266</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46296</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3206,10 +3218,10 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>'ACOMPANHAMENTO MENSAL'!$C$2:$Q$2</c:f>
+              <c:f>'ACOMPANHAMENTO MENSAL'!$C$2:$R$2</c:f>
               <c:numCache>
                 <c:formatCode>mmm\-yy</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>45839</c:v>
                 </c:pt>
@@ -3254,6 +3266,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>46266</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46296</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3344,10 +3359,10 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>'ACOMPANHAMENTO MENSAL'!$C$2:$Q$2</c:f>
+              <c:f>'ACOMPANHAMENTO MENSAL'!$C$2:$R$2</c:f>
               <c:numCache>
                 <c:formatCode>mmm\-yy</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>45839</c:v>
                 </c:pt>
@@ -3392,6 +3407,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>46266</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46296</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3458,10 +3476,10 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>'ACOMPANHAMENTO MENSAL'!$C$2:$Q$2</c:f>
+              <c:f>'ACOMPANHAMENTO MENSAL'!$C$2:$R$2</c:f>
               <c:numCache>
                 <c:formatCode>mmm\-yy</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>45839</c:v>
                 </c:pt>
@@ -3506,6 +3524,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>46266</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46296</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3592,10 +3613,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'ACOMPANHAMENTO MENSAL'!$C$2:$Q$2</c:f>
+              <c:f>'ACOMPANHAMENTO MENSAL'!$C$2:$R$2</c:f>
               <c:numCache>
                 <c:formatCode>mmm\-yy</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>45839</c:v>
                 </c:pt>
@@ -3640,16 +3661,19 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>46266</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46296</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ACOMPANHAMENTO MENSAL'!$C$9:$Q$9</c:f>
+              <c:f>'ACOMPANHAMENTO MENSAL'!$C$9:$R$9</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>532107.21</c:v>
                 </c:pt>
@@ -3694,6 +3718,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>90631.83</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>157869.14000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5017,10 +5044,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="97"/>
-      <c r="B8" s="122" t="s">
+      <c r="B8" s="124" t="s">
         <v>101</v>
       </c>
-      <c r="C8" s="122"/>
+      <c r="C8" s="124"/>
       <c r="D8" s="103"/>
       <c r="E8" s="103"/>
       <c r="F8" s="103"/>
@@ -5502,15 +5529,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="123" t="s">
+      <c r="A1" s="125" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="124"/>
-      <c r="F1" s="124"/>
-      <c r="G1" s="125"/>
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
+      <c r="E1" s="126"/>
+      <c r="F1" s="126"/>
+      <c r="G1" s="127"/>
     </row>
     <row r="2" spans="1:7" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -5611,22 +5638,22 @@
     </row>
     <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="126" t="s">
+      <c r="A8" s="128" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="127"/>
-      <c r="C8" s="128"/>
+      <c r="B8" s="129"/>
+      <c r="C8" s="130"/>
       <c r="D8" s="12"/>
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
       <c r="G8" s="12"/>
     </row>
     <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="126" t="s">
+      <c r="A9" s="128" t="s">
         <v>112</v>
       </c>
-      <c r="B9" s="127"/>
-      <c r="C9" s="128"/>
+      <c r="B9" s="129"/>
+      <c r="C9" s="130"/>
       <c r="D9" s="13"/>
       <c r="E9" s="13"/>
     </row>
@@ -6294,10 +6321,10 @@
         <f>M5-I6</f>
         <v>511198.30999999994</v>
       </c>
-      <c r="O6" s="129" t="s">
+      <c r="O6" s="122" t="s">
         <v>89</v>
       </c>
-      <c r="P6" s="129"/>
+      <c r="P6" s="122"/>
       <c r="Q6" s="82">
         <f>(Q4/O4)-1</f>
         <v>-0.46666646370129106</v>
@@ -6428,11 +6455,11 @@
         <f>M8-I9</f>
         <v>484757.02999999991</v>
       </c>
-      <c r="O9" s="130" t="s">
+      <c r="O9" s="131" t="s">
         <v>87</v>
       </c>
-      <c r="P9" s="130"/>
-      <c r="Q9" s="130"/>
+      <c r="P9" s="131"/>
+      <c r="Q9" s="131"/>
     </row>
     <row r="10" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="81" t="s">
@@ -6474,11 +6501,11 @@
         <f t="shared" ref="M10:M63" si="2">M9-I10</f>
         <v>475943.2699999999</v>
       </c>
-      <c r="O10" s="131" t="s">
+      <c r="O10" s="132" t="s">
         <v>88</v>
       </c>
-      <c r="P10" s="131"/>
-      <c r="Q10" s="131"/>
+      <c r="P10" s="132"/>
+      <c r="Q10" s="132"/>
     </row>
     <row r="11" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="81" t="s">
@@ -6520,11 +6547,11 @@
         <f t="shared" si="2"/>
         <v>467129.50999999989</v>
       </c>
-      <c r="O11" s="132" t="s">
+      <c r="O11" s="133" t="s">
         <v>90</v>
       </c>
-      <c r="P11" s="132"/>
-      <c r="Q11" s="132"/>
+      <c r="P11" s="133"/>
+      <c r="Q11" s="133"/>
     </row>
     <row r="12" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="83" t="s">
@@ -8334,10 +8361,10 @@
         <f>M5-I6</f>
         <v>1073254.2800000003</v>
       </c>
-      <c r="O6" s="129" t="s">
+      <c r="O6" s="122" t="s">
         <v>89</v>
       </c>
-      <c r="P6" s="129"/>
+      <c r="P6" s="122"/>
       <c r="Q6" s="82">
         <f>Q4/O4-1</f>
         <v>-0.36666658740617009</v>
@@ -8466,11 +8493,11 @@
         <f t="shared" si="2"/>
         <v>1017741.1400000004</v>
       </c>
-      <c r="O9" s="133" t="s">
+      <c r="O9" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="P9" s="133"/>
-      <c r="Q9" s="133"/>
+      <c r="P9" s="134"/>
+      <c r="Q9" s="134"/>
     </row>
     <row r="10" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="79" t="s">
@@ -8512,11 +8539,11 @@
         <f t="shared" si="2"/>
         <v>999236.76000000036</v>
       </c>
-      <c r="O10" s="130" t="s">
+      <c r="O10" s="131" t="s">
         <v>87</v>
       </c>
-      <c r="P10" s="130"/>
-      <c r="Q10" s="130"/>
+      <c r="P10" s="131"/>
+      <c r="Q10" s="131"/>
     </row>
     <row r="11" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="79" t="s">
@@ -8558,11 +8585,11 @@
         <f t="shared" si="2"/>
         <v>980732.38000000035</v>
       </c>
-      <c r="O11" s="131" t="s">
+      <c r="O11" s="132" t="s">
         <v>88</v>
       </c>
-      <c r="P11" s="131"/>
-      <c r="Q11" s="131"/>
+      <c r="P11" s="132"/>
+      <c r="Q11" s="132"/>
     </row>
     <row r="12" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="79" t="s">
@@ -11454,10 +11481,10 @@
         <f>M5-I6</f>
         <v>1727211.77</v>
       </c>
-      <c r="O6" s="129" t="s">
+      <c r="O6" s="122" t="s">
         <v>89</v>
       </c>
-      <c r="P6" s="129"/>
+      <c r="P6" s="122"/>
       <c r="Q6" s="82">
         <f>(Q4/O4)-1</f>
         <v>-0.26666663831011039</v>
@@ -11588,11 +11615,11 @@
         <f t="shared" ref="M9:M63" si="2">M8-I9</f>
         <v>1637873.24</v>
       </c>
-      <c r="O9" s="130" t="s">
+      <c r="O9" s="131" t="s">
         <v>87</v>
       </c>
-      <c r="P9" s="130"/>
-      <c r="Q9" s="130"/>
+      <c r="P9" s="131"/>
+      <c r="Q9" s="131"/>
     </row>
     <row r="10" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="81" t="s">
@@ -11634,11 +11661,11 @@
         <f t="shared" si="2"/>
         <v>1608093.73</v>
       </c>
-      <c r="O10" s="131" t="s">
+      <c r="O10" s="132" t="s">
         <v>88</v>
       </c>
-      <c r="P10" s="131"/>
-      <c r="Q10" s="131"/>
+      <c r="P10" s="132"/>
+      <c r="Q10" s="132"/>
     </row>
     <row r="11" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="81" t="s">
@@ -11680,11 +11707,11 @@
         <f t="shared" si="2"/>
         <v>1578314.22</v>
       </c>
-      <c r="O11" s="132" t="s">
+      <c r="O11" s="133" t="s">
         <v>90</v>
       </c>
-      <c r="P11" s="132"/>
-      <c r="Q11" s="132"/>
+      <c r="P11" s="133"/>
+      <c r="Q11" s="133"/>
     </row>
     <row r="12" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="81" t="s">
@@ -13460,10 +13487,10 @@
         <f>M5-I6</f>
         <v>88254.450000000012</v>
       </c>
-      <c r="O6" s="129" t="s">
+      <c r="O6" s="122" t="s">
         <v>89</v>
       </c>
-      <c r="P6" s="129"/>
+      <c r="P6" s="122"/>
       <c r="Q6" s="82">
         <f>(Q4/O4)-1</f>
         <v>-0.14999919494129588</v>
@@ -13549,11 +13576,11 @@
         <f t="shared" ref="M9:M63" si="2">M8-I9</f>
         <v>83689.590000000026</v>
       </c>
-      <c r="O9" s="130" t="s">
+      <c r="O9" s="131" t="s">
         <v>87</v>
       </c>
-      <c r="P9" s="130"/>
-      <c r="Q9" s="130"/>
+      <c r="P9" s="131"/>
+      <c r="Q9" s="131"/>
     </row>
     <row r="10" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="39"/>
@@ -13580,11 +13607,11 @@
         <f t="shared" si="2"/>
         <v>82167.97000000003</v>
       </c>
-      <c r="O10" s="131" t="s">
+      <c r="O10" s="132" t="s">
         <v>88</v>
       </c>
-      <c r="P10" s="131"/>
-      <c r="Q10" s="131"/>
+      <c r="P10" s="132"/>
+      <c r="Q10" s="132"/>
     </row>
     <row r="11" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="39"/>
@@ -13611,11 +13638,11 @@
         <f t="shared" si="2"/>
         <v>80646.350000000035</v>
       </c>
-      <c r="O11" s="132" t="s">
+      <c r="O11" s="133" t="s">
         <v>90</v>
       </c>
-      <c r="P11" s="132"/>
-      <c r="Q11" s="132"/>
+      <c r="P11" s="133"/>
+      <c r="Q11" s="133"/>
     </row>
     <row r="12" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="39"/>
@@ -15298,10 +15325,10 @@
       <c r="N6" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="P6" s="129" t="s">
+      <c r="P6" s="122" t="s">
         <v>89</v>
       </c>
-      <c r="Q6" s="129"/>
+      <c r="Q6" s="122"/>
       <c r="R6" s="82">
         <f>(R4/P4)-1</f>
         <v>-1</v>
@@ -15400,9 +15427,9 @@
       <c r="N9" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="P9" s="134"/>
-      <c r="Q9" s="134"/>
-      <c r="R9" s="134"/>
+      <c r="P9" s="123"/>
+      <c r="Q9" s="123"/>
+      <c r="R9" s="123"/>
     </row>
     <row r="10" spans="2:19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="39"/>
@@ -15432,9 +15459,9 @@
       <c r="N10" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="P10" s="134"/>
-      <c r="Q10" s="134"/>
-      <c r="R10" s="134"/>
+      <c r="P10" s="123"/>
+      <c r="Q10" s="123"/>
+      <c r="R10" s="123"/>
     </row>
     <row r="11" spans="2:19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="39"/>
@@ -15464,9 +15491,9 @@
       <c r="N11" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="P11" s="134"/>
-      <c r="Q11" s="134"/>
-      <c r="R11" s="134"/>
+      <c r="P11" s="123"/>
+      <c r="Q11" s="123"/>
+      <c r="R11" s="123"/>
     </row>
     <row r="12" spans="2:19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="39"/>
@@ -17634,14 +17661,14 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{420301BD-1EC9-404C-9D58-1869DDAA2327}">
-  <dimension ref="B2:Q9"/>
+  <dimension ref="B2:R9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="17" width="13.33203125" customWidth="1"/>
+    <col min="3" max="18" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:18" x14ac:dyDescent="0.3">
       <c r="C2" s="85">
         <v>45839</v>
       </c>
@@ -17687,8 +17714,11 @@
       <c r="Q2" s="85">
         <v>46266</v>
       </c>
-    </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="R2" s="85">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B3" s="84" t="s">
         <v>95</v>
       </c>
@@ -17741,8 +17771,12 @@
       <c r="Q3" s="27">
         <v>3796974.4</v>
       </c>
-    </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="R3" s="27">
+        <f>3713217.08</f>
+        <v>3713217.08</v>
+      </c>
+    </row>
+    <row r="4" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B4" s="84" t="s">
         <v>96</v>
       </c>
@@ -17791,8 +17825,11 @@
       <c r="Q4" s="27">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="R4" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B5" s="84" t="s">
         <v>76</v>
       </c>
@@ -17841,8 +17878,11 @@
         <f>16179.2</f>
         <v>16179.2</v>
       </c>
-    </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="R5" s="27">
+        <v>28180.61</v>
+      </c>
+    </row>
+    <row r="6" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B6" s="84" t="s">
         <v>77</v>
       </c>
@@ -17893,8 +17933,11 @@
         <f>74452.63</f>
         <v>74452.63</v>
       </c>
-    </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="R6" s="27">
+        <v>129688.53</v>
+      </c>
+    </row>
+    <row r="7" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B7" s="84" t="s">
         <v>97</v>
       </c>
@@ -17929,8 +17972,9 @@
       <c r="O7" s="27"/>
       <c r="P7" s="27"/>
       <c r="Q7" s="27"/>
-    </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="R7" s="27"/>
+    </row>
+    <row r="8" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B8" s="84" t="s">
         <v>8</v>
       </c>
@@ -17964,8 +18008,9 @@
       <c r="O8" s="27"/>
       <c r="P8" s="27"/>
       <c r="Q8" s="27"/>
-    </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="R8" s="27"/>
+    </row>
+    <row r="9" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B9" s="84" t="s">
         <v>99</v>
       </c>
@@ -18028,6 +18073,10 @@
       <c r="Q9" s="96">
         <f t="shared" si="2"/>
         <v>90631.83</v>
+      </c>
+      <c r="R9" s="96">
+        <f t="shared" ref="R9" si="3">SUM(R4:R8)</f>
+        <v>157869.14000000001</v>
       </c>
     </row>
   </sheetData>

--- a/parcelamentos_local.xlsx
+++ b/parcelamentos_local.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.121.21.252\controladoria\Vitor\TRIBUTARIO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A96A1E39-68A3-4984-8191-C9CAFE0E0404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74C77DA-36D4-41DB-98D4-55A7D809EA1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="804" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="804" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SALDO CREDOR INSS" sheetId="14" r:id="rId1"/>
@@ -425,28 +425,28 @@
     <t>SALDO</t>
   </si>
   <si>
-    <t>60/26</t>
-  </si>
-  <si>
-    <t>60/21</t>
-  </si>
-  <si>
     <t>60/10</t>
   </si>
   <si>
-    <t>60/8</t>
-  </si>
-  <si>
     <t>Parcelamento SC 30/08/2025</t>
-  </si>
-  <si>
-    <t>48/29</t>
   </si>
   <si>
     <t>Saldo Devedor Impostos Parcelados - Atualizado em 30.09.2026</t>
   </si>
   <si>
     <t>Status</t>
+  </si>
+  <si>
+    <t>48/48</t>
+  </si>
+  <si>
+    <t>60/28</t>
+  </si>
+  <si>
+    <t>60/22</t>
+  </si>
+  <si>
+    <t>60/16</t>
   </si>
 </sst>
 </file>
@@ -1260,12 +1260,6 @@
     <xf numFmtId="43" fontId="21" fillId="8" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1287,6 +1281,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1297,6 +1294,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5044,10 +5044,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="97"/>
-      <c r="B8" s="124" t="s">
+      <c r="B8" s="122" t="s">
         <v>101</v>
       </c>
-      <c r="C8" s="124"/>
+      <c r="C8" s="122"/>
       <c r="D8" s="103"/>
       <c r="E8" s="103"/>
       <c r="F8" s="103"/>
@@ -5529,15 +5529,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="125" t="s">
+      <c r="A1" s="123" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="126"/>
-      <c r="G1" s="127"/>
+      <c r="B1" s="124"/>
+      <c r="C1" s="124"/>
+      <c r="D1" s="124"/>
+      <c r="E1" s="124"/>
+      <c r="F1" s="124"/>
+      <c r="G1" s="125"/>
     </row>
     <row r="2" spans="1:7" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -5638,22 +5638,22 @@
     </row>
     <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="128" t="s">
+      <c r="A8" s="126" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="129"/>
-      <c r="C8" s="130"/>
+      <c r="B8" s="127"/>
+      <c r="C8" s="128"/>
       <c r="D8" s="12"/>
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
       <c r="G8" s="12"/>
     </row>
     <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="128" t="s">
-        <v>112</v>
-      </c>
-      <c r="B9" s="129"/>
-      <c r="C9" s="130"/>
+      <c r="A9" s="126" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" s="127"/>
+      <c r="C9" s="128"/>
       <c r="D9" s="13"/>
       <c r="E9" s="13"/>
     </row>
@@ -5684,14 +5684,14 @@
       </c>
       <c r="C11" s="17">
         <f>'PARCELAMENTO 06062024'!Q4</f>
-        <v>282040.54999999987</v>
+        <v>273226.78999999986</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E11" s="19">
-        <f>60-26</f>
-        <v>34</v>
+        <f>60-28</f>
+        <v>32</v>
       </c>
       <c r="F11" s="26"/>
     </row>
@@ -5704,14 +5704,14 @@
       </c>
       <c r="C12" s="17">
         <f>'PARCELAMENTO 05122024'!Q4</f>
-        <v>703166.67999999993</v>
+        <v>684662.3</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E12" s="19">
-        <f>60-21</f>
-        <v>39</v>
+        <f>60-22</f>
+        <v>38</v>
       </c>
       <c r="F12" s="24"/>
     </row>
@@ -5724,14 +5724,14 @@
       </c>
       <c r="C13" s="17">
         <f>'PARCELAMENTO 06062025'!Q4</f>
-        <v>1310298.6299999999</v>
+        <v>1280519.1199999999</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E13" s="19">
-        <f>60-10</f>
-        <v>50</v>
+        <f>60-16</f>
+        <v>44</v>
       </c>
       <c r="F13" s="24"/>
     </row>
@@ -5744,20 +5744,20 @@
       </c>
       <c r="C14" s="17">
         <f>'PARCELAMENTO 25112025 '!Q4</f>
-        <v>77603.11</v>
+        <v>73038.25</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E14" s="19">
-        <f>60-8</f>
-        <v>52</v>
+        <f>60-10</f>
+        <v>50</v>
       </c>
       <c r="F14" s="24"/>
     </row>
     <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="15" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B15" s="16">
         <v>45899</v>
@@ -5767,11 +5767,11 @@
         <v>0</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E15" s="19">
-        <f>48-29</f>
-        <v>19</v>
+        <f>48-48</f>
+        <v>0</v>
       </c>
       <c r="F15" s="24"/>
     </row>
@@ -5780,7 +5780,7 @@
       <c r="B16" s="20"/>
       <c r="C16" s="89">
         <f>SUM(C11:C15)</f>
-        <v>2373108.9699999993</v>
+        <v>2311446.46</v>
       </c>
       <c r="D16" s="20"/>
       <c r="E16" s="20"/>
@@ -6228,16 +6228,16 @@
         <v>528825.82999999996</v>
       </c>
       <c r="P4" s="33">
-        <f>I4+I5+I6+I7+I8+I9+I10+I11+I12+I13+I14+I15+I16+I17+I18+I19+I20+I21+I22+I23+I24+I25+I26+I27+I28+I29+I30+I31</f>
-        <v>246785.28000000009</v>
+        <f>I4+I5+I6+I7+I8+I9+I10+I11+I12+I13+I14+I15+I16+I17+I18+I19+I20+I21+I22+I23+I24+I25+I26+I27+I28+I29+I30+I31+I32</f>
+        <v>255599.0400000001</v>
       </c>
       <c r="Q4" s="34">
         <f>O4-P4</f>
-        <v>282040.54999999987</v>
+        <v>273226.78999999986</v>
       </c>
       <c r="R4" s="34">
-        <f>J5+J6+J7+J8+J9+J10+J11+J12+J13+J14+J15+J16+J17+J18+J19+J20+J21+J22+J23+J24+J25+J26+J27+J28+J29+J30+J31</f>
-        <v>33892.76</v>
+        <f>J5+J6+J7+J8+J9+J10+J11+J12+J13+J14+J15+J16+J17+J18+J19+J20+J21+J22+J23+J24+J25+J26+J27+J28+J29+J30+J31+J32</f>
+        <v>36517.490000000005</v>
       </c>
     </row>
     <row r="5" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
@@ -6321,13 +6321,13 @@
         <f>M5-I6</f>
         <v>511198.30999999994</v>
       </c>
-      <c r="O6" s="122" t="s">
+      <c r="O6" s="129" t="s">
         <v>89</v>
       </c>
-      <c r="P6" s="122"/>
+      <c r="P6" s="129"/>
       <c r="Q6" s="82">
         <f>(Q4/O4)-1</f>
-        <v>-0.46666646370129106</v>
+        <v>-0.4833331231191943</v>
       </c>
     </row>
     <row r="7" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
@@ -6455,11 +6455,11 @@
         <f>M8-I9</f>
         <v>484757.02999999991</v>
       </c>
-      <c r="O9" s="131" t="s">
+      <c r="O9" s="130" t="s">
         <v>87</v>
       </c>
-      <c r="P9" s="131"/>
-      <c r="Q9" s="131"/>
+      <c r="P9" s="130"/>
+      <c r="Q9" s="130"/>
     </row>
     <row r="10" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="81" t="s">
@@ -6501,11 +6501,11 @@
         <f t="shared" ref="M10:M63" si="2">M9-I10</f>
         <v>475943.2699999999</v>
       </c>
-      <c r="O10" s="132" t="s">
+      <c r="O10" s="131" t="s">
         <v>88</v>
       </c>
-      <c r="P10" s="132"/>
-      <c r="Q10" s="132"/>
+      <c r="P10" s="131"/>
+      <c r="Q10" s="131"/>
     </row>
     <row r="11" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="81" t="s">
@@ -6547,11 +6547,11 @@
         <f t="shared" si="2"/>
         <v>467129.50999999989</v>
       </c>
-      <c r="O11" s="133" t="s">
+      <c r="O11" s="132" t="s">
         <v>90</v>
       </c>
-      <c r="P11" s="133"/>
-      <c r="Q11" s="133"/>
+      <c r="P11" s="132"/>
+      <c r="Q11" s="132"/>
     </row>
     <row r="12" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="83" t="s">
@@ -6703,7 +6703,7 @@
         <v>8813.76</v>
       </c>
       <c r="J15" s="77">
-        <f t="shared" ref="J15:J31" si="3">K15-I15</f>
+        <f t="shared" ref="J15:J32" si="3">K15-I15</f>
         <v>906.93000000000029</v>
       </c>
       <c r="K15" s="28">
@@ -7130,10 +7130,12 @@
       <c r="I32" s="28">
         <v>8813.76</v>
       </c>
-      <c r="J32" s="77"/>
+      <c r="J32" s="77">
+        <f t="shared" si="3"/>
+        <v>2624.7299999999996</v>
+      </c>
       <c r="K32" s="28">
-        <f t="shared" si="1"/>
-        <v>8813.76</v>
+        <v>11438.49</v>
       </c>
       <c r="L32" s="29">
         <v>46326</v>
@@ -7869,11 +7871,11 @@
       </c>
       <c r="J64" s="87">
         <f>SUM(J4:J63)</f>
-        <v>33892.76</v>
+        <v>36517.490000000005</v>
       </c>
       <c r="K64" s="87">
         <f>SUM(K4:K63)</f>
-        <v>562718.5900000002</v>
+        <v>565343.32000000018</v>
       </c>
       <c r="L64" s="43"/>
       <c r="M64" s="44"/>
@@ -8268,16 +8270,16 @@
         <v>1110263.04</v>
       </c>
       <c r="P4" s="33">
-        <f>I4+I5+I6+I7+I8+I9+I10+I11+I12+I13+I14+I15+I16+I17+I18+I19+I20+I21+I22+I23+I24+I25</f>
-        <v>407096.36000000004</v>
+        <f>I4+I5+I6+I7+I8+I9+I10+I11+I12+I13+I14+I15+I16+I17+I18+I19+I20+I21+I22+I23+I24+I25+I26</f>
+        <v>425600.74000000005</v>
       </c>
       <c r="Q4" s="34">
         <f>O4-P4</f>
-        <v>703166.67999999993</v>
+        <v>684662.3</v>
       </c>
       <c r="R4" s="34">
-        <f>J5+J6+J7+J8+J9+J10+J11+J12+J13+J14+J15+J16+J17+J18+J19+J20+J21+J22+J23+J24+J25</f>
-        <v>46880.719999999979</v>
+        <f>J5+J6+J7+J8+J9+J10+J11+J12+J13+J14+J15+J16+J17+J18+J19+J20+J21+J22+J23+J24+J25+J26</f>
+        <v>51416.139999999978</v>
       </c>
     </row>
     <row r="5" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
@@ -8361,13 +8363,13 @@
         <f>M5-I6</f>
         <v>1073254.2800000003</v>
       </c>
-      <c r="O6" s="122" t="s">
+      <c r="O6" s="129" t="s">
         <v>89</v>
       </c>
-      <c r="P6" s="122"/>
+      <c r="P6" s="129"/>
       <c r="Q6" s="82">
         <f>Q4/O4-1</f>
-        <v>-0.36666658740617009</v>
+        <v>-0.38333325047008682</v>
       </c>
     </row>
     <row r="7" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
@@ -8480,7 +8482,7 @@
         <v>18504.38</v>
       </c>
       <c r="J9" s="28">
-        <f t="shared" ref="J9:J25" si="3">K9-I9</f>
+        <f t="shared" ref="J9:J26" si="3">K9-I9</f>
         <v>928.90999999999985</v>
       </c>
       <c r="K9" s="28">
@@ -8493,11 +8495,11 @@
         <f t="shared" si="2"/>
         <v>1017741.1400000004</v>
       </c>
-      <c r="O9" s="134" t="s">
+      <c r="O9" s="133" t="s">
         <v>86</v>
       </c>
-      <c r="P9" s="134"/>
-      <c r="Q9" s="134"/>
+      <c r="P9" s="133"/>
+      <c r="Q9" s="133"/>
     </row>
     <row r="10" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="79" t="s">
@@ -8539,11 +8541,11 @@
         <f t="shared" si="2"/>
         <v>999236.76000000036</v>
       </c>
-      <c r="O10" s="131" t="s">
+      <c r="O10" s="130" t="s">
         <v>87</v>
       </c>
-      <c r="P10" s="131"/>
-      <c r="Q10" s="131"/>
+      <c r="P10" s="130"/>
+      <c r="Q10" s="130"/>
     </row>
     <row r="11" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="79" t="s">
@@ -8585,11 +8587,11 @@
         <f t="shared" si="2"/>
         <v>980732.38000000035</v>
       </c>
-      <c r="O11" s="132" t="s">
+      <c r="O11" s="131" t="s">
         <v>88</v>
       </c>
-      <c r="P11" s="132"/>
-      <c r="Q11" s="132"/>
+      <c r="P11" s="131"/>
+      <c r="Q11" s="131"/>
     </row>
     <row r="12" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="79" t="s">
@@ -9204,8 +9206,13 @@
       <c r="I26" s="28">
         <v>18504.38</v>
       </c>
-      <c r="J26" s="28"/>
-      <c r="K26" s="28"/>
+      <c r="J26" s="28">
+        <f t="shared" si="3"/>
+        <v>4535.4199999999983</v>
+      </c>
+      <c r="K26" s="28">
+        <v>23039.8</v>
+      </c>
       <c r="L26" s="29">
         <v>46326</v>
       </c>
@@ -10464,11 +10471,11 @@
       </c>
       <c r="J64" s="78">
         <f>SUM(J4:J63)</f>
-        <v>46880.719999999979</v>
+        <v>51416.139999999978</v>
       </c>
       <c r="K64" s="78">
         <f>SUM(K4:K63)</f>
-        <v>435472.7</v>
+        <v>458512.5</v>
       </c>
       <c r="L64" s="43"/>
       <c r="M64" s="44"/>
@@ -11388,16 +11395,16 @@
         <v>1786770.79</v>
       </c>
       <c r="P4" s="33">
-        <f>I4+I5+I6+I7+I8+I9+I10+I11+I12+I13+I14+I15+I16+I17+I18+I19</f>
-        <v>476472.16000000009</v>
+        <f>I4+I5+I6+I7+I8+I9+I10+I11+I12+I13+I14+I15+I16+I17+I18+I19+I20</f>
+        <v>506251.6700000001</v>
       </c>
       <c r="Q4" s="34">
         <f>O4-P4</f>
-        <v>1310298.6299999999</v>
+        <v>1280519.1199999999</v>
       </c>
       <c r="R4" s="34">
-        <f>J5+J6+J7+J8+J9+J10+J11+J12+J13+J14+J15+J16+J17+J18+J19</f>
-        <v>41566.170000000027</v>
+        <f>J5+J6+J7+J8+J9+J10+J11+J12+J13+J14+J15+J16+J17+J18+J19+J20</f>
+        <v>47000.930000000022</v>
       </c>
     </row>
     <row r="5" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
@@ -11427,7 +11434,7 @@
         <v>29779.51</v>
       </c>
       <c r="J5" s="77">
-        <f t="shared" ref="J5:J19" si="1">K5-I5</f>
+        <f t="shared" ref="J5:J20" si="1">K5-I5</f>
         <v>297.79000000000087</v>
       </c>
       <c r="K5" s="28">
@@ -11481,13 +11488,13 @@
         <f>M5-I6</f>
         <v>1727211.77</v>
       </c>
-      <c r="O6" s="122" t="s">
+      <c r="O6" s="129" t="s">
         <v>89</v>
       </c>
-      <c r="P6" s="122"/>
+      <c r="P6" s="129"/>
       <c r="Q6" s="82">
         <f>(Q4/O4)-1</f>
-        <v>-0.26666663831011039</v>
+        <v>-0.28333330320449224</v>
       </c>
     </row>
     <row r="7" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
@@ -11615,11 +11622,11 @@
         <f t="shared" ref="M9:M63" si="2">M8-I9</f>
         <v>1637873.24</v>
       </c>
-      <c r="O9" s="131" t="s">
+      <c r="O9" s="130" t="s">
         <v>87</v>
       </c>
-      <c r="P9" s="131"/>
-      <c r="Q9" s="131"/>
+      <c r="P9" s="130"/>
+      <c r="Q9" s="130"/>
     </row>
     <row r="10" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="81" t="s">
@@ -11661,11 +11668,11 @@
         <f t="shared" si="2"/>
         <v>1608093.73</v>
       </c>
-      <c r="O10" s="132" t="s">
+      <c r="O10" s="131" t="s">
         <v>88</v>
       </c>
-      <c r="P10" s="132"/>
-      <c r="Q10" s="132"/>
+      <c r="P10" s="131"/>
+      <c r="Q10" s="131"/>
     </row>
     <row r="11" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="81" t="s">
@@ -11707,11 +11714,11 @@
         <f t="shared" si="2"/>
         <v>1578314.22</v>
       </c>
-      <c r="O11" s="133" t="s">
+      <c r="O11" s="132" t="s">
         <v>90</v>
       </c>
-      <c r="P11" s="133"/>
-      <c r="Q11" s="133"/>
+      <c r="P11" s="132"/>
+      <c r="Q11" s="132"/>
     </row>
     <row r="12" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="81" t="s">
@@ -12006,10 +12013,13 @@
       <c r="I20" s="28">
         <v>29779.51</v>
       </c>
-      <c r="J20" s="77"/>
+      <c r="J20" s="77">
+        <f t="shared" si="1"/>
+        <v>5434.7599999999984</v>
+      </c>
       <c r="K20" s="28">
-        <f t="shared" ref="K20:K63" si="3">I20+J20</f>
-        <v>29779.51</v>
+        <f>35214.27</f>
+        <v>35214.269999999997</v>
       </c>
       <c r="L20" s="29">
         <v>45961</v>
@@ -12031,7 +12041,7 @@
       </c>
       <c r="J21" s="77"/>
       <c r="K21" s="28">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="K21:K63" si="3">I21+J21</f>
         <v>29779.51</v>
       </c>
       <c r="L21" s="29">
@@ -13021,11 +13031,11 @@
       </c>
       <c r="J64" s="78">
         <f>SUM(J4:J63)</f>
-        <v>41566.170000000027</v>
+        <v>47000.930000000022</v>
       </c>
       <c r="K64" s="78">
         <f>SUM(K4:K63)</f>
-        <v>1828336.9600000002</v>
+        <v>1833771.7200000002</v>
       </c>
       <c r="L64" s="43"/>
       <c r="M64" s="44"/>
@@ -13423,16 +13433,16 @@
         <v>91297.69</v>
       </c>
       <c r="P4" s="33">
-        <f>I4+I5+I6+I7+I8+I9+I10+I11+I12</f>
-        <v>13694.579999999998</v>
+        <f>I4+I5+I6+I7+I8+I9+I10+I11+I12+I13+I14+I15</f>
+        <v>18259.439999999995</v>
       </c>
       <c r="Q4" s="34">
         <f>O4-P4</f>
-        <v>77603.11</v>
+        <v>73038.25</v>
       </c>
       <c r="R4" s="34">
         <f>J5+J6+J7+J8+J9+J10+J11+J12+J13+J14+J15+J16+J17+J18+J19+J20+J21+J22+J23+J24+J25+J26+J27+J28+J29</f>
-        <v>744.94000000000096</v>
+        <v>1118.0600000000013</v>
       </c>
     </row>
     <row r="5" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
@@ -13474,7 +13484,7 @@
         <v>1521.62</v>
       </c>
       <c r="J6" s="77">
-        <f t="shared" ref="J6:J13" si="1">K6-I6</f>
+        <f t="shared" ref="J6:J15" si="1">K6-I6</f>
         <v>33.770000000000209</v>
       </c>
       <c r="K6" s="28">
@@ -13487,13 +13497,13 @@
         <f>M5-I6</f>
         <v>88254.450000000012</v>
       </c>
-      <c r="O6" s="122" t="s">
+      <c r="O6" s="129" t="s">
         <v>89</v>
       </c>
-      <c r="P6" s="122"/>
+      <c r="P6" s="129"/>
       <c r="Q6" s="82">
         <f>(Q4/O4)-1</f>
-        <v>-0.14999919494129588</v>
+        <v>-0.19999892658839458</v>
       </c>
     </row>
     <row r="7" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
@@ -13576,11 +13586,11 @@
         <f t="shared" ref="M9:M63" si="2">M8-I9</f>
         <v>83689.590000000026</v>
       </c>
-      <c r="O9" s="131" t="s">
+      <c r="O9" s="130" t="s">
         <v>87</v>
       </c>
-      <c r="P9" s="131"/>
-      <c r="Q9" s="131"/>
+      <c r="P9" s="130"/>
+      <c r="Q9" s="130"/>
     </row>
     <row r="10" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="39"/>
@@ -13607,11 +13617,11 @@
         <f t="shared" si="2"/>
         <v>82167.97000000003</v>
       </c>
-      <c r="O10" s="132" t="s">
+      <c r="O10" s="131" t="s">
         <v>88</v>
       </c>
-      <c r="P10" s="132"/>
-      <c r="Q10" s="132"/>
+      <c r="P10" s="131"/>
+      <c r="Q10" s="131"/>
     </row>
     <row r="11" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="39"/>
@@ -13638,11 +13648,11 @@
         <f t="shared" si="2"/>
         <v>80646.350000000035</v>
       </c>
-      <c r="O11" s="133" t="s">
+      <c r="O11" s="132" t="s">
         <v>90</v>
       </c>
-      <c r="P11" s="133"/>
-      <c r="Q11" s="133"/>
+      <c r="P11" s="132"/>
+      <c r="Q11" s="132"/>
     </row>
     <row r="12" spans="2:18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="39"/>
@@ -13707,10 +13717,12 @@
       <c r="I14" s="27">
         <v>1521.62</v>
       </c>
-      <c r="J14" s="77"/>
+      <c r="J14" s="77">
+        <f t="shared" si="1"/>
+        <v>186.56000000000017</v>
+      </c>
       <c r="K14" s="28">
-        <f t="shared" si="0"/>
-        <v>1521.62</v>
+        <v>1708.18</v>
       </c>
       <c r="L14" s="29">
         <v>46293</v>
@@ -13731,10 +13743,12 @@
       <c r="I15" s="27">
         <v>1521.62</v>
       </c>
-      <c r="J15" s="77"/>
+      <c r="J15" s="77">
+        <f t="shared" si="1"/>
+        <v>186.56000000000017</v>
+      </c>
       <c r="K15" s="28">
-        <f t="shared" si="0"/>
-        <v>1521.62</v>
+        <v>1708.18</v>
       </c>
       <c r="L15" s="29">
         <v>46323</v>
@@ -15209,7 +15223,7 @@
         <v>23</v>
       </c>
       <c r="N3" s="30" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="P3" s="36" t="s">
         <v>24</v>
@@ -15325,10 +15339,10 @@
       <c r="N6" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="P6" s="122" t="s">
+      <c r="P6" s="129" t="s">
         <v>89</v>
       </c>
-      <c r="Q6" s="122"/>
+      <c r="Q6" s="129"/>
       <c r="R6" s="82">
         <f>(R4/P4)-1</f>
         <v>-1</v>
@@ -15427,9 +15441,9 @@
       <c r="N9" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="P9" s="123"/>
-      <c r="Q9" s="123"/>
-      <c r="R9" s="123"/>
+      <c r="P9" s="134"/>
+      <c r="Q9" s="134"/>
+      <c r="R9" s="134"/>
     </row>
     <row r="10" spans="2:19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="39"/>
@@ -15459,9 +15473,9 @@
       <c r="N10" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="P10" s="123"/>
-      <c r="Q10" s="123"/>
-      <c r="R10" s="123"/>
+      <c r="P10" s="134"/>
+      <c r="Q10" s="134"/>
+      <c r="R10" s="134"/>
     </row>
     <row r="11" spans="2:19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="39"/>
@@ -15491,9 +15505,9 @@
       <c r="N11" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="P11" s="123"/>
-      <c r="Q11" s="123"/>
-      <c r="R11" s="123"/>
+      <c r="P11" s="134"/>
+      <c r="Q11" s="134"/>
+      <c r="R11" s="134"/>
     </row>
     <row r="12" spans="2:19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="39"/>
